--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.0-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.0-2026-07-01.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>34 screens/variants across 5 tabs · 93 data-lineage rows (every on-screen number traced to its one engine) · 13 net-new engine specs (safe-to-spend paycheck, account-sync seam, dated canonical grid, scenario composer + adoption contract, multi-goal weigher, scam flag, bond rate-sensitivity).</t>
+          <t>37 screens/variants across 5 tabs · 94 data-lineage rows (every on-screen number traced to its one engine) · 13 net-new engine specs (safe-to-spend paycheck, account-sync seam, dated canonical grid, scenario composer + adoption contract, multi-goal weigher, scam flag, bond rate-sensitivity).</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -824,12 +824,12 @@
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Net worth tab — main screen</t>
+          <t>Idle cash — nudge detail</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>One true picture of everything you own and owe. A glance (one number, its yearly change, a simple trend) that expands into groups — by what it is, or by where it's held — with every account showing where its number comes from and how fresh it is. Money movement lives in the Cash flow tab; this is th</t>
+          <t>The designed landing for Home's idle-cash nudge (previously a dead-end): the fact, which accounts it sits in, and the plain comparison math of what that cash could earn — estimates, named rates, no instruction to act.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>REUSE-HEAVY: NetWorthScreen.tsx already has the donut/summary, class grouping, institution grouping, identity line, runway card, add/edit sheets and hide-balances. Net-new: summary-that-expands shell, source/last_synced fields + chips, monthly snapshot series for the trend, cash-flow glance tile, three-way add chooser, Account detail route.</t>
+          <t>NET-NEW light screen; closes walkthrough dead-end #1 (Home's marquee nudge led to an Invest tab with no cash section).</t>
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
@@ -853,27 +853,27 @@
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Connect flow — choose institution + honest consent</t>
+          <t>401(k) room this year — nudge detail</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>working</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Let a cautious 55–70 user link an account with zero surprises: pick the institution, read exactly what happens to their data (the approved honest wording — data flows through Plaid's servers; we no longer say 'never leaves your device'), then hand off to Plaid's own sign-in. Manual and file import a</t>
+          <t>The designed landing for Home's 401(k)-room nudge (previously pointing at a legacy screen): the limit, what's in, what's left, the per-month translation, and the honest 'change it at your employer' line. Links to the forward what-if to see the effect of using the room.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>NET-NEW screen (F1). Reuses the existing sheet/navigation patterns and the KeyboardAwareSheet component; the server token exchange follows the existing functions/ proxy pattern. The chooser reuses the two existing paths untouched.</t>
+          <t>NET-NEW light screen aligned with the live app's contribution-room surface; closes walkthrough dead-end #2.</t>
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Connect flow — accounts found + merge / reconcile</t>
+          <t>Net worth tab — main screen</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>The anti-duplicate gate. After Plaid returns the institution's accounts, the user picks which to track, and anything that looks like an account they already have becomes a merge question — connect-over-existing updates the existing row (keeping its history and settings) instead of creating a twin. T</t>
+          <t>One true picture of everything you own and owe. A glance (one number, its yearly change, a simple trend) that expands into groups — by what it is, or by where it's held — with every account showing where its number comes from and how fresh it is. Money movement lives in the Cash flow tab; this is th</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>NET-NEW screen (F1), but thin: all writes go through existing store.addAsset/updateAsset; the merge sheet component is built once here and REUSED by Import v2 (screen 4). Matching logic is a small pure helper (unit-testable like holdingsImport).</t>
+          <t>REUSE-HEAVY: NetWorthScreen.tsx already has the donut/summary, class grouping, institution grouping, identity line, runway card, add/edit sheets and hide-balances. Net-new: summary-that-expands shell, source/last_synced fields + chips, monthly snapshot series for the trend, cash-flow glance tile, three-way add chooser, Account detail route.</t>
         </is>
       </c>
       <c r="F11" s="4" t="n"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Import from a file v2 — pick, review, merge</t>
+          <t>Connect flow — choose institution + honest consent</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Import a spreadsheet file downloaded from a brokerage, now with the institution captured, every holding's classification shown AND correctable before saving (crypto, currencies and commodities land in Alternatives, Treasury bills in Cash — not mis-filed as stocks), and a merge step so re-importing t</t>
+          <t>Let a cautious 55–70 user link an account with zero surprises: pick the institution, read exactly what happens to their data (the approved honest wording — data flows through Plaid's servers; we no longer say 'never leaves your device'), then hand off to Plaid's own sign-in. Manual and file import a</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>MOSTLY REUSE: parser, preview, save path and error handling exist and are tested (src/domain/import/holdingsImport.test.ts). Net-new: institution field, crypto/currency/commodity patterns in classifyHolding (pure-function change, easy unit tests), per-row class picker, merge step (shared component from screen 3), provenance fields on save.</t>
+          <t>NET-NEW screen (F1). Reuses the existing sheet/navigation patterns and the KeyboardAwareSheet component; the server token exchange follows the existing functions/ proxy pattern. The chooser reuses the two existing paths untouched.</t>
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Account detail — any class</t>
+          <t>Connect flow — accounts found + merge / reconcile</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>One page per account, whatever it is: the balance, where the number comes from and how fresh it is, what the account holds, its full activity history, and the right record-activity buttons for its class — cash accounts get deposit/withdraw/transfer right here (today those are hidden inside the stock</t>
+          <t>The anti-duplicate gate. After Plaid returns the institution's accounts, the user picks which to track, and anything that looks like an account they already have becomes a merge question — connect-over-existing updates the existing row (keeping its history and settings) instead of creating a twin. T</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>NET-NEW screen, OLD parts: the transactions engine, ledger, trade-sheet interaction pattern (PerformanceScreen.tsx) and editors all exist. Work = one detail route, per-class action mapping, value_as_of field + 6-month rule, and rewiring bond/alt sell (and new buy) through recordTransaction instead of silent balance edits.</t>
+          <t>NET-NEW screen (F1), but thin: all writes go through existing store.addAsset/updateAsset; the merge sheet component is built once here and REUSED by Import v2 (screen 4). Matching logic is a small pure helper (unit-testable like holdingsImport).</t>
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bond editor — add, buy, sell, as-of</t>
+          <t>Import from a file v2 — pick, review, merge</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Track an individual bond or Treasury bill honestly: its face value, interest payments, maturity, a current value that carries its date (with a nudge when it goes stale), and — new in v1.1 — both buying more and selling recorded as visible history, not silent edits.</t>
+          <t>Import a spreadsheet file downloaded from a brokerage, now with the institution captured, every holding's classification shown AND correctable before saving (crypto, currencies and commodities land in Alternatives, Treasury bills in Cash — not mis-filed as stocks), and a merge step so re-importing t</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>REUSE: BondEditor form, validity, date picker, double-count guard, proportional-sale math, metrics. Net-new: 'treasury' kind entry, value_as_of + nudge, Buy-more action, and rewiring sale/buy/coupon through recordTransaction (small, well-tested seam — applyTransaction already supports all three types).</t>
+          <t>MOSTLY REUSE: parser, preview, save path and error handling exist and are tested (src/domain/import/holdingsImport.test.ts). Net-new: institution field, crypto/currency/commodity patterns in classifyHolding (pure-function change, easy unit tests), per-row class picker, merge step (shared component from screen 3), provenance fields on save.</t>
         </is>
       </c>
       <c r="F14" s="4" t="n"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Alternative editor — add, buy, sell, as-of</t>
+          <t>Account detail — any class</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Track anything that isn't a stock, bond or bank account — crypto, private funds, gold, annuities, option contracts — at a value you set, with that value carrying its date, a nudge when it goes stale, and buying/selling recorded as visible history (today: sale-only, and it leaves no trace).</t>
+          <t>One page per account, whatever it is: the balance, where the number comes from and how fresh it is, what the account holds, its full activity history, and the right record-activity buttons for its class — cash accounts get deposit/withdraw/transfer right here (today those are hidden inside the stock</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>REUSE: the whole AltEditor form, hints, benchmarks, sale confirmations and delete flow. Net-new: value_as_of + nudge, Buy-more, and routing buy/sell through recordTransaction — same small seam as the bond editor, shared action-sheet component.</t>
+          <t>NET-NEW screen, OLD parts: the transactions engine, ledger, trade-sheet interaction pattern (PerformanceScreen.tsx) and editors all exist. Work = one detail route, per-class action mapping, value_as_of field + 6-month rule, and rewiring bond/alt sell (and new buy) through recordTransaction instead of silent balance edits.</t>
         </is>
       </c>
       <c r="F15" s="4" t="n"/>
@@ -1027,27 +1027,27 @@
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Invest</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Invest — main (glance then drill)</t>
+          <t>Bond editor — add, buy, sell, as-of</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>both</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Grow &amp; Track hero for 55-70: one glance answers 'how am I doing?', everything below is a tap-deeper drill. Covers ALL investment classes — stocks/funds, bonds, alternatives — in one place. — The one screen that tells the truth about how the whole portfolio is doing: total return in dollars and perce</t>
+          <t>Track an individual bond or Treasury bill honestly: its face value, interest payments, maturity, a current value that carries its date (with a nudge when it goes stale), and — new in v1.1 — both buying more and selling recorded as visible history, not silent edits.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Mostly EXISTING: this screen is PerformanceScreen.tsx re-shelled to the glance-then-drill order, plus the Bonds and Alternatives groups folded in from BondsScreen.tsx / OtherInvestmentsScreen.tsx (today they are separate screens). NET-NEW: value_as_of field + freshness nudge, holding-level concentration helper, look-back entry. Route: the Invest tab replaces the current Performance entry; keep old routes redirecting.</t>
+          <t>REUSE: BondEditor form, validity, date picker, double-count guard, proportional-sale math, metrics. Net-new: 'treasury' kind entry, value_as_of + nudge, Buy-more action, and rewiring sale/buy/coupon through recordTransaction (small, well-tested seam — applyTransaction already supports all three types).</t>
         </is>
       </c>
       <c r="F16" s="4" t="n"/>
@@ -1056,12 +1056,12 @@
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Invest</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Holding detail — stock / fund (equity)</t>
+          <t>Alternative editor — add, buy, sell, as-of</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Drill: one ticker's full story — what you own, what you paid, what it's worth, how it compares, and the tax facts if you sold. — Everything about one stock or fund in plain terms: current worth, gain since purchase, an honest same-period market comparison, the purchase history that explains the cost</t>
+          <t>Track anything that isn't a stock, bond or bank account — crypto, private funds, gold, annuities, option contracts — at a value you set, with that value carrying its date, a nudge when it goes stale, and buying/selling recorded as visible history (today: sale-only, and it leaves no trace).</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Mostly EXISTING data + components; the page itself is NET-NEW as a routed detail screen (today PerformanceScreen shows expandable rows, not a full-screen drill). Low risk: it is a re-layout of tested helpers.</t>
+          <t>REUSE: the whole AltEditor form, hints, benchmarks, sale confirmations and delete flow. Net-new: value_as_of + nudge, Buy-more, and routing buy/sell through recordTransaction — same small seam as the bond editor, shared action-sheet component.</t>
         </is>
       </c>
       <c r="F17" s="4" t="n"/>
@@ -1090,22 +1090,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Holding detail — bond</t>
+          <t>Invest — main (glance then drill)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>working</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Worry-less lens: a bond owner mostly needs to know what it pays, when it matures, what it's worth today, and — new — roughly how its value moves if interest rates move. — One bond, fully explained: what it pays every year, when the face value comes back, what it's worth right now (and how old that n</t>
+          <t>Grow &amp; Track hero for 55-70: one glance answers 'how am I doing?', everything below is a tap-deeper drill. Covers ALL investment classes — stocks/funds, bonds, alternatives — in one place. — The one screen that tells the truth about how the whole portfolio is doing: total return in dollars and perce</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Bond math and sale flow EXIST (BondsScreen.tsx + src/domain/bonds). NET-NEW: value_as_of + freshness nudge, bondRateSensitivity helper + card, shared ReportedReturnEditor. This page replaces BondsScreen's expandable row as a routed detail; keep bondSummary for the group header on the main screen.</t>
+          <t>Mostly EXISTING: this screen is PerformanceScreen.tsx re-shelled to the glance-then-drill order, plus the Bonds and Alternatives groups folded in from BondsScreen.tsx / OtherInvestmentsScreen.tsx (today they are separate screens). NET-NEW: value_as_of field + freshness nudge, holding-level concentration helper, look-back entry. Route: the Invest tab replaces the current Performance entry; keep old routes redirecting.</t>
         </is>
       </c>
       <c r="F18" s="4" t="n"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Holding detail — alternative (crypto, gold, private stakes, annuities, other)</t>
+          <t>Holding detail — stock / fund (equity)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>These are the forgotten assets — manually valued, rarely updated. The page's job is a current value the user believes, dated, and easy to refresh. — Keep manually-valued investments honest: show the value WITH its date, nudge (not nag) when it's stale, let the user update it in one tap, and let them</t>
+          <t>Drill: one ticker's full story — what you own, what you paid, what it's worth, how it compares, and the tax facts if you sold. — Everything about one stock or fund in plain terms: current worth, gain since purchase, an honest same-period market comparison, the purchase history that explains the cost</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Sale flow and summaries EXIST (OtherInvestmentsScreen.tsx + src/domain/alternatives). NET-NEW: value_as_of + nudge (shared with bonds), reported-return card placement, look-back for manual assets (v2-able: ship the entry hidden for manual assets if dated value pairs are missing). This page replaces OtherInvestmentsScreen's row expansion as a routed detail.</t>
+          <t>Mostly EXISTING data + components; the page itself is NET-NEW as a routed detail screen (today PerformanceScreen shows expandable rows, not a full-screen drill). Low risk: it is a re-layout of tested helpers.</t>
         </is>
       </c>
       <c r="F19" s="4" t="n"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Look back — what if I'd moved money?</t>
+          <t>Holding detail — bond</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>The truth-teller answering hindsight questions with real past prices — closure, not regret-bait, and never a recommendation about tomorrow. — Answer the question every investor actually asks — 'what if I'd moved that money?' — with real historical prices and honest wording. It is explicitly backward</t>
+          <t>Worry-less lens: a bond owner mostly needs to know what it pays, when it matures, what it's worth today, and — new — roughly how its value moves if interest rates move. — One bond, fully explained: what it pays every year, when the face value comes back, what it's worth right now (and how old that n</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>NET-NEW screen + one small pure helper; all price data and pickers exist. Ship behind the Invest main card. Keep the forward what-if (sliders, on the Plan/Invest boundary per high-level design) visually distinct: forward uses sliders + range, backward uses dropdowns + exact past numbers.</t>
+          <t>Bond math and sale flow EXIST (BondsScreen.tsx + src/domain/bonds). NET-NEW: value_as_of + freshness nudge, bondRateSensitivity helper + card, shared ReportedReturnEditor. This page replaces BondsScreen's expandable row as a routed detail; keep bondSummary for the group header on the main screen.</t>
         </is>
       </c>
       <c r="F20" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>What if I add more? (forward what-if)</t>
+          <t>Holding detail — alternative (crypto, gold, private stakes, annuities, other)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>The forward companion to Look back, promised in the approved high-level design: slide 'add $X each month', pick a growth rate, and see where the path lands by your retire age — as a range across bad-to-good markets, labeled an estimate, never a promise. Ends in the shared Use-this-plan sheet so adop</t>
+          <t>These are the forgotten assets — manually valued, rarely updated. The page's job is a current value the user believes, dated, and easy to refresh. — Keep manually-valued investments honest: show the value WITH its date, nudge (not nag) when it's stale, let the user update it in one tap, and let them</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Engines EXIST (projectNestEgg, simulate band); screen is NET-NEW and satisfies the approved high-level design's Invest what-if (verification blocker #2). Distinct-from-Look-back rule per the Look-back build note.</t>
+          <t>Sale flow and summaries EXIST (OtherInvestmentsScreen.tsx + src/domain/alternatives). NET-NEW: value_as_of + nudge (shared with bonds), reported-return card placement, look-back for manual assets (v2-able: ship the entry hidden for manual assets if dated value pairs are missing). This page replaces OtherInvestmentsScreen's row expansion as a routed detail.</t>
         </is>
       </c>
       <c r="F21" s="4" t="n"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Record a transaction + History</t>
+          <t>Look back — what if I'd moved money?</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Chief of staff keeping the books: every buy, sale, dividend, coupon or cash move — for stocks, bonds AND alternatives — lands in one dated, auditable ledger. — One recording flow for every kind of money movement across all three investment classes, with guardrails (can't spend cash you don't have, c</t>
+          <t>The truth-teller answering hindsight questions with real past prices — closure, not regret-bait, and never a recommendation about tomorrow. — Answer the question every investor actually asks — 'what if I'd moved that money?' — with real historical prices and honest wording. It is explicitly backward</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Fully EXISTING (TransactionSheet + HistorySheet + ledger engine). Work is placement: surface both from the Invest tab and every detail page, and add COUPON/alt-sale rows to the visible history copy (types already exist in the ledger).</t>
+          <t>NET-NEW screen + one small pure helper; all price data and pickers exist. Ship behind the Invest main card. Keep the forward what-if (sliders, on the Plan/Invest boundary per high-level design) visually distinct: forward uses sliders + range, backward uses dropdowns + exact past numbers.</t>
         </is>
       </c>
       <c r="F22" s="4" t="n"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Empty, stale, hidden &amp; loading states</t>
+          <t>What if I add more? (forward what-if)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>The first five seconds and the worst five seconds: brand-new users, dead prices, public places, slow networks. These states carry the trust promise as much as the happy path. — Define exactly how the Invest tab behaves when there is nothing, when data is old or missing, when amounts must be private,</t>
+          <t>The forward companion to Look back, promised in the approved high-level design: slide 'add $X each month', pick a growth rate, and see where the path lands by your retire age — as a range across bad-to-good markets, labeled an estimate, never a promise. Ends in the shared Use-this-plan sheet so adop</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>All mechanisms EXIST; the work is a written state contract per screen + tests: (1) never $0 for a priced holding with no price, (2) never an unlabeled stale number, (3) no raw money() calls on the Invest tab (extend scripts/check-ui-tests.sh style gate), (4) empty-state renders with zero crashes in the 28-screen smoke suite.</t>
+          <t>Engines EXIST (projectNestEgg, simulate band); screen is NET-NEW and satisfies the approved high-level design's Invest what-if (verification blocker #2). Distinct-from-Look-back rule per the Look-back build note.</t>
         </is>
       </c>
       <c r="F23" s="4" t="n"/>
@@ -1259,27 +1259,27 @@
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Invest</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cash flow main — retired</t>
+          <t>Record a transaction + History</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>both</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>The retiree's paycheck, told truthfully month by month. The big number is what is safe to spend THIS month and THIS year, split into its real parts: the guaranteed money that arrives (Social Security, pension, annuity — each named), plus a safe draw from savings, minus the big bills that land in tha</t>
+          <t>Chief of staff keeping the books: every buy, sale, dividend, coupon or cash move — for stocks, bonds AND alternatives — lands in one dated, auditable ledger. — One recording flow for every kind of money movement across all three investment classes, with guardrails (can't spend cash you don't have, c</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The hero and decomposition are net-new (F5). The bars are a re-skin of cashflowYear once it is promoted to the F2 canonical grid — the rolling dated window, year-wrap labels, and month+year placement already exist in that helper. Draw-order and will-it-last reuse src/domain/decumulation and src/domain/retirement as-is. Today's CashFlowScreen.tsx is working-lens only and uses calendar January-December grids — it is replaced by this screen with a lens switch.</t>
+          <t>Fully EXISTING (TransactionSheet + HistorySheet + ledger engine). Work is placement: surface both from the Invest tab and every detail page, and add COUPON/alt-sale rows to the visible history copy (types already exist in the ledger).</t>
         </is>
       </c>
       <c r="F24" s="4" t="n"/>
@@ -1288,27 +1288,27 @@
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>Invest</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cash flow main — working</t>
+          <t>Empty, stale, hidden &amp; loading states</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>both</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>For someone still working: today's real cash flow — what comes in, what goes out, what is left — plus the same truthful dated 12-month bars (bonus in its chosen month, stock vesting in its vest months, a one-time payment on its real date). Below it, a clearly labeled PROJECTION of the retirement pay</t>
+          <t>The first five seconds and the worst five seconds: brand-new users, dead prices, public places, slow networks. These states carry the trust promise as much as the happy path. — Define exactly how the Invest tab behaves when there is nothing, when data is old or missing, when amounts must be private,</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Mostly a re-arrangement of what CashFlowScreen.tsx already computes; the two real changes are (1) swapping its calendar January-December grids for the dated F2 grid, and (2) the net-new projection card via F5's projection mode.</t>
+          <t>All mechanisms EXIST; the work is a written state contract per screen + tests: (1) never $0 for a priced holding with no price, (2) never an unlabeled stale number, (3) no raw money() calls on the Invest tab (extend scripts/check-ui-tests.sh style gate), (4) empty-state renders with zero crashes in the 28-screen smoke suite.</t>
         </is>
       </c>
       <c r="F25" s="4" t="n"/>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Month detail</t>
+          <t>Cash flow main — retired</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Both (retired example shown)</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Tap any bar and see exactly why that month looks the way it does: each income item on its real date, the big dated bills that land that month, the safe draw, and the resulting safe-to-spend. The month is fully dated (November 2026, not just 'Nov'), and the rows sum — visibly — to the number on the b</t>
+          <t>The retiree's paycheck, told truthfully month by month. The big number is what is safe to spend THIS month and THIS year, split into its real parts: the guaranteed money that arrives (Social Security, pension, annuity — each named), plus a safe draw from savings, minus the big bills that land in tha</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Net-new screen, but it is a pure renderer over one F2/F5 cell — no math of its own. Cheapest correct build: pass the cell object in and forbid any recomputation in the component (mirrors the one-concept-one-helper rule).</t>
+          <t>The hero and decomposition are net-new (F5). The bars are a re-skin of cashflowYear once it is promoted to the F2 canonical grid — the rolling dated window, year-wrap labels, and month+year placement already exist in that helper. Draw-order and will-it-last reuse src/domain/decumulation and src/domain/retirement as-is. Today's CashFlowScreen.tsx is working-lens only and uses calendar January-December grids — it is replaced by this screen with a lens switch.</t>
         </is>
       </c>
       <c r="F26" s="4" t="n"/>
@@ -1351,22 +1351,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Bill calendar v2</t>
+          <t>Cash flow main — working</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Working</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>The same 12 dated months as everywhere else, viewed as a running-balance table: money in, money out, and what is left at the end of each month, starting from real cash on hand. Big bills get day-level treatment ('will the money be there two days before it is due?'). This is where dated bills are add</t>
+          <t>For someone still working: today's real cash flow — what comes in, what goes out, what is left — plus the same truthful dated 12-month bars (bonus in its chosen month, stock vesting in its vest months, a one-time payment on its real date). Below it, a clearly labeled PROJECTION of the retirement pay</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Smallest lift of the tab: BillCalendarScreen.tsx already renders cashflowYear + upcomingBills + cashTotal. Work = point it at F2 (which IS cashflowYear promoted), add the year field on one-off bills, add the deferred-debt field + payoffPlan change, and retire its student-era wording (scholarships/loan-disbursement copy stays in code paths but out of this audience's UI).</t>
+          <t>Mostly a re-arrangement of what CashFlowScreen.tsx already computes; the two real changes are (1) swapping its calendar January-December grids for the dated F2 grid, and (2) the net-new projection card via F5's projection mode.</t>
         </is>
       </c>
       <c r="F27" s="4" t="n"/>
@@ -1380,22 +1380,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Draw-order steer sheet</t>
+          <t>Month detail</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Retired (working sees it in projection mode)</t>
+          <t>Both (retired example shown)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY the suggested order is what it is, in plain wor</t>
+          <t>Tap any bar and see exactly why that month looks the way it does: each income item on its real date, the big dated bills that land that month, the safe draw, and the resulting safe-to-spend. The month is fully dated (November 2026, not just 'Nov'), and the rows sum — visibly — to the number on the b</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>The order model, the required-withdrawal pin, and every why sentence already exist in src/domain/decumulation/index.ts — this sheet is mostly UI plus two net-new pieces: a stored user draw-order preference and the F5 re-run wrapper that feeds it into the existing simulation and depletion helpers.</t>
+          <t>Net-new screen, but it is a pure renderer over one F2/F5 cell — no math of its own. Cheapest correct build: pass the cell object in and forbid any recomputation in the component (mirrors the one-concept-one-helper rule).</t>
         </is>
       </c>
       <c r="F28" s="4" t="n"/>
@@ -1404,27 +1404,27 @@
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Plan hub</t>
+          <t>Bill calendar v2</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>The chief-of-staff desk: one calm place for the will-it-last number, the big decisions waiting on you, and your saved what-ifs. — The one true home of the will-it-last number, plus the doorway to every big decision and saved scenario. Nothing here changes your plan by itself -- every path ends at an</t>
+          <t>The same 12 dated months as everywhere else, viewed as a running-balance table: money in, money out, and what is left at the end of each month, starting from real cash on hand. Big bills get day-level treatment ('will the money be there two days before it is due?'). This is where dated bills are add</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Foundation EXISTS: simulate(), the store fields, the scenarios list, and SharpenPlanScreen. NET-NEW: this hub screen itself, the selectWillItLast selector, claim-window badge, planHistory revert row. CRITICAL: today retirementAssumptions is read ONLY by RetirementCockpit + SharpenPlanScreen -- the hub replaces RetirementCockpit's 'current' screen as the committed-plan home.</t>
+          <t>Smallest lift of the tab: BillCalendarScreen.tsx already renders cashflowYear + upcomingBills + cashTotal. Work = point it at F2 (which IS cashflowYear promoted), add the year field on one-off bills, add the deferred-debt field + payoffPlan change, and retire its student-era wording (scholarships/loan-disbursement copy stays in code paths but out of this audience's UI).</t>
         </is>
       </c>
       <c r="F29" s="4" t="n"/>
@@ -1433,27 +1433,27 @@
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Social Security claim timing</t>
+          <t>Draw-order steer sheet</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>Retired (working sees it in projection mode)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>The flagship decision: 62 vs 67 vs 70 laid out in your own dollars. You set how long you expect to live; we never crown a winner. — Show what claiming at 62, 67, or 70 pays per month, what each adds up to by the age YOU set, and what each does to the same will-it-last number the hub shows. Ends in t</t>
+          <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY the suggested order is what it is, in plain wor</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Engine mostly EXISTS (simulate already accepts the claim-start age -- guaranteed_start_age in RetirementInputs). NET-NEW: this screen, the benefit-by-claim-age factor helper, window nudge, and the adoption patch. The store already has ssClaimAge/ssMonthly/ssEligible fields waiting (useStore.ts:427).</t>
+          <t>The order model, the required-withdrawal pin, and every why sentence already exist in src/domain/decumulation/index.ts — this sheet is mostly UI plus two net-new pieces: a stored user draw-order preference and the F5 re-run wrapper that feeds it into the existing simulation and depletion helpers.</t>
         </is>
       </c>
       <c r="F30" s="4" t="n"/>
@@ -1462,27 +1462,27 @@
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Cash flow</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Multi-goal trade-off composer</t>
+          <t>Your monthly income (Social Security · pension · annuity)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Can I do it all? Parents, college, the mortgage, debt, and retirement saving -- together on one screen, with the shortfall and the retirement cost in plain sight. — Toggle several goals on together, set each one's monthly amount with a slider, and see two verdicts at once: does this month's money co</t>
+          <t>THE missing front door for the retired lens: where Social Security, pension and annuity amounts are typed in — two numbers a retiree knows by heart, 20 seconds, no bank login. Reached from the Home prompt ('Add your Social Security and pension'), from first-run when the user picks 'a retirement payc</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Single-goal math, capacity, debt payoff, and the retirement solver all EXIST -- the NET-NEW work is the F4 weigher that runs them together, the trim-one sweep, and the commitments field on the shared assumptions object. There is NO multi-goal engine in the code today; this is a headline v1 build item.</t>
+          <t>NET-NEW screen over EXISTING fields — closes the walkthrough's worst finding (guaranteed-income capture was undesigned; both old signposts led to wrong screens). The empty-Home 'Add something by hand … a pension' copy is corrected to route pensions HERE (income), not to the asset form (a pot).</t>
         </is>
       </c>
       <c r="F31" s="4" t="n"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Roth conversion (simple scenario)</t>
+          <t>Plan hub</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>One dial, one honest trade: pay some tax now, in a low-tax year, so more of later life is tax-free. Estimates, clearly labeled. — The simple case only (v1): convert X dollars this year. Show the tax cost now, the two later effects (smaller required withdrawals, bigger tax-free bucket), and the will-</t>
+          <t>The chief-of-staff desk: one calm place for the will-it-last number, the big decisions waiting on you, and your saved what-ifs. — The one true home of the will-it-last number, plus the doorway to every big decision and saved scenario. Nothing here changes your plan by itself -- every path ends at an</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>rothConversion() and rmdAtAge() EXIST; today's RothScreen.tsx is a disconnected calculator (local state, zero store writes) -- v1 rewires it to real balances (taxBucketSplit) and the F11 adoption flow. Keep v1 to the single-year, single-amount case exactly as the requirement says; multi-year ladders are out of scope.</t>
+          <t>Foundation EXISTS: simulate(), the store fields, the scenarios list, and SharpenPlanScreen. NET-NEW: this hub screen itself, the selectWillItLast selector, claim-window badge, planHistory revert row. CRITICAL: today retirementAssumptions is read ONLY by RetirementCockpit + SharpenPlanScreen -- the hub replaces RetirementCockpit's 'current' screen as the committed-plan home.</t>
         </is>
       </c>
       <c r="F32" s="4" t="n"/>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Retirement transition + required withdrawals</t>
+          <t>Social Security claim timing</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>The chief-of-staff view of the government-mandated yearly withdrawal: this year's required amount, how much of it is already taken, the deadline, a year-by-year schedule (clearly labeled estimates — future amounts move with balances), and a getting-ready checklist for the run-up to 73. Logistics and</t>
+          <t>The flagship decision: 62 vs 67 vs 70 laid out in your own dollars. You set how long you expect to live; we never crown a winner. — Show what claiming at 62, 67, or 70 pays per month, what each adds up to by the age YOU set, and what each does to the same will-it-last number the hub shows. Ends in t</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Engine EXISTS (rmdAtAge, divisors, ledger, completeness); the screen, taken-so-far tagging, and year projection wiring are NET-NEW. This screen satisfies the Plan hub's 'Retirement transition + required withdrawals' row — previously referenced but undesigned (verification blocker #1).</t>
+          <t>Engine mostly EXISTS (simulate already accepts the claim-start age -- guaranteed_start_age in RetirementInputs). NET-NEW: this screen, the benefit-by-claim-age factor helper, window nudge, and the adoption patch. The store already has ssClaimAge/ssMonthly/ssEligible fields waiting (useStore.ts:427).</t>
         </is>
       </c>
       <c r="F33" s="4" t="n"/>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Use this plan (adoption sheet -- shared component)</t>
+          <t>Multi-goal trade-off composer</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>The founder's non-negotiable: before anything changes, see exactly what changes; after it changes, one tap gets you back. — One shared sheet every scenario ends in. Preview the exact old-to-new list, confirm to write to the ONE shared assumptions source, and promise (then deliver) a one-tap way back</t>
+          <t>Can I do it all? Parents, college, the mortgage, debt, and retirement saving -- together on one screen, with the shortfall and the retirement cost in plain sight. — Toggle several goals on together, set each one's monthly amount with a slider, and see two verdicts at once: does this month's money co</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>This sheet is THE v1.1 addition and is one shared component -- Social Security, multi-goal, Roth, and the cockpit's 'Use as my plan' (RetirementCockpit.tsx ~:236, which today writes silently with no preview or undo) all route through it. Retiring the silent write path is part of the definition of done.</t>
+          <t>Single-goal math, capacity, debt payoff, and the retirement solver all EXIST -- the NET-NEW work is the F4 weigher that runs them together, the trim-one sweep, and the commitments field on the shared assumptions object. There is NO multi-goal engine in the code today; this is a headline v1 build item.</t>
         </is>
       </c>
       <c r="F34" s="4" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Will-it-last detail</t>
+          <t>Roth conversion (simple scenario)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1593,16 +1593,103 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Open the hood on the one number: what it means, the honest range, what moves it, and every assumption behind it with an edit link. — The canonical number's one explanation page: plain meaning, the best-to-worst band, ranked drivers (descriptive what-ifs, not advice), and the full assumptions list wi</t>
+          <t>One dial, one honest trade: pay some tax now, in a low-tax year, so more of later life is tax-free. Estimates, clearly labeled. — The simple case only (v1): convert X dollars this year. Show the tax cost now, the two later effects (smaller required withdrawals, bigger tax-free bucket), and the will-</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Engine fully EXISTS (simulate with band, completeness, fallback derivations). NET-NEW: this screen, the sensitivity sweep, source tagging (null-field check is trivial), and routing edits through the one-row preview instead of the silent write the cockpit does today.</t>
+          <t>rothConversion() and rmdAtAge() EXIST; today's RothScreen.tsx is a disconnected calculator (local state, zero store writes) -- v1 rewires it to real balances (taxBucketSplit) and the F11 adoption flow. Keep v1 to the single-year, single-amount case exactly as the requirement says; multi-year ladders are out of scope.</t>
         </is>
       </c>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Retirement transition + required withdrawals</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>The chief-of-staff view of the government-mandated yearly withdrawal: this year's required amount, how much of it is already taken, the deadline, a year-by-year schedule (clearly labeled estimates — future amounts move with balances), and a getting-ready checklist for the run-up to 73. Logistics and</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Engine EXISTS (rmdAtAge, divisors, ledger, completeness); the screen, taken-so-far tagging, and year projection wiring are NET-NEW. This screen satisfies the Plan hub's 'Retirement transition + required withdrawals' row — previously referenced but undesigned (verification blocker #1).</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Use this plan (adoption sheet -- shared component)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>The founder's non-negotiable: before anything changes, see exactly what changes; after it changes, one tap gets you back. — One shared sheet every scenario ends in. Preview the exact old-to-new list, confirm to write to the ONE shared assumptions source, and promise (then deliver) a one-tap way back</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>This sheet is THE v1.1 addition and is one shared component -- Social Security, multi-goal, Roth, and the cockpit's 'Use as my plan' (RetirementCockpit.tsx ~:236, which today writes silently with no preview or undo) all route through it. Retiring the silent write path is part of the definition of done.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Will-it-last detail</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Open the hood on the one number: what it means, the honest range, what moves it, and every assumption behind it with an edit link. — The canonical number's one explanation page: plain meaning, the best-to-worst band, ranked drivers (descriptive what-ifs, not advice), and the full assumptions list wi</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Engine fully EXISTS (simulate with band, completeness, fallback derivations). NET-NEW: this screen, the sensitivity sweep, source tagging (null-field check is trivial), and routing edits through the one-row preview instead of the silent write the cockpit does today.</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1615,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1728,7 +1815,7 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Tap hero card → Invest tab. Tap net worth line → Net worth tab. Tap an attention item → its route (Insight.route). Tap will-it-last strip → Plan tab. Tap eye → mask/unmask everywhere. Tap gear → Settings. Pull down to refresh → re-pull connected balances + prices, then 'Updated just now' stamp. Long-press an attention item → quiet sheet: 'Snooze 30 days / Not useful' (feeds ranking, never deletes the underlying fact).</t>
+Tap hero card → Invest tab. Tap net worth line → Net worth tab. Tap an attention item → its DESIGNED detail (idle cash → Idle-cash detail; 401(k) room → 401(k)-room detail; concentration → the named holding on Invest) — a nudge never drops the user on a tab with no matching content. Tap will-it-last strip → Plan tab. Tap eye → mask/unmask everywhere. Tap gear → Settings. Pull down to refresh → re-pull connected balances + prices, then 'Updated just now' stamp. Long-press an attention item → quiet sheet: 'Snooze 30 days / Not useful' (feeds ranking, never deletes the underlying fact). Tapping the hero's month figure pre-selects the 1-month period on Invest so the first number seen matches the one just tapped.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2153,7 +2240,7 @@
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
     </row>
-    <row r="21" ht="350" customHeight="1">
+    <row r="21" ht="375" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
@@ -2171,13 +2258,15 @@
 |   |  Social Security+pension |
 |   └ Safe draw     $1,640     |
 |      from your savings       |
-|   This year     ~$70,100     |
+|   − Big bills this month  $0 |
+|      (shows only when due)   |
+|   This year     ~$71,600     |
 |   varies month to month      |
 | [ See July's paycheck    &gt; ] |
 |                              |
 | WHAT NEEDS YOU (2)           |
 | 1◆ Worth a look: $2,400      |
-|    left checking Tue  See &gt;  |
+|    went out of checking  See &gt;  |
 | 2· Required withdrawal of    |
 |    $12,300 due by Dec 31     |
 |                      Plan &gt;  |
@@ -2206,7 +2295,7 @@
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
-Hero reads as one sentence: 'Safe to spend in July: 5,840 dollars, an estimate. 4,200 guaranteed from Social Security and pension, 1,640 safe to draw from savings. About 70,100 dollars this year.' Worth-a-look card announces 'Worth a look' first, then the fact — screen-reader tone matches visual calm. Larger default type for this lens (retiree eyes); all targets ≥44pt; breakdown uses tree lines PLUS the words Guaranteed/Safe draw, never indentation alone.</t>
+Hero reads as one sentence: 'Safe to spend in July: 5,840 dollars, an estimate. 4,200 guaranteed from Social Security and pension, 1,640 safe to draw from savings. About 71,600 dollars this year.' Worth-a-look card announces 'Worth a look' first, then the fact — screen-reader tone matches visual calm. Larger default type for this lens (retiree eyes); all targets ≥44pt; breakdown uses tree lines PLUS the words Guaranteed/Safe draw, never indentation alone.</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2376,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Guaranteed + safe draw must sum to the this-month figure to the dollar, on Home AND on Cash flow (agreement test)</t>
+          <t>PIN: guaranteed + safe draw − big bills landing this month = the this-month figure to the dollar, on Home AND Cash flow (agreement test). The bills line appears on Home whenever it is non-zero — the card must visibly sum in every month.</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2388,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>'This year ~$70,100 — varies month to month': the 12 real months added up, with the tilde and caption making clear months differ (a big pension payment in March, property tax in November).</t>
+          <t>'This year ~$71,600 — varies month to month': the 12 real months added up, with the tilde and caption making clear months differ (a big pension payment in March, property tax in November).</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2380,7 +2469,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Calm single line: '◆ Worth a look: $2,400 left checking Tue — See &gt;'. Magnifying-glass icon + the words 'Worth a look' (never a red badge, never the words fraud/alert). States the fact; the person decides.</t>
+          <t>Calm single line: '◆ Worth a look: $2,400 went out of checking, Tue — See &gt;'. Magnifying-glass icon + the words 'Worth a look' (never a red badge, never the words fraud/alert). States the fact; the person decides.</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2453,50 +2542,78 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="84" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Safe-draw explainer (the 'says who?' dot)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>A small (i) beside 'Safe draw' on Home and Cash flow opens the same plain sheet: 'What makes $1,640 safe? It is the largest steady monthly draw that keeps your will-it-last odds at Likely (80 or better), re-checked whenever your balances move. Spend more each month and the odds fall — try it in Plan.'</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW shared explainer sheet; content = the F5 derivation (engine spec) said once, plainly; the try-it link opens the Plan scenario with spending pre-nudged.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>none (explainer)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>One sheet, identical wording on Home and Cash flow — the single biggest number in the retired lens is never un-sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="98" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>• Loading: Placeholder bars; the month name still renders immediately ('SAFE TO SPEND — JULY') so the frame feels steady.
 • Guaranteed income not yet captured: Hero shows only what it can stand behind: 'Safe draw $1,640' plus a quiet line 'Add your Social Security and pension in Plan to see your full paycheck &gt; Plan'. Never assumes $0 guaranteed silently (the B-31 lesson).
-• A big bill lands this month: This-month figure is honestly lower; a caption explains in one line: 'Lower this month: property tax $2,900 due Nov 15'. Never smoothed away.
+• A big bill lands this month: This-month figure is honestly lower; a caption explains in one line: 'Lower this month: property tax $1,900 due Nov 15'. Never smoothed away.
 • Refresh failed: Same as working lens: keep last numbers, calm 'showing your numbers from Jun 30' line, Try again.
-• Balances hidden: $5,840 / $4,200 / $1,640 / ~$70,100 all become ••••; the month name, words, and 84% stay.
-• Age 73+ with withdrawal not yet taken: Required-withdrawal item stays pinned in What-needs-you until marked done in Plan; wording stays factual ('$12,300 due by Dec 31'), never urgent-red.</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-    </row>
-    <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+• Balances hidden: $5,840 / $4,200 / $1,640 / ~$71,600 all become ••••; the month name, words, and 84% stay.
+• Age 73+ with withdrawal not yet taken: Required-withdrawal item stays pinned in What-needs-you until marked done in Plan; wording stays factual ('$12,300 due by Dec 31'), never urgent-red.
+• Plan questions not yet answered: The hero shows ONLY the guaranteed income actually captured plus 'Answer 3 quick questions in Plan to see your safe draw' — the safe draw is NEVER computed from defaults the user didn't give. No un-sourced number, ever (June's first morning is designed, not accidental).</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>▶ Worth a look — transaction detail (F10)  ·  lens: both</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>The calm close-up of a flagged transaction: the plain facts, why it stood out (in one honest comparison), and a two-button resolution. Reassures more than it warns — most flags are the person's own spending. Never alarmist, never the words fraud or alert in v1 copy.</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="362.5" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="362.5" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Back        Worth a look   |
@@ -2529,167 +2646,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Entire screen NET-NEW, plus the F10 engine and two new persisted fields (flag record, known-payee list). Reuses Transaction data as-is — no schema change to existing fields. This is the thin v1: one rule set, one card, one detail view; no machine learning, no merchant databases.</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Back → Home, card still present if unresolved. Tap 'Yes, this was me' → single confirmation haptic, return to Home, quiet 'Noted.' toast. Tap 'Something's off' → checklist expands in place (no new screen jump for a worried user). Tap the account line → that account in Net worth. No swipe-to-dismiss — resolution is always an explicit choice.</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Title announces 'Worth a look' (calm phrasing is itself the accessibility choice). Fact block is one sentence for screen readers. Both buttons ≥48pt tall, full width, labeled exactly as their visible text. The comparison never relies on color; the magnifier icon always carries the text label. Checklist items are numbered words, not icons.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="46" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Fact block (amount, account, date, payee)</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>'$2,400 left your Chase checking on Tue, Jun 30. Paid to: APEX SOLUTIONS.' Pure facts from the transaction record — nothing inferred.</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING record: Transaction (src/domain/transactions/index.ts) fields; account name via resolveNetWorthRows rows</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Transaction.amount, date, account_id, note (payee text), type</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Must match the Home card and the same row in the Cash flow activity list to the penny and the day</t>
-        </is>
-      </c>
-    </row>
     <row r="36" ht="46" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Why we're showing this</t>
+          <t xml:space="preserve">   Fact block (amount, account, date, payee)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>One plain-English comparison per reason: unusually large → 'Your usual withdrawal from this account is about $310. This one is 8 times that.' First-time payee → 'First time we've seen this payee on this account.' Odd pattern → 'Three withdrawals from this account today, $3,100 together.' Always followed by the softener: 'Most large first-time payments are fine — you know best.'</t>
+          <t>'$2,400 left your Chase checking on Tue, Jun 30. Paid to: APEX SOLUTIONS.' Pure facts from the transaction record — nothing inferred.</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F10 flag engine output {reason, comparison} (proposed src/domain/transactions/flags.ts)</t>
+          <t>EXISTING record: Transaction (src/domain/transactions/index.ts) fields; account name via resolveNetWorthRows rows</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>flag.reason, flag.comparison (the typical-amount figure used), the 90-day history it was computed from</t>
+          <t>Transaction.amount, date, account_id, note (payee text), type</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>The 'usual amount' shown here is the exact figure the rule used — stored on the flag at flag time, so the explanation never drifts from the decision</t>
+          <t>Must match the Home card and the same row in the Cash flow activity list to the penny and the day</t>
         </is>
       </c>
     </row>
     <row r="37" ht="46" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Button — Yes, this was me</t>
+          <t xml:space="preserve">   Why we're showing this</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Primary, friendly. One tap: card leaves Home, flag saved as resolved-by-me, and for a first-time-payee flag the payee is remembered as known (so it never asks about them again).</t>
+          <t>One plain-English comparison per reason: unusually large → 'Your usual withdrawal from this account is about $310. This one is 8 times that.' First-time payee → 'First time we've seen this payee on this account.' Odd pattern → 'Three withdrawals from this account today, $3,100 together.' Always followed by the softener: 'Most large first-time payments are fine — you know best.'</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F10 resolve action (flag.status → 'was_me', known-payee list append)</t>
+          <t>NET-NEW: F10 flag engine output {reason, comparison} (proposed src/domain/transactions/flags.ts)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>flag.status, resolved_at, known_payees per account</t>
+          <t>flag.reason, flag.comparison (the typical-amount figure used), the 90-day history it was computed from</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Resolved flags never reappear on Home; they remain visible in the transaction's row detail</t>
+          <t>The 'usual amount' shown here is the exact figure the rule used — stored on the flag at flag time, so the explanation never drifts from the decision</t>
         </is>
       </c>
     </row>
     <row r="38" ht="46" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Button — Something's off, show me what to do</t>
+          <t xml:space="preserve">   Button — Yes, this was me</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Second button. Opens a short factual checklist (no commands, just the map): 1) Your bank's fraud line is on the back of your card — they can freeze the card and reverse charges; 2) If you shared a code or password recently, change it; 3) You can note what happened here for your records. Card moves to a quiet 'Flagged by you' section until you mark it settled.</t>
+          <t>Primary, friendly. One tap: card leaves Home, flag saved as resolved-by-me, and for a first-time-payee flag the payee is remembered as known (so it never asks about them again).</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F10 resolve action (flag.status → 'flagged') + static checklist view</t>
+          <t>NET-NEW: F10 resolve action (flag.status → 'was_me', known-payee list append)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>flag.status, user note</t>
+          <t>flag.status, resolved_at, known_payees per account</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>A flagged item stays counted in What-needs-you (as 'You flagged $2,400 — settled?') until closed, on both lenses</t>
+          <t>Resolved flags never reappear on Home; they remain visible in the transaction's row detail</t>
         </is>
       </c>
     </row>
     <row r="39" ht="46" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Button — Something's off, show me what to do</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Second button. Opens a short factual checklist (no commands, just the map): 1) Call the number on the back of your bank card — they can freeze the card and reverse charges; 2) If you shared a code or password recently, change it; 3) You can note what happened here for your records. Card moves to a quiet 'Flagged by you' section until you mark it settled.</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F10 resolve action (flag.status → 'flagged') + static checklist view</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>flag.status, user note</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>A flagged item stays counted in What-needs-you (as 'You flagged $2,400 — settled?') until closed, on both lenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="46" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Reassurance footer</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>'We can only look at your accounts — we can never move or block money. Your bank can.' Anchors the read-only promise at the exact moment of worry.</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>static copy (mirrors the F1 read-only connection promise)</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Same read-only wording as the connect-account screen</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="70" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41" ht="70" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>• Open (unresolved): As drawn. Card also visible on Home slot 1 until resolved.
 • Resolved — was me: Buttons replaced by 'You confirmed this on Jul 1 ✓ confirmed' (word + check). Reachable from the transaction row forever; gone from Home.
@@ -2698,34 +2815,34 @@
 • Multiple open flags: Home shows only the most recent card with 'and 1 more'; detail view gets previous/next arrows. More than 2 open flags in 30 days automatically loosens nothing — thresholds never auto-tighten in v1.</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-    </row>
-    <row r="42" ht="46" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+    </row>
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>▶ First run — what did you come for? (sets the lens)  ·  lens: both</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>The progressive first-run from the approved high-level design: two friendly questions — what you came for, and whether you're still working — set the lens (which hero leads Home) and the tab order. Skippable with no dead end; everything is changeable later.</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-    </row>
-    <row r="43" ht="262.5" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="262.5" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Welcome to FinWise           |
@@ -2750,146 +2867,146 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 NET-NEW light screen; closes the gap that the lens resolver read a stage no designed screen captured (verification finding #10). The connect flow itself is on the Net worth tab (already designed).</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Pick + Continue -&gt; first-run Home with suggestions ordered by intent. Skip -&gt; first-run Home with defaults. Settings -&gt; reopen anytime.</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+Pick + Continue -&gt; first-run Home; 'retirement paycheck' + retired leads with the Monthly-income fast-path door (enter Social Security + pension first, connect later or never). Skip -&gt; first-run Home with defaults. Settings -&gt; reopen anytime.</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Radio groups with full labels; the consequence sentence ('this sets up your Home and tab order') is read before the choices. Large targets; no time pressure.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="46" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   What-did-you-come-for pick</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Three plain intents. It orders the first suggestions (which account to connect first, which tab to tour) — it never locks anything.</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: intent field on the onboarding profile (src/domain/profile/onboarding.ts); consumed by the first-run Home's suggestion order.</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>intent ('grow' | 'paycheck' | 'whole_picture')</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Intent only orders suggestions; it never changes any number anywhere.</t>
-        </is>
-      </c>
-    </row>
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stage question (still working / retired)</t>
+          <t xml:space="preserve">   What-did-you-come-for pick</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>The one answer that flexes the whole app: working -&gt; Grow &amp; Track hero + working tab order; retired -&gt; Safe-to-spend hero + retired tab order.</t>
+          <t>Three plain intents. It orders the first suggestions (which account to connect first, which tab to tour) — it never locks anything.</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>EXISTING profile: stage derived from onboarding (src/domain/profile/onboarding.ts) — this screen is the designed capture point the lens resolver reads (Home lens resolver element).</t>
+          <t>NET-NEW: intent field on the onboarding profile (src/domain/profile/onboarding.ts); consumed by the first-run Home's suggestion order.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>stage ('working' | 'retired')</t>
+          <t>intent ('grow' | 'paycheck' | 'whole_picture')</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>PIN: the lens set here = the tab order and hero on every later screen — one stage field, read by the one lens resolver.</t>
+          <t>Intent only orders suggestions; it never changes any number anywhere.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Stage question (still working / retired)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>The one answer that flexes the whole app: working -&gt; Grow &amp; Track hero + working tab order; retired -&gt; Safe-to-spend hero + retired tab order.</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING profile: stage derived from onboarding (src/domain/profile/onboarding.ts) — this screen is the designed capture point the lens resolver reads (Home lens resolver element).</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>stage ('working' | 'retired')</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the lens set here = the tab order and hero on every later screen — one stage field, read by the one lens resolver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Skip — just explore</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Skips both questions: defaults to the whole-picture intent + working lens, Home opens in its honest empty state. No dead end, no nagging.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Defaults in the lens resolver; first-run Home (already designed) handles the empty state.</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>defaults</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Skipping never produces different numbers — only default ordering.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>• First launch: Shown once before the first-run Home; both questions optional.
 • Revisited from Settings: Same screen, titled 'Your setup'; changing the stage re-orders tabs immediately with a one-line confirmation.</t>
         </is>
       </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-    </row>
-    <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>▶ Home — first run (nothing connected yet)  ·  lens: both</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>The empty Home never shows fake zeros or demo charts — it makes one promise (your real numbers, read-only) and offers exactly two doors in: connect an institution, or add something by hand. Shows what Home will become so the effort has a visible payoff.</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-    </row>
-    <row r="50" ht="362.5" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+    </row>
+    <row r="51" ht="362.5" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Welcome, Pat        (eye)[=] |
@@ -2906,8 +3023,8 @@
 |   never touch your money.    |
 |                              |
 | [ Add something by hand  &gt; ] |
-|   Your home, a pension, or   |
-|   an account with no login   |
+|   Your home, or an account   |
+|   with no login              |
 |                              |
 |  WHAT YOU'LL SEE HERE        |
 |  · Your whole picture in     |
@@ -2922,140 +3039,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Layout NET-NEW (simple). Connect button blocks on the F1 seam (net-new, the PRD's top build item); add-by-hand REUSES the existing manual flow, so this screen can ship with by-hand only if F1 lands later — the connect button then reads 'Coming soon' honestly rather than hiding.</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Tap connect → institution picker (F1 flow). Tap add-by-hand → existing manual add. Tabs remain tappable — each shows its own empty state rather than trapping the user on Home. Pull-to-refresh disabled (nothing to refresh).</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Both doors are full-width ≥48pt buttons announced with their sub-lines ('Connect your first account, takes about 2 minutes, read-only'). Illustration marked decorative (skipped by screen readers). Preview list is a proper list for rotor navigation.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Connect your first account (button)</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Primary button into the account-linking flow (banks, brokerages, retirement accounts, credit cards, loans). Sub-line carries the two trust facts: about 2 minutes, and read-only.</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F1 secure read-only account-sync seam (provider module + Connection record — PRD gap: no aggregator module exists in the repo today)</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>creates Connection {institution, status, last_successful_update} + AssetAccount rows on success</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>The read-only promise wording here = the worth-a-look footer = Settings connections screen</t>
-        </is>
-      </c>
-    </row>
     <row r="52" ht="46" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Add something by hand (button)</t>
+          <t xml:space="preserve">   Connect your first account (button)</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>For things with no login: home value, a pension, a private holding. Opens the existing add flow.</t>
+          <t>Primary button into the account-linking flow (banks, brokerages, retirement accounts, credit cards, loans). Sub-line carries the two trust facts: about 2 minutes, and read-only.</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: manual add-account flow (Net worth tab; account kinds from ASSET_KINDS in src/domain/assets/index.ts)</t>
+          <t>NET-NEW: F1 secure read-only account-sync seam (provider module + Connection record — PRD gap: no aggregator module exists in the repo today)</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>AssetAccount kind, balance, label</t>
+          <t>creates Connection {institution, status, last_successful_update} + AssetAccount rows on success</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Manually added rows appear identically on Net worth and inside totals everywhere</t>
+          <t>The read-only promise wording here = the worth-a-look footer = Settings connections screen</t>
         </is>
       </c>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   What you'll see here (preview list)</t>
+          <t xml:space="preserve">   Add something by hand (button)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Three plain lines previewing the real Home: whole picture, what needs you in dollars, honest odds. Words only — no fake example numbers that could be mistaken for data.</t>
+          <t>For things with no login: home value, a private holding, a certificate of deposit. Opens the existing add flow. A PENSION is income, not a pot — the word is deliberately NOT offered here; pensions and Social Security are entered on the Monthly-income screen (the retired fast-path door leads there), so nobody is asked what their pension is 'worth'.</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>static copy</t>
+          <t>EXISTING: manual add-account flow (Net worth tab; account kinds from ASSET_KINDS in src/domain/assets/index.ts)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>AssetAccount kind, balance, label</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>The three promises correspond one-to-one to the three real Home blocks (hero, What-needs-you, will-it-last)</t>
+          <t>Manually added rows appear identically on Net worth and inside totals everywhere</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   What you'll see here (preview list)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Three plain lines previewing the real Home: whole picture, what needs you in dollars, honest odds. Words only — no fake example numbers that could be mistaken for data.</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>static copy</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>The three promises correspond one-to-one to the three real Home blocks (hero, What-needs-you, will-it-last)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Greeting / header</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>'Welcome, Pat' if a name exists from sign-up, else 'Welcome'. Eye and gear present but eye is inert (nothing to hide) — kept so the header never rearranges later.</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>EXISTING: name resolution in src/screens/HomeScreen.tsx</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>store.user.name</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Header layout identical to populated Home</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="56" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Retired-intent income fast-path</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>If first-run answers were 'a retirement paycheck I can trust' + retired, the empty Home leads with a THIRD door above the other two: 'Get your paycheck — enter your Social Security and pension (2 minutes, no bank login)' → the Monthly-income screen. Two typed numbers give her a real hero before any connect decision.</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>intent + stage from the first-run screen; navigation to the Monthly-income screen (Cash flow tab).</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>intent, stage</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>The amounts land in the same ri_* fields the hero reads — instant, honest payoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="56" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>• Zero data (as drawn): No hero, no zeros, no placeholder charts. Tabs other than Home show their own honest empty states.
 • Connecting (in progress): Button becomes 'Connecting to Chase…' with progress words ('Fetching your accounts — usually under a minute'). Cancel available. On success, Home rebuilds live with a one-time 'Here's your picture ✓' moment.
@@ -3063,34 +3207,34 @@
 • First data arrived (1 account): Switches to the partial-data Home: real hero from what exists + a single quiet card 'Add the rest for your full picture' listing what's missing by name (e.g. 'no retirement account yet').</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-    </row>
-    <row r="57" ht="46" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+    </row>
+    <row r="59" ht="46" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>▶ Home — balances hidden (mask everything)  ·  lens: both</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Coffee-shop mode: one tap makes every money amount unreadable over a shoulder while the page stays fully useful — direction words, percentages, and the will-it-last chance remain. Same rule on the retired lens: all four paycheck dollars mask, month name and words stay.</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="7" t="n"/>
-    </row>
-    <row r="58" ht="362.5" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+    </row>
+    <row r="60" ht="362.5" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Good morning, Pat (eye-off)  |
@@ -3123,147 +3267,147 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Pure REUSE: mechanism shipped (mask-ALL fixed in the build-33 round). Home rebuild work = discipline + a test: every new Home component must format money through useMoney(); add a UI test that walks Home with hideBalances on and asserts zero '$' characters render.</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Tap eye anywhere → toggle globally. Everything else behaves exactly as the unmasked screen — navigation is never disabled by hiding.</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Masked values announce as 'hidden' (not 'bullet bullet bullet'). Eye announces 'Show balances' when hidden — labels already exist in src/components/TopBar.tsx. The banner is polite-priority for screen readers (announced once, not repeated per element).</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="46" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Mask rule</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>EVERY dollar figure app-wide renders as •••• (hero, breakdowns, attention items, net worth, detail views — including the worth-a-look amounts). Percentages, ratios in words ('8 times your usual'), dates, and the will-it-last chance stay: they are readings, not balances.</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: useMoney().m / .compact returning BALANCE_MASK when hideBalances is on (src/components/useMoney.ts); flag in src/store/useStore.ts</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>hideBalances</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>One flag, no exceptions — a build gate audits that no Home component calls the raw money() formatter for a balance (this was the mask-ALL fix from the build-33 device test)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="46" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Hidden banner</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>One-line reminder under the header: 'Balances hidden — tap the eye to show'. Present on every tab while hidden.</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING pattern: TopBar eye + accessibility labels (src/components/TopBar.tsx)</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>hideBalances</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Same line, same position on all five tabs</t>
-        </is>
-      </c>
-    </row>
     <row r="61" ht="46" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Mask rule</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>EVERY dollar figure app-wide renders as •••• (hero, breakdowns, attention items, net worth, detail views — including the worth-a-look amounts). Percentages, ratios in words ('8 times your usual'), dates, and the will-it-last chance stay: they are readings, not balances.</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: useMoney().m / .compact returning BALANCE_MASK when hideBalances is on (src/components/useMoney.ts); flag in src/store/useStore.ts</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>hideBalances</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>One flag, no exceptions — a build gate audits that no Home component calls the raw money() formatter for a balance (this was the mask-ALL fix from the build-33 device test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="46" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Hidden banner</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>One-line reminder under the header: 'Balances hidden — tap the eye to show'. Present on every tab while hidden.</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING pattern: TopBar eye + accessibility labels (src/components/TopBar.tsx)</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>hideBalances</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Same line, same position on all five tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="46" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Eye (off) toggle</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Eye-with-slash icon; tapping restores instantly. No confirmation, no animation delay.</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>EXISTING: toggleHideBalances (src/store/useStore.ts)</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>hideBalances</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>State persists across app restarts and both lenses</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>• Hidden + pull-to-refresh: Refresh works normally; new numbers arrive already masked — no flash of real figures.
-• Hidden + worth-a-look card: Card shows '•••• left checking Tue'; detail view masks both dollars but keeps the words-based comparison, so a flag can still be triaged privately.
+• Hidden + worth-a-look card: Card shows '•••• went out of checking, Tue'; detail view masks both dollars but keeps the words-based comparison, so a flag can still be triaged privately.
 • Reveal: Instant, all screens at once. No per-figure peek in v1 (one rule is easier to trust).</t>
         </is>
       </c>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-    </row>
-    <row r="64" ht="46" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+    </row>
+    <row r="66" ht="46" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>▶ Home — stale connection + partial data  ·  lens: both</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Honesty when the pipes are imperfect: an old connection gets a calm, specific banner (which institution, since when, one fix button); every number touched by old data carries an 'as of' stamp; and anything we can't stand behind becomes an invitation, never a guess. Show what's true first.</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-    </row>
-    <row r="65" ht="362.5" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+    </row>
+    <row r="67" ht="362.5" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Good morning, Pat   (eye)[=] |
@@ -3296,140 +3440,140 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Banner + balance staleness are NET-NEW and blocked on the F1 Connection entity; price stamps REUSE priceFreshness today (can ship first). The partial-data behaviors are mostly free — the insights engine already skips null inputs; the work is the will-it-last invitation state and the stamp explainer sheet.</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Tap Fix connection → institution re-link (F1). Tap an as-of stamp → one-sentence explainer sheet: 'This includes your Chase accounts, last updated Jun 27. Everything else is current.' Tap the invitation strip → Plan's 3 questions. Pull-to-refresh retries the stale connection first.</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Banner is announced once on arrival ('Information: Chase hasn't updated since June 27'), not on every scroll. Stamps are part of each number's spoken sentence ('…as of June 27'). Info icon always paired with words. Fix button ≥44pt.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="46" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Stale-connection banner</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>'ⓘ Chase hasn't updated since Jun 27. Numbers may be behind. [Fix connection &gt;]'. Info icon + words (never a yellow bar alone). Names the institution and date; appears when a connection is more than 48 hours old or needs a fresh login. Manual-only users never see it.</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F1 Connection record's last_successful_update + status (no sync module exists yet — PRD gap)</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Connection.institution, last_successful_update, status</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Same connection status and date as the Settings connections list; one source</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="46" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   As-of stamps on affected numbers</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Any figure that includes stale data gets 'as of Jun 27' next to it; hero also says which part ('Chase part'). Price-driven staleness uses the existing freshness read.</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING for prices: priceFreshness (src/services/marketData.ts); NET-NEW for account balances: oldest last_successful_update among included connections</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>price fetch timestamps; Connection.last_successful_update per included account</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Same stamp logic and wording as the Performance screen's freshness line — one helper, both places</t>
-        </is>
-      </c>
-    </row>
     <row r="68" ht="46" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Partial will-it-last invitation</t>
+          <t xml:space="preserve">   Stale-connection banner</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>When the plan inputs aren't answered yet, the strip becomes: 'Answer 3 quick questions in Plan to see your odds &gt; Plan'. Never shows a chance computed from guessed inputs.</t>
+          <t>'ⓘ Chase hasn't updated since Jun 27. Numbers may be behind. [Fix connection &gt;]'. Info icon + words (never a yellow bar alone). Names the institution and date; appears when a connection is more than 48 hours old or needs a fresh login. Manual-only users never see it.</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>EXISTING gate: absence of a stored RetirementState (buildRetirementState output, src/domain/retirement/index.ts)</t>
+          <t>NET-NEW: F1 Connection record's last_successful_update + status (no sync module exists yet — PRD gap)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>presence/absence of RetirementState; plan completeness (planPct input in src/domain/insights/index.ts)</t>
+          <t>Connection.institution, last_successful_update, status</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Plan tab shows the same 3 questions; completing them lights up Home and the insights retireChance simultaneously</t>
+          <t>Same connection status and date as the Settings connections list; one source</t>
         </is>
       </c>
     </row>
     <row r="69" ht="46" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   As-of stamps on affected numbers</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Any figure that includes stale data gets 'as of Jun 27' next to it; hero also says which part ('Chase part'). Price-driven staleness uses the existing freshness read.</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING for prices: priceFreshness (src/services/marketData.ts); NET-NEW for account balances: oldest last_successful_update among included connections</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>price fetch timestamps; Connection.last_successful_update per included account</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Same stamp logic and wording as the Performance screen's freshness line — one helper, both places</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="46" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Partial will-it-last invitation</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>When the plan inputs aren't answered yet, the strip becomes: 'Answer 3 quick questions in Plan to see your odds &gt; Plan'. Never shows a chance computed from guessed inputs.</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING gate: absence of a stored RetirementState (buildRetirementState output, src/domain/retirement/index.ts)</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>presence/absence of RetirementState; plan completeness (planPct input in src/domain/insights/index.ts)</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Plan tab shows the same 3 questions; completing them lights up Home and the insights retireChance simultaneously</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="46" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Shorter What-needs-you</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Only rules whose inputs are trustworthy fire; a list of 1 is shown as 1. A missing-data nudge may appear as a normal ranked item ('Add your retirement account — your picture is missing it') but is never dressed as urgent.</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>EXISTING: buildInsights simply receives null/absent inputs and its rules skip (nullable InsightInput fields, src/domain/insights/index.ts)</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>InsightInput with nulls for unknowns</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Insights screen shows the same reduced set</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="56" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72" ht="56" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>• One stale connection (as drawn): Banner + stamps; everything else live. Fix button opens the re-link flow for that institution only.
 • All connections stale / offline: Banner generalizes: 'We couldn't reach your banks — showing everything as of Jun 27.' Single date, single stamp at top instead of per-number clutter.
@@ -3437,9 +3581,287 @@
 • Stale + hidden balances: Both rules stack: •••• with 'as of Jun 27' stamps; the banner still names the institution.</t>
         </is>
       </c>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+    </row>
+    <row r="74" ht="46" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>▶ Idle cash — nudge detail  ·  lens: both</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>The designed landing for Home's idle-cash nudge (previously a dead-end): the fact, which accounts it sits in, and the plain comparison math of what that cash could earn — estimates, named rates, no instruction to act.</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
+      <c r="G74" s="7" t="n"/>
+    </row>
+    <row r="75" ht="287.5" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>WIREFRAME</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>+------------------------------+
+| &lt; Back    Your idle cash     |
+|                              |
+| $18,400 of your cash is      |
+| earning about $0.            |
+|                              |
+| Where it sits                |
+|  Chase checking   $12,400    |
+|   earning ~0.0%              |
+|  Chase savings     $6,000    |
+|   earning ~0.1%              |
+|                              |
+| For comparison (estimates)   |
+|  In high-yield savings       |
+|   (~4.1%): ~$750/yr          |
+|  In a money-market fund      |
+|   (~4.4%): ~$810/yr          |
+|  Rates are examples — banks  |
+|  differ. We never move your  |
+|  money; you decide.          |
+|                              |
+| [ See my cash accounts &gt; ]   |
++------------------------------+</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>BUILD NOTE:
+NET-NEW light screen; closes walkthrough dead-end #1 (Home's marquee nudge led to an Invest tab with no cash section).</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>INTERACTIONS:
+Home idle-cash card -&gt; HERE (was a drop onto the Invest tab). 'See my cash accounts' -&gt; Net worth filtered to cash.</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSIBILITY:
+Read as one story: fact, where, comparison. Rates always paired with the word estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="46" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Idle-cash fact + by-account list</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>The same $18,400 as the Home card, broken into the accounts it sits in with their (user-entered or known) rates.</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: cashTotal + cash-class accounts (src/domain/assets/index.ts); per-account rate = user-entered or kind default.</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>cash-class balances, rates</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>PIN: total = the Home card figure = the Net worth Cash row — one cashTotal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="46" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Comparison math (estimates)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>What the same dollars would earn at typical high-yield-savings and money-market rates — '$750/yr' style, labeled estimates with example rates shown.</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW small calc: balance × example rate; rates are named constants with an as-of date, never a recommendation of a product.</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>cash total × example rates</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Comparison uses the same total shown above it; never advises, shows math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   STATES</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>• Rates unknown: Accounts without a rate show 'rate not set [add]' — the comparison still runs on the total.
+• Hidden balances: Amounts mask; percentages stay.</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
+    </row>
+    <row r="80" ht="46" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>▶ 401(k) room this year — nudge detail  ·  lens: working</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>The designed landing for Home's 401(k)-room nudge (previously pointing at a legacy screen): the limit, what's in, what's left, the per-month translation, and the honest 'change it at your employer' line. Links to the forward what-if to see the effect of using the room.</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="7" t="n"/>
+    </row>
+    <row r="81" ht="287.5" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>WIREFRAME</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>+------------------------------+
+| &lt; Back   401(k) room         |
+|                              |
+| $9,200 of room left in your  |
+| workplace retirement account |
+| this year.                   |
+|                              |
+| The yearly limit   $31,000   |
+|  (age 50+ catch-up incl.)    |
+| You have put in    $21,800   |
+| Room left           $9,200   |
+| Months left to use it    6   |
+|  = about $1,530/mo           |
+|                              |
+| Money in a 401(k) grows      |
+| without tax until you take   |
+| it out. Changing what you    |
+| put in happens AT YOUR       |
+| EMPLOYER — we just show      |
+| the math.                    |
+|                              |
+| [ Try it in a what-if &gt; ]    |
++------------------------------+</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>BUILD NOTE:
+NET-NEW light screen aligned with the live app's contribution-room surface; closes walkthrough dead-end #2.</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>INTERACTIONS:
+Home 401(k) card -&gt; HERE. Try-it -&gt; forward what-if prefilled.</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSIBILITY:
+The four math rows read as one sentence; catch-up rule stated in words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="46" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Room math</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Limit (with age-50+ catch-up), contributed so far, room left, and room ÷ months remaining.</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: k401Headroom(age, contributions) + IRS_LIMITS (src/domain/income/limits.ts) — the same helper the Home card uses.</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>age, year-to-date 401(k) contributions, IRS limit table</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the room figure = the Home card figure — one helper (k401Headroom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="46" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Try-it link</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>'Try it in a what-if' opens Invest's forward what-if pre-set to +$1,530/mo.</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Navigation with prefill into the designed forward what-if screen.</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>prefill addMonthly</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Same engines as the what-if; no separate math here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   STATES</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>• No earned income: The nudge never fires (existing B-48 gate), so this screen is unreachable — stated for completeness.
+• Hidden balances: Dollar figures mask.</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3452,7 +3874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3572,7 +3994,7 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Tap a class row → jump to those accounts (existing scrollToClass). Tap 'Show accounts &amp; detail' → expand/collapse; toggle By class / By institution. Tap an account row → Account detail (screen 5). Tap the cash-flow glance → Cash flow tab. Tap [+] → chooser (Link / Add by hand / Import). Pull to refresh → sync connected accounts + refresh prices. Tap the eye → hide/show balances.</t>
+Tap a class row → jump to those accounts (existing scrollToClass). Tap 'Show accounts &amp; detail' → expand/collapse; toggle By class / By institution. Tap an account row → Account detail (screen 5). Tap the cash-flow glance → Cash flow tab. Tap [+] → chooser (Link / Add by hand / Import). Pull to refresh → sync connected accounts + refresh prices. Tap the eye → hide/show balances. 'Your path ahead (from Plan)' taps to the Will-it-last detail in Plan (the band chart + assumptions).</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3938,6 +4360,8 @@
 | [ Search: fide|           ]  |
 |  &gt; Fidelity Investments      |
 |  &gt; Fidelity NetBenefits      |
+|    (workplace 401(k)s are    |
+|     usually here)            |
 |                              |
 | Before you continue          |
 |  . Read-only: we can see     |
@@ -4085,13 +4509,40 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="70" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Same-brand disambiguation hint</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>When a search returns sibling institutions (Fidelity Investments vs Fidelity NetBenefits), a one-line hint under each: 'workplace 401(k)s are usually under NetBenefits' — the two-Fidelity stumble, answered where it happens.</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>copy + institution metadata from the provider list</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>institution kind hint</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>• Searching: Type-ahead list with a clear 'Can't find it? Add it by hand or import a file instead' escape under the results — no dead end.
 • Opening Plaid / linking: Full-screen progress with 'Connecting to Fidelity — this can take a few seconds'. Cancel is always available and returns to the chooser with nothing saved.
@@ -4100,34 +4551,34 @@
 • Offline: Link path disabled with 'You're offline — you can still add accounts by hand'; manual path fully works.</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-    </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>▶ Connect flow — accounts found + merge / reconcile  ·  lens: both</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>The anti-duplicate gate. After Plaid returns the institution's accounts, the user picks which to track, and anything that looks like an account they already have becomes a merge question — connect-over-existing updates the existing row (keeping its history and settings) instead of creating a twin. The same sheet serves re-imports.</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="337.5" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="337.5" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Fidelity — connected         |
@@ -4158,113 +4609,113 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 NET-NEW screen (F1), but thin: all writes go through existing store.addAsset/updateAsset; the merge sheet component is built once here and REUSED by Import v2 (screen 4). Matching logic is a small pure helper (unit-testable like holdingsImport).</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Check/uncheck accounts; choose Same/Different per match; confirm. 'Different — keep both' adds a new row whose label gets the last-4 suffix so the two are tellable apart. Back cancels without writing.</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Checkboxes and radio choices are proper toggles with spoken state. The merge question is read as one sentence including both balances. The warning icon is paired with the words 'looks like an account you already track' — never an icon alone.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Accounts-found checklist</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Every account Plaid returned, with its name, last-4 digits and current balance, each with a checkbox. Unchecked accounts are simply not tracked (and can be added later).</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F1 sync seam — fetchAccounts(connection_id). Each checked account is written via the EXISTING store.addAsset (src/store/useStore.ts) with source:'connected', institution_id, connection_id, last_synced.</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>label, institution, institution_id, connection_id, balance, kind (mapped from Plaid's account type), source, last_synced</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Linked accounts enter the same accounts array every total reads — totalAssets, assetAllocation and buildNetWorth pick them up with zero new math.</t>
-        </is>
-      </c>
-    </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Duplicate-match card (merge rule)</t>
+          <t xml:space="preserve">   Accounts-found checklist</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>When a found account matches one you already track, a plain question: same account (update it — recommended) or different (keep both). 'Same' explains what happens: your existing row keeps its history, notes and retirement settings; only the balance and freshness change.</t>
+          <t>Every account Plaid returned, with its name, last-4 digits and current balance, each with a checkbox. Unchecked accounts are simply not tracked (and can be added later).</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F1 sync seam — merge rule: candidate match when institution_id (or normalized institution name) matches AND (account name similarity OR last-4 digits OR balance within 10%). Merge executes via the EXISTING store.updateAsset (keeps asset_id) setting source:'connected', connection_id, last_synced, balance. Precedent: the existing double-count guard in BondsScreen.tsx ('Part of an existing account?') already asks this kind of question.</t>
+          <t>NET-NEW: F1 sync seam — fetchAccounts(connection_id). Each checked account is written via the EXISTING store.addAsset (src/store/useStore.ts) with source:'connected', institution_id, connection_id, last_synced.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>institution_id, institution, label, last-4 mask, balance, asset_id (preserved on merge)</t>
+          <t>label, institution, institution_id, connection_id, balance, kind (mapped from Plaid's account type), source, last_synced</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Merge preserves asset_id, so the transaction history (transactions filtered by account_id), retirement earmark (retirement_pct) and class settings all survive — one institution, one account, one continuous number.</t>
+          <t>Linked accounts enter the same accounts array every total reads — totalAssets, assetAllocation and buildNetWorth pick them up with zero new math.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Duplicate-match card (merge rule)</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>When a found account matches one you already track, a plain question: same account (update it — recommended) or different (keep both). 'Same' explains what happens: your existing row keeps its history, notes and retirement settings; only the balance and freshness change.</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F1 sync seam — merge rule: candidate match when institution_id (or normalized institution name) matches AND (account name similarity OR last-4 digits OR balance within 10%). Merge executes via the EXISTING store.updateAsset (keeps asset_id) setting source:'connected', connection_id, last_synced, balance. Precedent: the existing double-count guard in BondsScreen.tsx ('Part of an existing account?') already asks this kind of question.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>institution_id, institution, label, last-4 mask, balance, asset_id (preserved on merge)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Merge preserves asset_id, so the transaction history (transactions filtered by account_id), retirement earmark (retirement_pct) and class settings all survive — one institution, one account, one continuous number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Confirmation button + honesty line</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>The button states exactly what will happen ('Add 2 accounts + update 1'); the line beneath promises nothing is added twice without asking.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>NET-NEW: F1 sync seam (copy + orchestration); writes are the existing store actions only.</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>After confirming, the Net worth headline updates through the same buildNetWorth path — the user watches one number change once.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="70" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="70" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>• No duplicates: Merge card doesn't appear; button reads 'Add 3 accounts'.
 • Duplicate detected: Merge card appears per match, defaulting to 'Same account — update it'; the button text updates to reflect adds vs updates.
@@ -4273,34 +4724,34 @@
 • Hidden balances: Balances in the checklist mask as •••• (the shared money formatters); names and last-4 stay visible so matching still works.</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-    </row>
-    <row r="32" ht="46" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>▶ Import from a file v2 — pick, review, merge  ·  lens: both</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Import a spreadsheet file downloaded from a brokerage, now with the institution captured, every holding's classification shown AND correctable before saving (crypto, currencies and commodities land in Alternatives, Treasury bills in Cash — not mis-filed as stocks), and a merge step so re-importing the same institution updates instead of duplicating.</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-    </row>
-    <row r="33" ht="362.5" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="362.5" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt;  Import from a file        |
@@ -4333,167 +4784,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 MOSTLY REUSE: parser, preview, save path and error handling exist and are tested (src/domain/import/holdingsImport.test.ts). Net-new: institution field, crypto/currency/commodity patterns in classifyHolding (pure-function change, easy unit tests), per-row class picker, merge step (shared component from screen 3), provenance fields on save.</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Pick file → review → (fix any class via the row's picker) → set institution → resolve merge question if shown → Import. 'Choose a different file' restarts without saving.</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Each preview row already reads as one grouped sentence (name, class, value) — kept. The class picker announces current and new class. The institution field is labeled and its purpose explained ('so this account files under Vanguard'). Errors are announced, not just colored red.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="46" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   File pick + robust reading</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Pick the file; we read it even when the brokerage exported it in an unusual text encoding, and we tell you plainly if we can't ('Your data is safe — try exporting again').</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: pickFile + readCsvText (src/screens/ImportHoldingsScreen.tsx) using readFileString (src/services/fileRead) and decodeCsvBase64 + parseCsv (src/domain/import/holdingsImport.ts).</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>raw file text → rows</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>One parser for every brokerage file; the preview total is computed from the same parsed rows that get saved.</t>
-        </is>
-      </c>
-    </row>
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Institution field</t>
+          <t xml:space="preserve">   File pick + robust reading</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>One required question — which institution is this file from? Pre-guessed from the file name when possible. This is what makes the account show up under 'By institution' and what powers the no-duplicates check.</t>
+          <t>Pick the file; we read it even when the brokerage exported it in an unusual text encoding, and we tell you plainly if we can't ('Your data is safe — try exporting again').</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW (v1.1 requirement): the import screen today only asks an account NAME (accountName state) — institution is never captured. New field writes AssetAccount.institution (field EXISTS in src/domain/assets/index.ts) on every account the import creates.</t>
+          <t>EXISTING: pickFile + readCsvText (src/screens/ImportHoldingsScreen.tsx) using readFileString (src/services/fileRead) and decodeCsvBase64 + parseCsv (src/domain/import/holdingsImport.ts).</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>institution, institution_id (when it matches a known one), source:'imported', last_synced = import date</t>
+          <t>raw file text → rows</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Uses the same institution field the By-institution grouping (NetWorthScreen.tsx invGroup 'account') and the merge rule read — one field, three features.</t>
+          <t>One parser for every brokerage file; the preview total is computed from the same parsed rows that get saved.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="46" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Classification review (per-row, editable)</t>
+          <t xml:space="preserve">   Institution field</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Every holding shows the class we detected — and a tap lets you correct it before anything is saved. Crypto (BTC, ETH, coin names), foreign currencies and commodities (gold, silver) now classify as Alternatives; Treasury bills as Cash with the treasury tag; bonds as Bonds.</t>
+          <t>One required question — which institution is this file from? Pre-guessed from the file name when possible. This is what makes the account show up under 'By institution' and what powers the no-duplicates check.</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: classifyHolding (src/domain/import/holdingsImport.ts) already routes certificates of deposit / Treasury bills / money-market to cash, put-call contracts to alternatives, bond words to bonds — but has NO crypto/currency/commodity patterns, so those default to stocks today (the v1.1 bug). NET-NEW: extend classifyHolding's patterns + add the per-row class picker (today the class label in the preview is read-only, src/screens/ImportHoldingsScreen.tsx).</t>
+          <t>NET-NEW (v1.1 requirement): the import screen today only asks an account NAME (accountName state) — institution is never captured. New field writes AssetAccount.institution (field EXISTS in src/domain/assets/index.ts) on every account the import creates.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>assetClass per ImportedHolding; saved as explicit asset_class (which always wins in assetClassOf)</t>
+          <t>institution, institution_id (when it matches a known one), source:'imported', last_synced = import date</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>The class chosen here is stored as the explicit asset_class, the same field assetClassOf honors first — so the donut, class rows and Alternatives screen all agree with what the user approved in the preview.</t>
+          <t>Uses the same institution field the By-institution grouping (NetWorthScreen.tsx invGroup 'account') and the merge rule read — one field, three features.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="46" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Merge-not-duplicate step</t>
+          <t xml:space="preserve">   Classification review (per-row, editable)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>If an account from this institution already exists, the same question as the connect flow: update it (recommended, no twin) or add as new. Re-importing next quarter's file refreshes your numbers instead of doubling them.</t>
+          <t>Every holding shows the class we detected — and a tap lets you correct it before anything is saved. Crypto (BTC, ETH, coin names), foreign currencies and commodities (gold, silver) now classify as Alternatives; Treasury bills as Cash with the treasury tag; bonds as Bonds.</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: reuses the merge sheet from screen 3 (F1 sync seam merge rule). Update path replaces the matched account's positions/balance via the EXISTING store.updateAsset; add path is today's confirmImport via store.addAsset (src/screens/ImportHoldingsScreen.tsx).</t>
+          <t>EXISTING: classifyHolding (src/domain/import/holdingsImport.ts) already routes certificates of deposit / Treasury bills / money-market to cash, put-call contracts to alternatives, bond words to bonds — but has NO crypto/currency/commodity patterns, so those default to stocks today (the v1.1 bug). NET-NEW: extend classifyHolding's patterns + add the per-row class picker (today the class label in the preview is read-only, src/screens/ImportHoldingsScreen.tsx).</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>institution match → asset_id preserved on update; positions, balance, last_synced refreshed</t>
+          <t>assetClass per ImportedHolding; saved as explicit asset_class (which always wins in assetClassOf)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Same merge rule and same store actions as connecting — the user learns one behavior: 'FinWise never doubles an account'.</t>
+          <t>The class chosen here is stored as the explicit asset_class, the same field assetClassOf honors first — so the donut, class rows and Alternatives screen all agree with what the user approved in the preview.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="46" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Merge-not-duplicate step</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>If an account from this institution already exists, the same question as the connect flow: update it (recommended, no twin) or add as new. Re-importing next quarter's file refreshes your numbers instead of doubling them.</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: reuses the merge sheet from screen 3 (F1 sync seam merge rule). Update path replaces the matched account's positions/balance via the EXISTING store.updateAsset; add path is today's confirmImport via store.addAsset (src/screens/ImportHoldingsScreen.tsx).</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>institution match → asset_id preserved on update; positions, balance, last_synced refreshed</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Same merge rule and same store actions as connecting — the user learns one behavior: 'FinWise never doubles an account'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Import confirm</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>One button stating the count; equities become one tracked account (with each holding and its cost preserved), and each cash / bond / alternative line becomes its own correctly-classed entry.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>EXISTING: confirmImport (src/screens/ImportHoldingsScreen.tsx) — equities → one account with positions and derive_balance:true; others → per-class accounts via CLASS_DEFAULTS; prices refresh via store.refreshPrices.</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>positions[], lots[], balance, asset_class, kind, tax_bucket, target_return; plus new institution/source/last_synced</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Imported equities join the same positions model the transactions engine and price refresh (recomputeBalances) operate on — imported and hand-entered holdings are indistinguishable downstream.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="98" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40" ht="98" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>• Intro: Existing 'what we look for' card (symbol, quantity, cost columns). The privacy note is reworded to the honest standard: the file is read on this device; your saved data syncs encrypted to your cloud backup.
 • Reading file: Existing busy spinner on the button; cancel-safe (nothing saved until confirm).
@@ -4504,34 +4955,34 @@
 • Hidden balances: All preview amounts mask (money2 already masks under hide-balances — existing behavior).</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-    </row>
-    <row r="41" ht="46" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+    </row>
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>▶ Account detail — any class  ·  lens: both</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>One page per account, whatever it is: the balance, where the number comes from and how fresh it is, what the account holds, its full activity history, and the right record-activity buttons for its class — cash accounts get deposit/withdraw/transfer right here (today those are hidden inside the stocks screen), bonds and alternatives get buy AND sell with visible history.</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42" ht="362.5" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+    </row>
+    <row r="43" ht="362.5" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt;  Fidelity Brokerage        |
@@ -4564,167 +5015,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 NET-NEW screen, OLD parts: the transactions engine, ledger, trade-sheet interaction pattern (PerformanceScreen.tsx) and editors all exist. Work = one detail route, per-class action mapping, value_as_of field + 6-month rule, and rewiring bond/alt sell (and new buy) through recordTransaction instead of silent balance edits.</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Tap a record-activity button → small sheet (date defaults today, amount, shares/price for trades, destination account for transfers, preview of the effect) → Save appends to the ledger and updates the balance atomically. Tap a history row → detail with a delete option (deleteTransaction exists; deleting warns it recalculates the balance). Edit → the class-appropriate editor (AssetSheet, BondEditor, AltEditor).</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Action buttons say their outcome ('Record a deposit into Chase Checking'). History rows read as full sentences with signed amounts spoken as 'minus five thousand two hundred dollars'. The stale-value nudge is a labeled alert, and the paused state is announced in words. All amounts respect hidden-balances in spoken output too.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="46" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Header: name, source, freshness</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Account name + institution, the source chip (Connected read-only / Imported / Manual) and the last-updated stamp. Paused connections show the amber 'Connection paused' word with a Fix button.</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F1 sync seam fields (source, last_synced, connection_id) rendered here; account data is the EXISTING AssetAccount (src/domain/assets/index.ts).</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>label, institution, source, last_synced, connection_id</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Same chip component and wording as the tab's account rows — source language is identical everywhere.</t>
-        </is>
-      </c>
-    </row>
     <row r="44" ht="46" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Balance + class/wrapper line + holdings line</t>
+          <t xml:space="preserve">   Header: name, source, freshness</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>The account's value; underneath, what it is (asset class) and how it's taxed (plain word: taxable / tax-deferred / tax-free); for tracked accounts, the tickers it holds.</t>
+          <t>Account name + institution, the source chip (Connected read-only / Imported / Manual) and the last-updated stamp. Paused connections show the amber 'Connection paused' word with a Fix button.</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: balance (rebuilt from positions by recomputeBalances when derive_balance is true — wired in src/store/useStore.ts); assetClassOf + taxTreatmentOf + ASSET_CLASS_LABEL (src/domain/assets/index.ts); ticker surfacing mirrors withTickers in NetWorthScreen.tsx.</t>
+          <t>NET-NEW: F1 sync seam fields (source, last_synced, connection_id) rendered here; account data is the EXISTING AssetAccount (src/domain/assets/index.ts).</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>balance, cash_balance, positions, asset_class, tax_treatment, derive_balance</t>
+          <t>label, institution, source, last_synced, connection_id</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>This balance is the very number totalAssets sums — no per-screen recomputation, per the one-helper rule (repo CLAUDE.md money-math gate).</t>
+          <t>Same chip component and wording as the tab's account rows — source language is identical everywhere.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Record-activity buttons (per class)</t>
+          <t xml:space="preserve">   Balance + class/wrapper line + holdings line</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Only the actions that make sense for this account: cash accounts → Deposit / Withdraw / Transfer; stock accounts → Buy / Sell / Dividend / Deposit / Withdraw / Transfer; bonds → Buy more / Sell / Coupon received; alternatives → Buy more / Sell. Every action asks date + amount (and shares + price where relevant) and shows the effect before saving.</t>
+          <t>The account's value; underneath, what it is (asset class) and how it's taxed (plain word: taxable / pre-tax (taxed when it comes out) / tax-free (Roth)); for tracked accounts, the tickers it holds.</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>EXISTING ENGINE: recordTransaction (src/store/useStore.ts) → applyTransaction (src/domain/transactions/index.ts) with types BUY / SELL / DEPOSIT / WITHDRAWAL / TRANSFER / DIVIDEND / INTEREST / COUPON — pure and tested, including sell-clamping and the cash-goes-to-the-right-field rule (usesSleeve). NET-NEW: surfacing it HERE — today the only entry point is the trade sheet inside the stocks screen (src/screens/PerformanceScreen.tsx), and bond/alternative sales bypass the ledger entirely.</t>
+          <t>EXISTING: balance (rebuilt from positions by recomputeBalances when derive_balance is true — wired in src/store/useStore.ts); assetClassOf + taxTreatmentOf + ASSET_CLASS_LABEL (src/domain/assets/index.ts); ticker surfacing mirrors withTickers in NetWorthScreen.tsx.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Transaction {date, type, account_id, counter_account_id, ticker, shares, price, amount, note}</t>
+          <t>balance, cash_balance, positions, asset_class, tax_treatment, derive_balance</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Every recorded action goes through the ONE engine, so balances update by the same tested rules whether recorded here, on the stocks screen, or (v1.1) in the bond/alternative editors — and the Cash flow tab reads the same ledger.</t>
+          <t>This balance is the very number totalAssets sums — no per-screen recomputation, per the one-helper rule (repo CLAUDE.md money-math gate).</t>
         </is>
       </c>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Activity history</t>
+          <t xml:space="preserve">   Record-activity buttons (per class)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>The account's transactions newest-first, each in plain words with its signed cash effect ('Buy VTI, 20 shares at $260, −$5,200'). Bonds and alternatives finally get a visible history instead of silent balance edits.</t>
+          <t>Only the actions that make sense for this account: cash accounts → Deposit / Withdraw / Transfer; stock accounts → Buy / Sell / Dividend / Deposit / Withdraw / Transfer; bonds → Buy more / Sell / Coupon received; alternatives → Buy more / Sell. Every action asks date + amount (and shares + price where relevant) and shows the effect before saving.</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: store.transactions filtered by account_id (append-only ledger, src/store/useStore.ts); labels via txnLabel and amounts via cashEffect (src/domain/transactions/index.ts).</t>
+          <t>EXISTING ENGINE: recordTransaction (src/store/useStore.ts) → applyTransaction (src/domain/transactions/index.ts) with types BUY / SELL / DEPOSIT / WITHDRAWAL / TRANSFER / DIVIDEND / INTEREST / COUPON — pure and tested, including sell-clamping and the cash-goes-to-the-right-field rule (usesSleeve). NET-NEW: surfacing it HERE — today the only entry point is the trade sheet inside the stocks screen (src/screens/PerformanceScreen.tsx), and bond/alternative sales bypass the ledger entirely.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>transactions[] where account_id = this account</t>
+          <t>Transaction {date, type, account_id, counter_account_id, ticker, shares, price, amount, note}</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>History and balance can't drift: the balance was produced by applying exactly these ledger entries (applyTransaction), plus price moves for tracked holdings.</t>
+          <t>Every recorded action goes through the ONE engine, so balances update by the same tested rules whether recorded here, on the stocks screen, or (v1.1) in the bond/alternative editors — and the Cash flow tab reads the same ledger.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="46" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Activity history</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>The account's transactions newest-first, each in plain words with its signed cash effect ('Buy VTI, 20 shares at $260, −$5,200'). Bonds and alternatives finally get a visible history instead of silent balance edits.</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: store.transactions filtered by account_id (append-only ledger, src/store/useStore.ts); labels via txnLabel and amounts via cashEffect (src/domain/transactions/index.ts).</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>transactions[] where account_id = this account</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>History and balance can't drift: the balance was produced by applying exactly these ledger entries (applyTransaction), plus price moves for tracked holdings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Value as of &lt;date&gt; + Update value (bonds, alternatives, manual accounts)</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>For anything without a live price, the value carries its date ('Value as of Jun 30, 2026'), editable in place. At 6+ months old, a gentle nudge: 'This value is 7 months old — still right?' One tap confirms (re-stamps today) or updates the number.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>NET-NEW (v1.1): field value_as_of on AssetAccount, set whenever balance is hand-edited, imported, or confirmed; staleness rule = value_as_of older than 6 months. Editing writes through the EXISTING store.updateAsset.</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>value_as_of ('YYYY-MM-DD'), balance</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>The as-of date is display honesty only — the balance remains the single stored number every total reads. Confirming re-stamps the date without touching the amount.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="98" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49" ht="98" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>• Connected, healthy: Edit limits to name/class/retirement settings (balance is read-only, it syncs); Disconnect offered with the promise 'your numbers and history stay — it just stops updating' (source flips to manual, last balance kept).
 • Connection paused / expired: Amber 'Connection paused' word + last-updated date + 'Fix connection' into the re-link flow. Balance stays as of last sync. Never $0, never removed.
@@ -4735,34 +5186,34 @@
 • Hidden balances: All amounts mask via the shared formatters; activity types and dates stay readable.</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-    </row>
-    <row r="50" ht="46" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+    </row>
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>▶ Bond editor — add, buy, sell, as-of  ·  lens: both</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Track an individual bond or Treasury bill honestly: its face value, interest payments, maturity, a current value that carries its date (with a nudge when it goes stale), and — new in v1.1 — both buying more and selling recorded as visible history, not silent edits.</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="7" t="n"/>
-    </row>
-    <row r="51" ht="337.5" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+    </row>
+    <row r="52" ht="337.5" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Add / edit a bond            |
@@ -4793,167 +5244,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 REUSE: BondEditor form, validity, date picker, double-count guard, proportional-sale math, metrics. Net-new: 'treasury' kind entry, value_as_of + nudge, Buy-more action, and rewiring sale/buy/coupon through recordTransaction (small, well-tested seam — applyTransaction already supports all three types).</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Kind toggle switches Treasury bill / bond wording. Maturity date opens the existing native date picker (default-commit fix kept). Buy more / Sell open small amount+date sheets with a before/after preview; Save writes ledger + account atomically. 'Sold the whole position' shortcut prefills the full amount (existing).</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Every field labeled; the maturity picker announces the chosen date (existing accessibility label kept). The 12-month cash-vs-bond rule is stated in visible text under the date, not hidden in a tooltip. Sale confirmations read the full sentence including both values. Nudges are announced alerts.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="46" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Bond fields (name, institution, face, rate, maturity, value, held-in)</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>The existing add/edit form: name, optional institution, face value, yearly interest rate, maturity date via a date picker, current value (blank = face), and which wrapper it sits in.</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: BondEditor (src/screens/BondsScreen.tsx) — fields face_value, coupon_rate, maturity_date, balance, institution, tax_bucket on AssetAccount; date-picker default-commit fix (#11) kept; the double-count guard ('Part of an existing account?' alert) kept.</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>label, institution, face_value, coupon_rate, maturity_date, balance, tax_bucket, kind</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>A bond IS an AssetAccount, so it flows into totalAssets, the Bonds class row and the nest egg with zero extra plumbing — that is the existing design, unchanged.</t>
-        </is>
-      </c>
-    </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Treasury-bill sub-kind</t>
+          <t xml:space="preserve">   Bond fields (name, institution, face, rate, maturity, value, held-in)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>A one-tap kind choice: Treasury bill vs regular bond. Picking Treasury bill labels it properly everywhere and applies the approved rule automatically: maturing within 12 months it counts as cash, longer counts as a bond.</t>
+          <t>The existing add/edit form: name, optional institution, face value, yearly interest rate, maturity date via a date picker, current value (blank = face), and which wrapper it sits in.</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW (v1.1): add kind 'treasury' to ASSET_KINDS (src/domain/assets/index.ts). The 12-month rule ALREADY EXISTS: maturityClass (src/domain/assets/index.ts) — applied once at save, stored as explicit asset_class (approved entry rule, build-34 #8); isCashEquivalentLabel already catches 'T-bill' wording.</t>
+          <t>EXISTING: BondEditor (src/screens/BondsScreen.tsx) — fields face_value, coupon_rate, maturity_date, balance, institution, tax_bucket on AssetAccount; date-picker default-commit fix (#11) kept; the double-count guard ('Part of an existing account?' alert) kept.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>kind:'treasury', asset_class (set once via maturityClass), maturity_date</t>
+          <t>label, institution, face_value, coupon_rate, maturity_date, balance, tax_bucket, kind</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Because the class is stored explicitly at save (assetClassOf honors it first), the tab's Cash and Bonds rows, the donut and the importer all file the same Treasury bill the same way.</t>
+          <t>A bond IS an AssetAccount, so it flows into totalAssets, the Bonds class row and the nest egg with zero extra plumbing — that is the existing design, unchanged.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Value as of + staleness nudge</t>
+          <t xml:space="preserve">   Treasury-bill sub-kind</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>The current value always shows the date you last set it, editable in place. At 6+ months a nudge asks 'still right?' — confirm re-stamps today, or type the new value.</t>
+          <t>A one-tap kind choice: Treasury bill vs regular bond. Picking Treasury bill labels it properly everywhere and applies the approved rule automatically: maturing within 12 months it counts as cash, longer counts as a bond.</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW (v1.1): value_as_of field (shared with screen 5); today the bonds screen footnote admits 'value is what you enter' but carries no date. Rendering rule shared app-wide.</t>
+          <t>NET-NEW (v1.1): add kind 'treasury' to ASSET_KINDS (src/domain/assets/index.ts). The 12-month rule ALREADY EXISTS: maturityClass (src/domain/assets/index.ts) — applied once at save, stored as explicit asset_class (approved entry rule, build-34 #8); isCashEquivalentLabel already catches 'T-bill' wording.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>value_as_of, balance</t>
+          <t>kind:'treasury', asset_class (set once via maturityClass), maturity_date</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Same field and same 6-month rule as alternatives and manual accounts — one staleness concept, one wording.</t>
+          <t>Because the class is stored explicitly at save (assetClassOf honors it first), the tab's Cash and Bonds rows, the donut and the importer all file the same Treasury bill the same way.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Buy more + Sell with history</t>
+          <t xml:space="preserve">   Value as of + staleness nudge</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>'Buy more' records a purchase (amount, date) that raises the value and face proportionally; 'Sell' records full or partial proceeds. Both appear in the visible history here and in Account detail. A full sale asks 'Close this bond?' before removing it.</t>
+          <t>The current value always shows the date you last set it, editable in place. At 6+ months a nudge asks 'still right?' — confirm re-stamps today, or type the new value.</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>EXISTING (partial): applySale in BondsScreen.tsx handles partial sale (lowers balance, scales face_value proportionally) and full close — but as a silent balance edit, sale-only, no buy, no trace. NET-NEW (v1.1): route both through recordTransaction (src/store/useStore.ts) as BUY / SELL ledger entries (types EXIST in src/domain/transactions/index.ts) so history is real; COUPON entries record interest received.</t>
+          <t>NET-NEW (v1.1): value_as_of field (shared with screen 5); today the bonds screen footnote admits 'value is what you enter' but carries no date. Rendering rule shared app-wide.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Transaction {type:'BUY'|'SELL'|'COUPON', account_id, amount, date}; face_value scaled on partial sale (existing proportional rule kept)</t>
+          <t>value_as_of, balance</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Bond buys/sells land in the same ledger the Cash flow tab and Account detail read — the confirmation sheet still previews the before/after values exactly as today's alert does.</t>
+          <t>Same field and same 6-month rule as alternatives and manual accounts — one staleness concept, one wording.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="46" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Buy more + Sell with history</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>'Buy more' records a purchase (amount, date) that raises the value and face proportionally; 'Sell' records full or partial proceeds. Both appear in the visible history here and in Account detail. A full sale asks 'Close this bond?' before removing it.</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING (partial): applySale in BondsScreen.tsx handles partial sale (lowers balance, scales face_value proportionally) and full close — but as a silent balance edit, sale-only, no buy, no trace. NET-NEW (v1.1): route both through recordTransaction (src/store/useStore.ts) as BUY / SELL ledger entries (types EXIST in src/domain/transactions/index.ts) so history is real; COUPON entries record interest received.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Transaction {type:'BUY'|'SELL'|'COUPON', account_id, amount, date}; face_value scaled on partial sale (existing proportional rule kept)</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Bond buys/sells land in the same ledger the Cash flow tab and Account detail read — the confirmation sheet still previews the before/after values exactly as today's alert does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Bond metrics (context, unchanged)</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Yearly interest income, current yield, estimated yield-to-maturity and the soonest maturity — labeled as estimates, matching the truth-teller rule.</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>EXISTING: bondInfo, annualCoupon, currentYield, approxYTM, yearsToMaturity, bondSummary (src/domain/bonds); the 'estimate' footnote already exists on BondsScreen.tsx.</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>face_value, coupon_rate, maturity_date, balance</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Metrics derive from the same four stored fields the editor saves — no second copy of the bond's numbers.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="98" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="98" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>• Add new: Save disabled until name, face value, rate and a valid maturity date exist (existing validity rule). If the institution matches a non-bond account with a balance, the existing double-count question fires ('part of it' lowers that account so nothing counts twice).
 • Edit: All fields prefilled (existing); history section visible; Delete confirms.
@@ -4964,34 +5415,34 @@
 • Hidden balances: All amounts mask; dates, rate and maturity stay visible.</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-    </row>
-    <row r="59" ht="46" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="60" ht="46" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>▶ Alternative editor — add, buy, sell, as-of  ·  lens: both</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Track anything that isn't a stock, bond or bank account — crypto, private funds, gold, annuities, option contracts — at a value you set, with that value carrying its date, a nudge when it goes stale, and buying/selling recorded as visible history (today: sale-only, and it leaves no trace).</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="7" t="n"/>
-    </row>
-    <row r="60" ht="337.5" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="337.5" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Add / edit an investment     |
@@ -5022,140 +5473,140 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 REUSE: the whole AltEditor form, hints, benchmarks, sale confirmations and delete flow. Net-new: value_as_of + nudge, Buy-more, and routing buy/sell through recordTransaction — same small seam as the bond editor, shared action-sheet component.</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Type chips switch hint + benchmark live (existing). Buy more / Sell open the shared amount+date sheet with before/after preview. 'Sold all of it' shortcut prefills the full value (existing). Save/Cancel as today.</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Chips are toggle buttons with selected state announced. Hints are visible text, not tooltips. Sale/close confirmations read as full sentences with both values. The staleness nudge is an announced alert paired with the clock icon and words.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="46" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Type chips + honest hint</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Pick what it is; each type shows a one-line truth ('Illiquid; values are estimates until a sale') and its historical benchmark, labeled as a benchmark, not a promise.</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: AltEditor (src/screens/OtherInvestmentsScreen.tsx) — ALT_KINDS chips (src/domain/alternatives), ALT_HINT copy, benchmarkReturn (src/domain/assets/index.ts) with sources in BENCHMARK_META.</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>kind, target_return</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>The same benchmarkReturn feeds this hint, the Alternatives screen summary and the retirement projection's blended return — one benchmark table.</t>
-        </is>
-      </c>
-    </row>
     <row r="62" ht="46" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Name, institution, value, held-in</t>
+          <t xml:space="preserve">   Type chips + honest hint</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>The existing form: name, where it's held (institution — this is what groups it under 'By institution' on the tab), current value, and its tax wrapper.</t>
+          <t>Pick what it is; each type shows a one-line truth ('Illiquid; values are estimates until a sale') and its historical benchmark, labeled as a benchmark, not a promise.</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: AltEditor fields → store.addAsset / store.updateAsset (src/store/useStore.ts); AssetAccount.institution, balance, tax_bucket.</t>
+          <t>EXISTING: AltEditor (src/screens/OtherInvestmentsScreen.tsx) — ALT_KINDS chips (src/domain/alternatives), ALT_HINT copy, benchmarkReturn (src/domain/assets/index.ts) with sources in BENCHMARK_META.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>label, institution, balance, tax_bucket, asset_class:'alternatives'</t>
+          <t>kind, target_return</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>An alternative IS an AssetAccount with class 'alternatives' — alternativesTotal, the donut and the tab's Alternatives row all read the same stored balance.</t>
+          <t>The same benchmarkReturn feeds this hint, the Alternatives screen summary and the retirement projection's blended return — one benchmark table.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="46" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Value as of + staleness nudge</t>
+          <t xml:space="preserve">   Name, institution, value, held-in</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>'Value as of &lt;date&gt;' under the value, editable in place; at 6+ months: 'This value is 8 months old — still right?' Confirm re-stamps, or update the number. Especially important here — these have no live prices.</t>
+          <t>The existing form: name, where it's held (institution — this is what groups it under 'By institution' on the tab), current value, and its tax wrapper.</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW (v1.1): value_as_of field (same field, rule and wording as bonds and manual accounts); today the screen's footnote says 'values are what you enter' with no date.</t>
+          <t>EXISTING: AltEditor fields → store.addAsset / store.updateAsset (src/store/useStore.ts); AssetAccount.institution, balance, tax_bucket.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>value_as_of, balance</t>
+          <t>label, institution, balance, tax_bucket, asset_class:'alternatives'</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>One staleness rule app-wide (6 months) — same words on bonds, alternatives and manual accounts.</t>
+          <t>An alternative IS an AssetAccount with class 'alternatives' — alternativesTotal, the donut and the tab's Alternatives row all read the same stored balance.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="46" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Value as of + staleness nudge</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>'Value as of &lt;date&gt;' under the value, editable in place; at 6+ months: 'This value is 8 months old — still right?' Confirm re-stamps, or update the number. Especially important here — these have no live prices.</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW (v1.1): value_as_of field (same field, rule and wording as bonds and manual accounts); today the screen's footnote says 'values are what you enter' with no date.</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>value_as_of, balance</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>One staleness rule app-wide (6 months) — same words on bonds, alternatives and manual accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="46" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Buy more + Sell with history</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>'Buy more' records money added (raises the value); 'Sell' records full or partial proceeds (existing confirmations kept: partial lowers it, full asks 'Close this investment?'). Both write visible history rows.</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>EXISTING (partial): applySale in OtherInvestmentsScreen.tsx — sale-only, silent balance edit, full sale just deletes. NET-NEW (v1.1): both actions write BUY / SELL entries via recordTransaction (src/store/useStore.ts) so the history survives and the Cash flow tab sees the movement.</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Transaction {type:'BUY'|'SELL', account_id, amount, date}</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Identical action sheet and ledger path as bonds and Account detail — record once, read everywhere.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="84" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66" ht="84" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>• Add new: Save disabled until name and a value above zero exist (existing validity).
 • Edit: Prefilled; history visible; Delete uses the existing 'Delete this holding?' confirm.
@@ -5165,9 +5616,9 @@
 • Hidden balances: Amounts mask; type, name and dates stay visible.</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5308,7 +5759,7 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Tap a period chip -&gt; whole screen recomputes. Tap any holding row -&gt; its detail (screens 2/3/4 by type). Tap 'See all' -&gt; full ranked list; 'By account' -&gt; same rows grouped by account, each account row showing its reported yearly return with an Edit pencil. Tap the concentration callout -&gt; scrolls to that holding. Tap Look back -&gt; screen 5. Eye icon in the top bar toggles hide-balances globally. Pull to refresh re-fetches prices (fetchPriceSeries, src/services/marketData.ts).</t>
+Tap a period chip -&gt; whole screen recomputes. Tap any holding row -&gt; its detail (screens 2/3/4 by type). Tap 'See all' -&gt; full ranked list; 'By account' -&gt; same rows grouped by account, each account row showing its reported yearly return with an Edit pencil. Tap the concentration callout -&gt; scrolls to that holding. Tap Look back -&gt; screen 5. Eye icon in the top bar toggles hide-balances globally. Pull to refresh re-fetches prices (fetchPriceSeries, src/services/marketData.ts). Arriving from Home's 'this month' figure opens with the 1M period selected (handoff rule: the number you tapped is the number you land on).</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6185,7 +6636,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
@@ -6196,7 +6647,8 @@
           <t>• Value 6+ months old: A nudge card appears above the facts: '! This value is 7 months old. Still about right?' with [Yes, keep it] (stamps value_as_of to today without changing the number) and [Update value].
 • No coupon or no maturity (e.g. a bond fund): The rate-sensitivity card and yield-to-maturity line HIDE (no honest math possible); bond funds with a live ticker show the standard equity-style return instead. Never a guessed number.
 • Bond matured: Banner: 'This bond matured Jun 30, 2036 — record what happened' with [Record payoff]; yields and sensitivity hide (approxYTM already returns nothing when matured).
-• Hide balances on: $95,000 / $100,000 / $4,500 masked to ••••; percentages, dates and years-away remain.</t>
+• Hide balances on: $95,000 / $100,000 / $4,500 masked to ••••; percentages, dates and years-away remain.
+• Bond FUND (has a ticker, no maturity): Routes to the equity-style detail INCLUDING the vs-the-market card, PLUS one plain sentence in place of the rates card: 'Bond funds fall when interest rates rise — rates rose this year, which is why this fund is down.' The user leaves with the story, not just the number.</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
@@ -7266,7 +7718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7332,7 +7784,7 @@
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="7" t="n"/>
     </row>
-    <row r="3" ht="387.5" customHeight="1">
+    <row r="3" ht="400" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
@@ -7345,7 +7797,7 @@
 |                              |
 | Safe to spend                |
 |  This month        $5,840    |
-|  This year   ~$70,100 est.   |
+|  This year   ~$71,600 est.   |
 |   + Guaranteed      $4,200   |
 |     Social Security $2,600   |
 |     Pension         $1,600   |
@@ -7362,13 +7814,14 @@
 |  Jan 27  in|#####| out|###|  |
 |  ...     Jun 27              |
 |  (tap a month for detail)    |
+| [ All bills &amp; the calendar &gt; ]|
 |                              |
 | Draw comes from   Steer it &gt; |
 |  1 Cash     2 Taxable        |
 |  3 Pre-tax  4 Roth    Why? &gt; |
 |                              |
 | Will it last?  Likely - 84%  |
-|  estimate, range 71-95%      |
+|  estimate - 71-95% across bad-to-good markets      |
 |  Lives in your Plan &gt;        |
 +------------------------------+</t>
         </is>
@@ -7382,7 +7835,7 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Tap any month bar → Month detail for that dated month. Tap 'Steer it' → Draw-order steer sheet. Tap 'Why?' → plain-English explainer per bucket (text already written in withdrawalOrder). Tap the will-it-last strip → Plan tab (canonical home). Pull to refresh → re-pull balances and re-derive the hero. Tap 'this year' → expands a 12-row list of the same cells as the bars.</t>
+Tap any month bar → Month detail for that dated month. Tap 'Steer it' → Draw-order steer sheet. Tap 'Why?' → plain-English explainer per bucket (text already written in withdrawalOrder). Tap the will-it-last strip → Plan tab (canonical home). Pull to refresh → re-pull balances and re-derive the hero. Tap 'this year' → expands a 12-row list of the same cells as the bars. 'All bills &amp; the calendar' -&gt; Bill calendar v2 (add/edit dated bills — the first-run 'add your property tax' step lands here too).</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -7454,7 +7907,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>~$70,100 with an 'estimate' tag — the sum of the 12 dated cells, so lumpy months are counted as they really fall.</t>
+          <t>~$71,600 with an 'estimate' tag — the sum of the 12 dated cells, so lumpy months are counted as they really fall.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -7671,7 +8124,7 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
     </row>
-    <row r="16" ht="350" customHeight="1">
+    <row r="16" ht="400" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
@@ -7696,6 +8149,11 @@
 |    + Bonus lands Mar $8,000  |
 |  ...     Jun 27              |
 |  (tap a month for detail)    |
+| [ All bills &amp; the calendar &gt; ]|
+|                              |
+| Committed from your Plan     |
+|  (shows here once adopted,   |
+|   e.g. parents $2,000/mo)    |
 |                              |
 | Your future paycheck         |
 |  PROJECTION - an estimate,   |
@@ -7718,7 +8176,7 @@
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Tap a bar → Month detail. Tap the projection card → Plan tab retirement section. Tap spent-so-far → Budget screen this-month view. Lens switches automatically from the profile (receiving retirement income → retired lens) with a manual toggle in settings.</t>
+Tap a bar → Month detail. Tap the projection card → the Will-it-last detail in Plan (where its assumptions live, each with an edit link). Tap spent-so-far → Month detail for the current month (this design owns it; no legacy screen). Lens switches automatically from the profile (receiving retirement income → retired lens) with a manual toggle in settings. 'All bills &amp; the calendar' -&gt; Bill calendar v2 (add/edit dated bills — the first-run 'add your property tax' step lands here too).</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -7863,49 +8321,77 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Plan commitments line (working lens)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Once a multi-goal plan is adopted, each commitment appears as a named line ('Parents $2,000/mo · from your Plan') and the surplus line becomes 'Free to spend AFTER your plan' — the month never silently overstates free money.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: reads commitments[] from the F11 shared assumptions (the adoption patch); subtracted after bills+debt in the displayed free-to-spend.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>commitments[] {label, monthlyAmount}</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the composer's 'shortfall here can never coexist with a surplus on Cash flow' — now satisfiable on THIS lens: adopted commitments visibly reduce free-to-spend (the walkthrough's trust-breaker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="84" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>• No income captured (empty): In/out card collapses to a friendly setup prompt ('Tell us what you earn and we will map your year'); bars render as gray placeholders with dated labels so the shape of the promise is visible.
 • Pre-retirement projection: The future-paycheck card ALWAYS carries the 'PROJECTION — an estimate, not a promise' label; if retirement inputs are missing it shows a 'finish your Plan to see this' link instead of guessing.
 • Hidden balances: Dollars masked; surplus sign still shown as the word 'ahead' or 'behind' with an icon.
 • Stale balances: Same calm 'as of' banner as the retired lens; the spent-so-far line notes the last transaction date it knows about.
-• Deficit month: A month where spending exceeds take-home shows a minus surplus with a word flag and one plain sentence ('March take-home dips because of the insurance bill — your bonus month covers it').</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+• Deficit month: A month where spending exceeds take-home shows a minus surplus with a word flag and one plain sentence ('March take-home dips because of the insurance bill — your bonus month covers it').
+• After adopting commitments: The commitments block lists each adopted goal; 'Surplus' is relabeled 'Free to spend after your plan' with the subtraction visible. Removing the plan (revert) restores the plain surplus.</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>▶ Month detail  ·  lens: Both (retired example shown)</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Tap any bar and see exactly why that month looks the way it does: each income item on its real date, the big dated bills that land that month, the safe draw, and the resulting safe-to-spend. The month is fully dated (November 2026, not just 'Nov'), and the rows sum — visibly — to the number on the bar.</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="312.5" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="312.5" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Cash flow    November 2026 |
@@ -7934,167 +8420,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Net-new screen, but it is a pure renderer over one F2/F5 cell — no math of its own. Cheapest correct build: pass the cell object in and forbid any recomputation in the component (mirrors the one-concept-one-helper rule).</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Swipe left/right → previous/next dated month (stops at the 12-month window edges, with 'beyond the window' explained in words). Tap a bill row → edit that bill (Bill calendar's editor). Tap safe draw → the draw-order steer sheet. Back → returns to the main screen scrolled to the same bar.</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 The screen reads top-to-bottom as a sentence: month, headline, why, then rows. Each row announces name, date in full ('November fifteenth'), and amount. Plus/minus announced as 'in'/'out'.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Dated month title</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>'November 2026' — full month and year, from the tapped F2 cell.</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>F2 canonical grid cell (promoted cashflowYear, src/domain/cashflow/index.ts — its label logic already appends the year across the wrap).</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>cell.calendarMonth, cell.year</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>PIN: title matches the tapped bar's label exactly.</t>
-        </is>
-      </c>
-    </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Safe to spend headline + reason line</t>
+          <t xml:space="preserve">   Dated month title</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>$3,940 with one plain sentence for unusual months ('lower than usual — property tax lands this month').</t>
+          <t>'November 2026' — full month and year, from the tapped F2 cell.</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F5 paycheck engine — this is the same cell's netSafeToSpend the bar and (for the current month) the hero show; the reason line names the largest dated bill in the cell.</t>
+          <t>F2 canonical grid cell (promoted cashflowYear, src/domain/cashflow/index.ts — its label logic already appends the year across the wrap).</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>F5 cell.netSafeToSpend, cell.bills[] (largest)</t>
+          <t>cell.calendarMonth, cell.year</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>PIN: headline = bar = hero (when current month); the agreement test sums the visible rows and must reproduce it.</t>
+          <t>PIN: title matches the tapped bar's label exactly.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Money-in list with real dates</t>
+          <t xml:space="preserve">   Safe to spend headline + reason line</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>'Social Security · 3rd · $2,600', 'Pension · 1st · $1,600', 'Safe draw · $1,640' (retired) or salary/bonus/vesting rows (working). Day shown when known; plain month otherwise — no invented dates.</t>
+          <t>$3,940 with one plain sentence for unusual months ('lower than usual — property tax lands this month').</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>EXISTING amounts: retirementIncomeMonthly per-source fields (src/domain/income/onboarding.ts) / salaryGrossByMonth, bonusMonth, rsuGrants vest dates (same file). NET-NEW: per-source pay-day field (optional) and F5's per-month placement.</t>
+          <t>NET-NEW: F5 paycheck engine — this is the same cell's netSafeToSpend the bar and (for the current month) the hero show; the reason line names the largest dated bill in the cell.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ri_* + ri_*_freq + NET-NEW ri_*_day, salaryByMonth, bonusMonth, rsuGrants[].date</t>
+          <t>F5 cell.netSafeToSpend, cell.bills[] (largest)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PIN: per-source amounts equal the named lines on the main screen's guaranteed decomposition.</t>
+          <t>PIN: headline = bar = hero (when current month); the agreement test sums the visible rows and must reproduce it.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Big bills list (dated)</t>
+          <t xml:space="preserve">   Money-in list with real dates</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>'Property tax · Nov 15 · −$1,900' — the dated non-monthly bills that reduce this month's safe-to-spend.</t>
+          <t>'Social Security · 3rd · $2,600', 'Pension · 1st · $1,600', 'Safe draw · $1,640' (retired) or salary/bonus/vesting rows (working). Day shown when known; plain month otherwise — no invented dates.</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: non-monthly spending categories in their months (spendByMonth, src/domain/budget/index.ts) with day-level dates from upcomingBills (src/domain/cashflow/index.ts: dueDate built from months + dueDay).</t>
+          <t>EXISTING amounts: retirementIncomeMonthly per-source fields (src/domain/income/onboarding.ts) / salaryGrossByMonth, bonusMonth, rsuGrants vest dates (same file). NET-NEW: per-source pay-day field (optional) and F5's per-month placement.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>spendCats months/dueDay/amount, NET-NEW year on one-off bills</t>
+          <t>ri_* + ri_*_freq + NET-NEW ri_*_day, salaryByMonth, bonusMonth, rsuGrants[].date</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>PIN: identical bill rows (label, date, amount) as the Bill calendar's 'Coming up' for this month.</t>
+          <t>PIN: per-source amounts equal the named lines on the main screen's guaranteed decomposition.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Big bills list (dated)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>'Property tax · Nov 15 · −$1,900' — the dated non-monthly bills that reduce this month's safe-to-spend.</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: non-monthly spending categories in their months (spendByMonth, src/domain/budget/index.ts) with day-level dates from upcomingBills (src/domain/cashflow/index.ts: dueDate built from months + dueDay).</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>spendCats months/dueDay/amount, NET-NEW year on one-off bills</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>PIN: identical bill rows (label, date, amount) as the Bill calendar's 'Coming up' for this month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Regular bills list</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>'Mortgage · 1st · $1,240', 'Car insurance · 20th · $310' — the everyday bills the safe-to-spend envelope pays for, listed for completeness but NOT subtracted twice.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>EXISTING: monthly spending categories (spendBuckets/spendByMonth, src/domain/budget/index.ts) and debt payments (requiredPayment + due_day, src/domain/debt/index.ts). A deferred debt appears here only from its NET-NEW first_payment_date onward.</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>spendCats monthly bucket, Debt.due_day, Debt.monthly_payment, NET-NEW Debt.first_payment_date</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>PIN: a deferred debt shows in NO month before its first payment date, on any surface (grid, calendar, this list) — one test walks all three.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="70" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>• Current month: Adds a 'so far' line using actual transactions (budgetVsActual) under the regular-bills list; headline notes 'as of today'.
 • Quiet month (no dated bills): Big-bills section shows 'No big bills this month' in words — the section never silently disappears, so absence is information.
@@ -8103,41 +8589,41 @@
 • Stale balances: Footer swaps to 'as of &lt;date&gt; — refresh your accounts to update these'.</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-    </row>
-    <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>▶ Bill calendar v2  ·  lens: Both</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>The same 12 dated months as everywhere else, viewed as a running-balance table: money in, money out, and what is left at the end of each month, starting from real cash on hand. Big bills get day-level treatment ('will the money be there two days before it is due?'). This is where dated bills are added and edited, and where a deferred loan visibly starts paying in its real first month.</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="400" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="400" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Bill calendar                |
 |  July 2026 - June 2027       |
 |                              |
 | Cash on hand now  $18,400    |
-|  from your linked accounts   |
+|  from your accounts   |
 |  (edit)                      |
 |                              |
 | OK  You stay above zero in   |
@@ -8166,221 +8652,221 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Smallest lift of the tab: BillCalendarScreen.tsx already renders cashflowYear + upcomingBills + cashTotal. Work = point it at F2 (which IS cashflowYear promoted), add the year field on one-off bills, add the deferred-debt field + payoffPlan change, and retire its student-era wording (scholarships/loan-disbursement copy stays in code paths but out of this audience's UI).</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Tap a row → Month detail for that dated month. Tap a coming-up bill → edit it. 'Add a dated bill' → the form above. Editing cash on hand re-chains all 12 End balances immediately.</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Table rows read as full sentences ('November 2026: in five thousand eight hundred forty, out seven thousand seven hundred fifty, ending balance two thousand one hundred — short-risk flagged'). '!' always paired with the word 'short'. Form fields have full labels and date pickers, not free text.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="46" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Window title</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>'July 2026 – June 2027' — states the dated window outright.</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>F2 canonical grid anchor (promoted cashflowYear, src/domain/cashflow/index.ts).</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>anchor month/year</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>PIN: same window as the Cash flow bars.</t>
-        </is>
-      </c>
-    </row>
     <row r="36" ht="46" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Cash on hand</t>
+          <t xml:space="preserve">   Window title</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>$18,400 auto-filled from linked accounts, editable — the starting balance the table carries forward.</t>
+          <t>'July 2026 – June 2027' — states the dated window outright.</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: cashTotal(accounts) in src/domain/assets (already how BillCalendarScreen.tsx seeds its input), with the manual-edit affordance kept.</t>
+          <t>F2 canonical grid anchor (promoted cashflowYear, src/domain/cashflow/index.ts).</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>asset accounts, tax_bucket cash</t>
+          <t>anchor month/year</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>PIN: equals the cash figure Net worth shows for the same accounts.</t>
+          <t>PIN: same window as the Cash flow bars.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="46" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Verdict line</t>
+          <t xml:space="preserve">   Cash on hand</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>'OK — you stay above zero in all 12 months; lowest point $18,400 (today)' or 'Careful — short in Nov 2026 and Jan 2027', always with the dated month named.</t>
+          <t>$18,400 auto-filled from linked accounts, editable — the starting balance the table carries forward.</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: cashflowYear's shortMonths and lowestBalance (src/domain/cashflow/index.ts), carried into F2.</t>
+          <t>EXISTING: cashTotal(accounts) in src/domain/assets (already how BillCalendarScreen.tsx seeds its input), with the manual-edit affordance kept.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>cell.runningBalance, shortMonths, lowestBalance</t>
+          <t>asset accounts, tax_bucket cash</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>PIN: the flagged months match the '!' flags on the Cash flow bars.</t>
+          <t>PIN: equals the cash figure Net worth shows for the same accounts.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="46" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   12-row dated table (In / Out / End)</t>
+          <t xml:space="preserve">   Verdict line</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>One row per dated month, Jul 26 → Jun 27, with inflow, outflow, and end-of-month balance; short months flagged with '!' plus a word.</t>
+          <t>'OK — you stay above zero in all 12 months; lowest point $18,400 (today)' or 'Careful — short in Nov 2026 and Jan 2027', always with the dated month named.</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: cashflowYear already returns exactly this shape ({label, inflow, outflow, net, balance} × 12 with year-wrap labels); it is promoted to F2 and re-read here.</t>
+          <t>EXISTING: cashflowYear's shortMonths and lowestBalance (src/domain/cashflow/index.ts), carried into F2.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>F2 cells</t>
+          <t>cell.runningBalance, shortMonths, lowestBalance</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>PIN: row In/Out = the Cash flow bar's in/out for the same cell; End chains exactly (previous End + In − Out).</t>
+          <t>PIN: the flagged months match the '!' flags on the Cash flow bars.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="46" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Coming up (day-level big bills)</t>
+          <t xml:space="preserve">   12-row dated table (In / Out / End)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>'Property tax $1,900 due Nov 15, 2026 — covered: about $9,850 there by Nov 13' or, when short, how much to set aside and by when.</t>
+          <t>One row per dated month, Jul 26 → Jun 27, with inflow, outflow, and end-of-month balance; short months flagged with '!' plus a word.</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: upcomingBills in src/domain/cashflow/index.ts (dueDate, needByDate two days before, askByDate, availableByNeed, shortfall). Copy re-aimed at 55-70: the cover source reads 'your savings or a backup', not a family ask.</t>
+          <t>EXISTING: cashflowYear already returns exactly this shape ({label, inflow, outflow, net, balance} × 12 with year-wrap labels); it is promoted to F2 and re-read here.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>UpcomingBill: dueDate, needByDate, askByDate, shortfall, availableByNeed</t>
+          <t>F2 cells</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>PIN: each bill's amount and date match its row in Month detail and its month's Out on the table.</t>
+          <t>PIN: row In/Out = the Cash flow bar's in/out for the same cell; End chains exactly (previous End + In − Out).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="46" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Add / edit a dated bill</t>
+          <t xml:space="preserve">   Coming up (day-level big bills)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>A small form: name, amount, due date (day, month, AND year for one-offs), repeats-yearly toggle, essential-or-flexible.</t>
+          <t>'Property tax $1,900 due Nov 15, 2026 — covered: about $24,900 there by Nov 13' or, when short, how much to set aside and by when.</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>EXISTING storage: writes a non-monthly spending category (spendCats: amount, months, dueDay, tier — src/domain/budget/index.ts consumes it). NET-NEW: a year field on one-off bills; the grid can already place month+year via slotForMY (cashflowYear, src/domain/cashflow/index.ts), which today only scholarship/loan items use.</t>
+          <t>EXISTING: upcomingBills in src/domain/cashflow/index.ts (dueDate, needByDate two days before, askByDate, availableByNeed, shortfall). Copy re-aimed at 55-70: the cover source reads 'your savings or a backup', not a family ask.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>spendCats: label, amount, months[], dueDay, tier, NET-NEW year</t>
+          <t>UpcomingBill: dueDate, needByDate, askByDate, shortfall, availableByNeed</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>PIN: saving a bill updates the F2 cells once, and the table, bars, hero, and month detail all move together — one recompute event.</t>
+          <t>PIN: each bill's amount and date match its row in Month detail and its month's Out on the table.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="46" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Add / edit a dated bill</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>A small form: name, amount, due date (day, month, AND year for one-offs), repeats-yearly toggle, essential-or-flexible.</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING storage: writes a non-monthly spending category (spendCats: amount, months, dueDay, tier — src/domain/budget/index.ts consumes it). NET-NEW: a year field on one-off bills; the grid can already place month+year via slotForMY (cashflowYear, src/domain/cashflow/index.ts), which today only scholarship/loan items use.</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>spendCats: label, amount, months[], dueDay, tier, NET-NEW year</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>PIN: saving a bill updates the F2 cells once, and the table, bars, hero, and month detail all move together — one recompute event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Deferred debt row</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>'Car loan (new) — first payment Mar 1, 2027, $385/month' — visible now, but Out rows before Mar 27 show no payment for it.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>NET-NEW FIELD: Debt.first_payment_date (src/domain/debt/index.ts — the Debt record has due_day and payoff_date today, but payoffPlan starts every debt's payments at month 1 = now, and the grid has no way to start a payment later). F5/F2 place requiredPayment monthly from max(today, first_payment_date); payoffPlan's loop starts this debt's payments at that month while interest still accrues from now.</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Debt.first_payment_date (NET-NEW), due_day, monthly_payment, minimum_monthly_payment, interest_rate_apr</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>PIN (new, v1.1): no surface shows a payment for a deferred debt before its first payment date, and the payoff plan's debt-free date reflects the deferral — one test covers grid, calendar, month detail, and payoff math.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="70" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43" ht="70" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>• Setup incomplete (empty): Keeps the existing gate: explains the calendar is built from income timing + bills, offers 'Finish my setup' (BillCalendarScreen.tsx already does this).
 • Short months present: Verdict flips to 'Careful' with the dated months named; short rows get '!' + the word 'short'; the biggest cause is named in one sentence.
@@ -8389,34 +8875,34 @@
 • Stale balances: Cash-on-hand line shows 'as of &lt;date&gt;' and the verdict adds 'based on balances from &lt;date&gt;'.</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-    </row>
-    <row r="44" ht="46" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+    </row>
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>▶ Draw-order steer sheet  ·  lens: Retired (working sees it in projection mode)</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY the suggested order is what it is, in plain words. Guide, never advise: the suggested order is a starting point the user can overrule, and the required-by-law withdrawal after age 73 is pinned and explained, not negotiable.</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-    </row>
-    <row r="45" ht="325" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="325" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | Where the draw comes from    |
@@ -8446,167 +8932,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 The order model, the required-withdrawal pin, and every why sentence already exist in src/domain/decumulation/index.ts — this sheet is mostly UI plus two net-new pieces: a stored user draw-order preference and the F5 re-run wrapper that feeds it into the existing simulation and depletion helpers.</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Drag or tap up/down arrows to reorder (except the pinned step). 'Why this order?' → explainer sheet. 'Re-run with my order' → comparison updates in place, then 'Keep this order' saves. 'Reset to suggested' → previews the default before saving. Closing without saving changes nothing.</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Reordering works via buttons (not drag-only). Each bucket announces name, balance, and position ('Pre-tax, four hundred fifteen thousand dollars, third of four — move up, move down'). The before/after comparison is read as a sentence, arrows never carry the meaning alone.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="46" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Bucket list with balances</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Cash $38,000 / Taxable $210,000 / Pre-tax $415,000 / Roth $88,000, numbered in draw order, with up/down reorder controls.</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: taxBucketSplit(accounts) in src/domain/decumulation/index.ts (retirement-earmarked portion via earmarkedAmount, src/domain/assets); suggested order + per-step balances from withdrawalOrder(split, age) (same file).</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>AssetAccount.tax_bucket, earmark, age</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>PIN: the four balances sum to the nest egg behind the safe draw and match Net worth's grouping of the same accounts.</t>
-        </is>
-      </c>
-    </row>
     <row r="47" ht="46" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pinned required-withdrawal step (age 73+)</t>
+          <t xml:space="preserve">   Bucket list with balances</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>For users 73 or older, step 1 becomes 'Required withdrawal — first: $15,660' with the sentence that the law makes you take this from pre-tax accounts whether you need it or not; it cannot be reordered.</t>
+          <t>Cash $38,000 / Taxable $210,000 / Pre-tax $415,000 / Roth $88,000, numbered in draw order, with up/down reorder controls.</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: withdrawalOrder already injects this step using RMD_START_AGE (73) and rmdAtAge(preTax, age) with the Uniform Lifetime Table divisors (src/domain/decumulation/index.ts).</t>
+          <t>EXISTING: taxBucketSplit(accounts) in src/domain/decumulation/index.ts (retirement-earmarked portion via earmarkedAmount, src/domain/assets); suggested order + per-step balances from withdrawalOrder(split, age) (same file).</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>age, preTax balance, rmdDivisor</t>
+          <t>AssetAccount.tax_bucket, earmark, age</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>PIN: the required amount here = the required-withdrawal figure shown in Plan's retirement section (same helper, same balance).</t>
+          <t>PIN: the four balances sum to the nest egg behind the safe draw and match Net worth's grouping of the same accounts.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="46" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Why explainer</t>
+          <t xml:space="preserve">   Pinned required-withdrawal step (age 73+)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>One plain sentence per bucket ('Cash first — it earns the least, so use it before it loses to inflation', 'Roth last — tax-free growth, so let it run'), shown in a tap-through sheet.</t>
+          <t>For users 73 or older, step 1 becomes 'Required withdrawal — first: $15,660' with the sentence that the law makes you take this from pre-tax accounts whether you need it or not; it cannot be reordered.</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: the why strings are already authored on each OrderStep in withdrawalOrder (src/domain/decumulation/index.ts) — reuse verbatim, they are already plain English.</t>
+          <t>EXISTING: withdrawalOrder already injects this step using RMD_START_AGE (73) and rmdAtAge(preTax, age) with the Uniform Lifetime Table divisors (src/domain/decumulation/index.ts).</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>OrderStep.why</t>
+          <t>age, preTax balance, rmdDivisor</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>PIN: identical wording wherever the order is explained (main-screen preview and this sheet render the same strings).</t>
+          <t>PIN: the required amount here = the required-withdrawal figure shown in Plan's retirement section (same helper, same balance).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="46" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Re-run comparison</t>
+          <t xml:space="preserve">   Why explainer</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>'With your order: Will it last 84% → 82%, lasts to age 92 → 90 (estimates)' — suggested versus user order, side by side, before committing.</t>
+          <t>One plain sentence per bucket ('Cash first — it earns the least, so use it before it loses to inflation', 'Roth last — tax-free growth, so let it run'), shown in a tap-through sheet.</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F5 re-run wrapper. Under the hood it re-runs EXISTING math with order-aware tax drag: withdrawalPlan + depletionAge (src/domain/decumulation/index.ts) for the lasts-to age, simulate() (src/domain/retirement/index.ts) for the percentage. Honesty rule: if a reorder changes taxes too little to move the answer, say 'about the same' rather than inventing precision.</t>
+          <t>EXISTING: the why strings are already authored on each OrderStep in withdrawalOrder (src/domain/decumulation/index.ts) — reuse verbatim, they are already plain English.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>user draw_order (NET-NEW stored preference), simulate inputs, depletionAge inputs</t>
+          <t>OrderStep.why</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>PIN: after 'Re-run with my order' is saved, the main screen's preview, the safe draw derivation, and Plan all read the same stored order — one preference, no forks.</t>
+          <t>PIN: identical wording wherever the order is explained (main-screen preview and this sheet render the same strings).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Re-run comparison</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>'With your order: Will it last 84% → 82%, lasts to age 92 → 90 (estimates)' — suggested versus user order, side by side, before committing.</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F5 re-run wrapper. Under the hood it re-runs EXISTING math with order-aware tax drag: withdrawalPlan + depletionAge (src/domain/decumulation/index.ts) for the lasts-to age, simulate() (src/domain/retirement/index.ts) for the percentage. Honesty rule: if a reorder changes taxes too little to move the answer, say 'about the same' rather than inventing precision.</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>user draw_order (NET-NEW stored preference), simulate inputs, depletionAge inputs</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>PIN: after 'Re-run with my order' is saved, the main screen's preview, the safe draw derivation, and Plan all read the same stored order — one preference, no forks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Reset to suggested</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>One tap back to the math's suggested order, with the change previewed the same way.</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>EXISTING default: withdrawalOrder's base order (cash → taxable → pre-tax → Roth).</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>draw_order preference cleared</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>PIN: reset makes the preview identical to a fresh install's suggestion.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="70" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>• Under 73: No pinned step; all four buckets are freely reorderable.
 • 73 or older: Required-withdrawal step pinned on top with its legal explanation; the rest reorderable beneath it.
@@ -8615,9 +9101,179 @@
 • Working user: Sheet opens in projection mode with a banner: 'This is how your future draw would work — a projection, not today's money.'</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+    </row>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>▶ Your monthly income (Social Security · pension · annuity)  ·  lens: retired</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>THE missing front door for the retired lens: where Social Security, pension and annuity amounts are typed in — two numbers a retiree knows by heart, 20 seconds, no bank login. Reached from the Home prompt ('Add your Social Security and pension'), from first-run when the user picks 'a retirement paycheck I can trust' + retired, from the Plan hub, and from the claim screen's already-receiving path. This screen is the source of the paycheck hero's guaranteed half.</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+    </row>
+    <row r="55" ht="325" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>WIREFRAME</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>+------------------------------+
+| &lt; Back   Your monthly income |
+|                              |
+| The money that arrives no    |
+| matter what markets do.      |
+|                              |
+| Social Security              |
+|  I receive it   [yes] [not   |
+|                       yet]   |
+|  Each month   [$ 2,600    ]  |
+|  Arrives on   [the 3rd  v ]  |
+|                              |
+| Pension                      |
+|  Each month   [$ 1,600    ]  |
+|  Paid        [monthly    v]  |
+|  (or quarterly / once a      |
+|   year, in [month])          |
+|                              |
+| Annuity or other             |
+|  [ + Add another income ]    |
+|                              |
+| Your guaranteed income       |
+|  $4,200 a month              |
+|                              |
+| [        Save             ]  |
++------------------------------+</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>BUILD NOTE:
+NET-NEW screen over EXISTING fields — closes the walkthrough's worst finding (guaranteed-income capture was undesigned; both old signposts led to wrong screens). The empty-Home 'Add something by hand … a pension' copy is corrected to route pensions HERE (income), not to the asset form (a pot).</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>INTERACTIONS:
+Home prompt 'Add your Social Security and pension' -&gt; HERE. First-run pick 'a retirement paycheck I can trust' + 'retired' -&gt; asks these two questions immediately after (before any connect talk). Plan hub 'your income' row -&gt; HERE. Claim screen 'Already receiving? enter what you get' -&gt; HERE. Save -&gt; back where she came from, hero updated.</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSIBILITY:
+Number pads for amounts; every field labeled in full; the running total is announced on change. No time pressure, no required fields beyond one amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Social Security block (receiving now vs not yet)</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>'I receive it: yes / not yet' then the monthly amount and arrival day. 'Not yet' routes to the claim-timing decision instead of asking for an amount.</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING fields: ri_ss + frequency + the currentRetirementIncomeMonthly received-now gate (src/domain/income/onboarding.ts); NET-NEW: this dedicated screen (today capture lives only inside legacy onboarding). Day feeds the F5 dated placement (ri_*_day).</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>ri_ss, ri_ss_freq, ri_ss_day, receiving flag</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the amount saved here IS the 'Social Security $2,600' line on Home, Cash flow and Month detail — one field, no copies (the B-31 pin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Pension block with real rhythm</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Monthly amount — or quarterly / once-a-year with the month it lands (a December pension lump shows up in December, not smeared).</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING fields ri_pension + freq; NET-NEW ri_pension_month for annual/quarterly placement (F5 requirement).</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>ri_pension, ri_pension_freq, ri_pension_month</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>PIN: placement here = the month the F5 grid shows the lump — one rhythm field drives both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="46" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Running guaranteed total</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>'Your guaranteed income: $4,200 a month' updates as she types — instant payoff before she even saves.</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Sum of the fields above via retirementIncomeMonthly (src/domain/income/onboarding.ts).</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>sum of ri_*</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>PIN: equals the hero's 'Guaranteed' line the moment she lands back on Home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   STATES</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>• First entry (from Home prompt or first-run): Empty fields, example placeholders in gray; Save enabled once any amount is entered; Home hero updates immediately on save.
+• Not receiving yet: Social Security flips to 'not yet' → amount hidden, one line: 'Deciding when to claim? Compare 62 / 67 / 70 in Plan' with the link.
+• Hidden balances: Amounts mask; labels stay.</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8630,7 +9286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8716,9 +9372,9 @@
 |                              |
 | BIG DECISIONS                |
 | &gt; Claim Social Security      |
-|   window opens Sep 2026  (!) |
-| &gt; Retirement transition +    |
-|   required withdrawals (73)  |
+|   you can claim from Sep 2026 |
+| &gt; Required withdrawals —     |
+|   they start at 73  |
 | &gt; Afford it all? home /      |
 |   college / parents / debt   |
 | &gt; Move money into a Roth     |
@@ -8889,13 +9545,40 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Your monthly income row (retired lens)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>A hub row 'Your income — Social Security $2,600 · Pension $1,600 [edit]' linking to the Monthly-income screen, so guaranteed income is findable from Plan too (not just the Home prompt).</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>retirementIncomeMonthly fields; navigation to the Cash flow Monthly-income screen.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ri_*</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Same amounts as the hero lines — one source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: No fake percent. The will-it-last card becomes 'Answer three questions to see if your money lasts' (age, monthly spending, what you have) linking to Sharpen your plan. Decision rows stay visible but open with their own starter questions.
 • Estimate ready: Full card with chance, range, and the word 'estimate'. Assumption sources (you set it / estimated from your data) are one tap away on the detail screen.
@@ -8903,34 +9586,34 @@
 • Hidden balances: Dollar figures mask to dots using the app-wide hide setting; percentages, ages, and dates stay visible because they are not balances.</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>▶ Social Security claim timing  ·  lens: both</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>The flagship decision: 62 vs 67 vs 70 laid out in your own dollars. You set how long you expect to live; we never crown a winner. — Show what claiming at 62, 67, or 70 pays per month, what each adds up to by the age YOU set, and what each does to the same will-it-last number the hub shows. Ends in the Use-this-plan sheet.</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="325" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="325" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Plan  Claim Social Security|
@@ -8939,7 +9622,7 @@
 | Your statement amount at 67  |
 |  $2,600/mo          [edit]   |
 |                              |
-| Claim   Monthly   By age 90  |
+| Claim   Monthly  Total by 90 |
 | at 62   $1,820    $611,520   |
 | at 67   $2,600    $717,600   |
 | at 70   $3,224    $773,760   |
@@ -8960,233 +9643,261 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Engine mostly EXISTS (simulate already accepts the claim-start age -- guaranteed_start_age in RetirementInputs). NET-NEW: this screen, the benefit-by-claim-age factor helper, window nudge, and the adoption patch. The store already has ssClaimAge/ssMonthly/ssEligible fields waiting (useStore.ts:427).</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Slider drag re-runs totals and bars live (seeded runs are fast and deterministic). Edit statement amount inline. Remind me -&gt; notification permission flow. Any Use-as-my-plan -&gt; adoption sheet. Back -&gt; hub, sandbox discarded with no prompt (nothing was at risk).</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Bars are labeled with age + percent text, never color-only; the three options also read as a plain sentence list for screen readers ('Claiming at 62 pays 1,820 a month...'). Slider has plus/minus stepper buttons as an alternative to dragging. All copy states 'estimate'.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Statement amount input</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>The monthly benefit from the user's own Social Security statement at their full claiming age (67). Everything else on the screen is computed from this one number they typed.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Field EXISTS in the store: ssMonthly on retirementAssumptions (src/store/useStore.ts:427); written via setRetirementAssumptions (:628) only through the adoption sheet -- editing here updates the sandbox.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>ssMonthly (dollars per month, today's dollars), ssEligible</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>PIN: the monthly figure for the ADOPTED claim age = guaranteedMonthly fed to simulate() = the deposit line Cash flow shows for post-claim months. One number, three homes, one source.</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Three-way compare table (monthly + lifetime)</t>
+          <t xml:space="preserve">   Statement amount input</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>For 62 / 67 / 70: the monthly check and the total collected by the live-to age on the slider, all in today's dollars. Plain note under the table: 'earlier = smaller checks for longer; later = bigger checks for fewer years'.</t>
+          <t>The monthly benefit from the user's own Social Security statement at their full claiming age (67). Everything else on the screen is computed from this one number they typed.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F8 helper ssBenefitAtClaimAge(statementMonthly, claimAge) applying the government's standard early-claim reduction and delayed-claim credit percentages; lifetime total = monthly x months from claim age to the slider age (today's dollars, no market math).</t>
+          <t>Field EXISTS in the store: ssMonthly on retirementAssumptions (src/store/useStore.ts:427); written via setRetirementAssumptions (:628) only through the adoption sheet -- editing here updates the sandbox.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>per option: claimAge, monthly, lifetimeToSliderAge</t>
+          <t>ssMonthly (dollars per month, today's dollars), ssEligible</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>PIN: the '67' row always equals the statement amount exactly (the factor at full claiming age is 1.0) -- a unit test pins this so the table can never drift from the user's own input.</t>
+          <t>PIN: the monthly figure for the ADOPTED claim age = guaranteedMonthly fed to simulate() = the deposit line Cash flow shows for post-claim months. One number, three homes, one source.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Effect on will-it-last (three labeled bars)</t>
+          <t xml:space="preserve">   Three-way compare table (monthly + lifetime)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The hub's chance number re-run three times, once per claim age (62: 79%, 67: 84%, 70: 88%), each bar labeled with age + percent, marked 'estimates'.</t>
+          <t>For 62 / 67 / 70: the monthly check and the total collected by the live-to age on the slider, all in today's dollars. Plain note under the table: 'earlier = smaller checks for longer; later = bigger checks for fewer years'.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: simulate() in src/domain/retirement/index.ts:115 already takes guaranteed_start_age (the claim age) and guaranteed_monthly_income as inputs -- no engine change needed, three seeded runs with the sandbox values.</t>
+          <t>NET-NEW: F8 helper ssBenefitAtClaimAge(statementMonthly, claimAge) applying the government's standard early-claim reduction and delayed-claim credit percentages; lifetime total = monthly x months from claim age to the slider age (today's dollars, no market math).</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>guaranteed_start_age = 62/67/70; guaranteed_monthly_income = benefit at that age; all other inputs from the shared assumptions</t>
+          <t>per option: claimAge, monthly, lifetimeToSliderAge</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>PIN: the bar for the CURRENTLY adopted claim age must equal the hub's headline percent to the digit -- same seed, same inputs, agreement test.</t>
+          <t>PIN: the '67' row always equals the statement amount exactly (the factor at full claiming age is 1.0) -- a unit test pins this so the table can never drift from the user's own input.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   If-you-live-to slider</t>
+          <t xml:space="preserve">   Effect on will-it-last (three labeled bars)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>A slider the USER moves (default: the plan-to age already in their plan). It re-computes the lifetime totals and the three bars. Caption: 'Your assumption, not our prediction.'</t>
+          <t>The hub's chance number re-run three times, once per claim age (62: 79%, 67: 84%, 70: 88%), each bar labeled with age + percent, marked 'estimates'.</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Sandbox-only local state (same pattern as today's RetirementCockpit sandbox sliders, RetirementCockpit.tsx ~:193-198); feeds horizon_age into simulate() and the lifetime-total months. Nothing is stored until adoption.</t>
+          <t>EXISTING: simulate() in src/domain/retirement/index.ts:115 already takes guaranteed_start_age (the claim age) and guaranteed_monthly_income as inputs -- no engine change needed, three seeded runs with the sandbox values.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>liveToAge (sandbox); horizonAge (shared, only on adoption)</t>
+          <t>guaranteed_start_age = 62/67/70; guaranteed_monthly_income = benefit at that age; all other inputs from the shared assumptions</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>PIN: slider default = retirementAssumptions.horizonAge so the screen opens showing the same world the hub number lives in.</t>
+          <t>PIN: the bar for the CURRENTLY adopted claim age must equal the hub's headline percent to the digit -- same seed, same inputs, agreement test.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Window + Remind me</t>
+          <t xml:space="preserve">   If-you-live-to slider</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>'Your window opens Sep 2026' (the month they turn 62) and a Remind-me button that schedules a notification. Logistics only -- no opinion attached.</t>
+          <t>A slider the USER moves (default: the plan-to age already in their plan). It re-computes the lifetime totals and the three bars. Caption: 'Your assumption, not our prediction.'</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F8 claim-window nudge -- window dates derived from birth date; reminder uses the app's existing notification scaffolding.</t>
+          <t>Trying it out-only local state (same pattern as today's RetirementCockpit sandbox sliders, RetirementCockpit.tsx ~:193-198); feeds horizon_age into simulate() and the lifetime-total months. Nothing is stored until adoption.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>birth date -&gt; windowOpens (age-62 month), full-age month, age-70 month</t>
+          <t>liveToAge (sandbox); horizonAge (shared, only on adoption)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>PIN: the same window date drives the badge on the Plan hub decision row.</t>
+          <t>PIN: slider default = retirementAssumptions.horizonAge so the screen opens showing the same world the hub number lives in.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Window + Remind me</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>'You can claim any time from Sep 2026 (age 62) to 70 — no deadline' (the month they turn 62) and a Remind-me button that schedules a notification. Logistics only -- no opinion attached.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F8 claim-window nudge -- window dates derived from birth date; reminder uses the app's existing notification scaffolding.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>birth date -&gt; windowOpens (age-62 month), full-age month, age-70 month</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the same window date drives the badge on the Plan hub decision row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Use-as-my-plan buttons (one per option)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Each column has 'Use claim at 62/67/70 as my plan'. Tapping opens the shared adoption sheet with the exact old-to-new list for that option.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>NET-NEW: F11 composer -- the button builds the change-list patch {ssClaimAge, ssMonthly at that age -&gt; guaranteedMonthly, horizonAge if the slider moved}; the sheet does the write via setRetirementAssumptions (src/store/useStore.ts:628).</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>patch: ssClaimAge, guaranteedMonthly, horizonAge</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>PIN: the numbers on the button's preview sheet are the same objects rendered in this screen's table -- one computation, passed through, never recomputed differently.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Statement-amount finder line</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Under the input: 'It's on your Social Security statement — ssa.gov/myaccount or the mailed copy. No rush; the example numbers stay until you have it.'</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>copy only</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: If no statement amount yet: the table shows a worked example in gray labeled 'example numbers', with one input box on top -- 'Type the monthly amount from your Social Security statement to see YOUR numbers.'
-• Scenario running (sandbox): Moving the slider or editing the amount shows the banner 'Sandbox -- this won't change your plan until you tap Use this plan.'
+• Scenario running (sandbox): Moving the slider or editing the amount shows the banner 'Trying it out -- this won't change your plan until you tap Use this plan.'
 • Post-adoption: The adopted column gets a 'your plan' chip; the button row becomes 'Your plan: claim at 67 -- change it' plus the hub's Back-to-previous-plan affordance.
-• Hidden balances: Monthly and lifetime dollars mask to dots; the three percent bars and ages stay visible so the shape of the decision survives hiding.</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-    </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+• Hidden balances: Monthly and lifetime dollars mask to dots; the three percent bars and ages stay visible so the shape of the decision survives hiding.
+• Already receiving benefits: One question above the fold: 'Already receiving Social Security?' → 'Enter what you get each month instead' links to the Monthly-income screen (Cash flow). The claim-timing compare is for the not-yet-claimed; a receiver is never asked for a statement amount or shown claim windows. The hub row chip then reads 'you receive $2,600/mo ✓'.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>▶ Multi-goal trade-off composer  ·  lens: both</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Can I do it all? Parents, college, the mortgage, debt, and retirement saving -- together on one screen, with the shortfall and the retirement cost in plain sight. — Toggle several goals on together, set each one's monthly amount with a slider, and see two verdicts at once: does this month's money cover it, and what does it do to retirement. Ends in Use this plan.</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="387.5" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="400" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Plan   Afford it all?      |
-| Sandbox -- nothing changes   |
+| Trying it out -- nothing changes   |
 | until you tap Use this plan  |
 |                              |
 | Try these together:          |
@@ -9200,12 +9911,16 @@
 | [x] Keep retirement $1,500   |
 |                              |
 | Can you do it all?           |
+|  (your regular bills, incl.  |
+|   the mortgage, are already  |
+|   counted)                   |
 |  Short $400/mo this year     |
 |  [ where the money goes &gt; ]  |
 |                              |
 | Effect on retirement         |
 |  Retire age    67 -&gt; 69      |
 |  Will-it-last  84% -&gt; 76%    |
+|   (Likely -&gt; Uncertain)      |
 |  estimate, not a promise     |
 |                              |
 | What if you trim one?        |
@@ -9217,233 +9932,233 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Single-goal math, capacity, debt payoff, and the retirement solver all EXIST -- the NET-NEW work is the F4 weigher that runs them together, the trim-one sweep, and the commitments field on the shared assumptions object. There is NO multi-goal engine in the code today; this is a headline v1 build item.</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Toggle flips recompute both verdicts immediately; slider drags debounce to one recompute on release. 'Where the money goes' expands inline. Trim hints are tappable -- tapping one applies that amount to the slider (still sandbox). Save prompts for a name.</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Every toggle announces its goal and amount; verdict line is plain text, not color-coded alone (word 'Short'/'Covered' always present). Sliders have stepper buttons and accept typed amounts. Recomputes announce politely via the screen reader ('updated: short 400 a month').</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Goal toggle rows with per-goal sliders</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Each goal (help parents, college fund, home down-payment, extra on debt, keep saving for retirement) with an on/off switch and a monthly-amount slider. Goals with a target show their finish date at the chosen pace.</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: goals seeded by the seedGoals store action (src/store/useStore.ts:583) / goalsFromOnboarding (src/domain/goals/index.ts:51); finish dates from monthsToGoal (src/domain/goals/index.ts:116) and requiredMonthly (:108). NET-NEW: F4 multi-goal weigher runs them TOGETHER (today's math is one goal at a time).</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>per goal: id, label, monthlyAmount (slider), target amount, saved so far, computed end date; retirement row maps to contribMonthly</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>PIN: a goal's single-goal finish date here = the finish date the goal shows anywhere else at the same monthly amount -- both call monthsToGoal().</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Extra-on-debt row</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>A special goal row: the extra monthly payment, the resulting payoff month, and the interest saved ('paid off May 2031, saves $4,100 in interest').</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: payoffPlan() in src/domain/debt/index.ts:96 (takes the debt list + extra monthly, returns the payoff schedule); debts from the store's liabilities.</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>extraMonthly (slider), payoff month, total interest with vs without the extra</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>PIN: payoff month here = payoff month on the Money/Debts screen for the same extra amount -- one payoffPlan() call path.</t>
-        </is>
-      </c>
-    </row>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Can-you-do-it-all verdict</t>
+          <t xml:space="preserve">   Goal toggle rows with per-goal sliders</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>One line: 'Covered, with $250/mo to spare' or 'Short $400/mo this year', plus a tap-through 'where the money goes' stacked list (income in, essentials, each goal, what's left).</t>
+          <t>Each goal (help parents, college fund, home down-payment, extra on debt, keep saving for retirement) with an on/off switch and a monthly-amount slider. Goals with a target show their finish date at the chosen pace.</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>EXISTING capacity: availableToSaveSummary() in src/domain/goals/index.ts:70 -- the same available-to-save number the Cash flow tab uses. NET-NEW: F4 weigher does the subtraction across all toggled goals and builds the stacked list.</t>
+          <t>EXISTING: goals seeded by the seedGoals store action (src/store/useStore.ts:583) / goalsFromOnboarding (src/domain/goals/index.ts:51); finish dates from monthsToGoal (src/domain/goals/index.ts:116) and requiredMonthly (:108). NET-NEW: F4 multi-goal weigher runs them TOGETHER (today's math is one goal at a time).</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>capacity (monthly), committed = sum of toggled monthly amounts, surplus/shortfall = capacity - committed</t>
+          <t>per goal: id, label, monthlyAmount (slider), target amount, saved so far, computed end date; retirement row maps to contribMonthly</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>PIN: 'capacity' = Cash flow tab's available-to-save to the dollar -- same helper, pinned by an agreement test. A shortfall here can never coexist with a surplus on Cash flow.</t>
+          <t>PIN: a goal's single-goal finish date here = the finish date the goal shows anywhere else at the same monthly amount -- both call monthsToGoal().</t>
         </is>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Effect-on-retirement panel</t>
+          <t xml:space="preserve">   Extra-on-debt row</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Two before-and-after lines: retire age (67 -&gt; 69) and will-it-last (84% -&gt; 76%), labeled 'estimate, not a promise'. 'Before' is the adopted plan; 'after' is this combination.</t>
+          <t>A special goal row: the extra monthly payment, the resulting payoff month, and the interest saved ('paid off May 2031, saves $4,100 in interest').</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: solveRetireAge() (src/domain/retirement/index.ts:225) and simulate() (:115), fed with the retirement row's dial as the contribution. NET-NEW: F4 weigher builds the year-by-year contribution picture (goals that end give their money back to saving when they finish).</t>
+          <t>EXISTING: payoffPlan() in src/domain/debt/index.ts:96 (takes the debt list + extra monthly, returns the payoff schedule); debts from the store's liabilities.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>annual_contribution = retirement dial x 12 (goal end dates noted), everything else from shared assumptions</t>
+          <t>extraMonthly (slider), payoff month, total interest with vs without the extra</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>PIN: the 'before' side (67, 84%) = the hub's current numbers exactly -- read from the same selector, not retyped.</t>
+          <t>PIN: payoff month here = payoff month on the Money/Debts screen for the same extra amount -- one payoffPlan() call path.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   What-if-you-trim-one hints</t>
+          <t xml:space="preserve">   Can-you-do-it-all verdict</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>For each active goal, one descriptive line: 'Parents at $1,500 instead: retire 68, chance 81%.' Wording is always what-happens-if, never you-should.</t>
+          <t>One line: 'Covered, with $250/mo to spare' or 'Short $400/mo this year', plus a tap-through 'where the money goes' stacked list (income in, essentials, each goal, what's left).</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F4 weigher re-runs the same math with one dial at a reduced amount per hint; deterministic because simulate() is seeded.</t>
+          <t>EXISTING capacity: availableToSaveSummary() in src/domain/goals/index.ts:70 -- the same available-to-save number the Cash flow tab uses. NET-NEW: F4 weigher does the subtraction across all toggled goals and builds the stacked list.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>per hint: goal, trimmed amount, resulting retire age + chance</t>
+          <t>capacity (monthly), committed = sum of toggled monthly amounts, surplus/shortfall = capacity - committed</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>PIN: applying a hint's amount to the slider reproduces the hint's numbers exactly -- the hint IS a pre-run of the slider, not separate math.</t>
+          <t>PIN: 'capacity' = Cash flow tab's available-to-save to the dollar -- same helper, pinned by an agreement test. A shortfall here can never coexist with a surplus on Cash flow.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Effect-on-retirement panel</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Two before-and-after lines: retire age (67 -&gt; 69) and will-it-last (84% -&gt; 76%), labeled 'estimate, not a promise'. 'Before' is the adopted plan; 'after' is this combination.</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: solveRetireAge() (src/domain/retirement/index.ts:225) and simulate() (:115), fed with the retirement row's dial as the contribution. NET-NEW: F4 weigher builds the year-by-year contribution picture (goals that end give their money back to saving when they finish).</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>annual_contribution = retirement dial x 12 (goal end dates noted), everything else from shared assumptions</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the 'before' side (67, 84%) = the hub's current numbers exactly -- read from the same selector, not retyped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   What-if-you-trim-one hints</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>For each active goal, one descriptive line: 'Parents at $1,500 instead: retire 68, chance 81%.' Wording is always what-happens-if, never you-should.</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F4 weigher re-runs the same math with one dial at a reduced amount per hint; deterministic because simulate() is seeded.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>per hint: goal, trimmed amount, resulting retire age + chance</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>PIN: applying a hint's amount to the slider reproduces the hint's numbers exactly -- the hint IS a pre-run of the slider, not separate math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Save scenario / Use this plan buttons</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Save scenario bookmarks the combination under a name without touching the plan. Use this plan opens the adoption sheet listing every number that would change.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>EXISTING: saveRetirementScenario (src/store/useStore.ts:630-635). NET-NEW: F11 adoption patch = {contribMonthly = retirement dial, commitments = the toggled goal rows}; commitments is a new field on the shared assumptions object.</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>patch: contribMonthly, commitments[] {goalId, label, monthlyAmount, endDate}</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>PIN: after adoption, each commitment appears as a planned monthly line in the Cash flow paycheck view with the same label and amount.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: No goals yet: the screen offers the four starter goals with off switches and typical example amounts in gray ('example'), plus 'Add your own'. Capacity line asks for income/spending if missing, linking to Cash flow setup.
-• Scenario running (sandbox): Persistent top banner: 'Sandbox -- nothing changes until you tap Use this plan.' All slider moves are local; leaving the screen offers 'Save as scenario?' only if something moved.
+• Scenario running (sandbox): Persistent top banner: 'Trying it out -- nothing changes until you tap Use this plan.' All slider moves are local; leaving the screen offers 'Save as scenario?' only if something moved.
 • Post-adoption: Confirmation ('This is your plan now'), goals show 'in your plan' chips, and the hub's Back-to-previous-plan row appears.
 • Hidden balances: Dollar amounts mask; toggles, dates, retire ages, and percents stay readable so the trade-off shape survives.</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-    </row>
-    <row r="31" ht="46" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>▶ Roth conversion (simple scenario)  ·  lens: both</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>One dial, one honest trade: pay some tax now, in a low-tax year, so more of later life is tax-free. Estimates, clearly labeled. — The simple case only (v1): convert X dollars this year. Show the tax cost now, the two later effects (smaller required withdrawals, bigger tax-free bucket), and the will-it-last impact. You decide; ends in Use this plan.</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="362.5" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="362.5" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Plan  Move money to a Roth |
-| Sandbox -- nothing changes   |
+| Trying it out -- nothing changes   |
 | until you tap Use this plan  |
 |                              |
 | Convert this year            |
@@ -9472,202 +10187,202 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 rothConversion() and rmdAtAge() EXIST; today's RothScreen.tsx is a disconnected calculator (local state, zero store writes) -- v1 rewires it to real balances (taxBucketSplit) and the F11 adoption flow. Keep v1 to the single-year, single-amount case exactly as the requirement says; multi-year ladders are out of scope.</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Slider drag recomputes the four result lines on release. Tap the tax line to see and change the rate assumption. Save prompts for a name. Use this plan -&gt; adoption sheet.</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 All four results are plain sentences (screen-reader friendly by construction). Slider has steppers and typed entry. 'Estimate' is text, not a color or icon alone. The why-do-this paragraph targets a grade-6 reading level.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Convert-this-year slider</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Amount to convert, capped at the user's real pre-tax balance shown right below it ('from your pre-tax $310,000').</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: taxBucketSplit() in src/domain/decumulation/index.ts:10 gives the real pre-tax / tax-free / taxable buckets from accounts. Today's src/screens/RothScreen.tsx uses typed-in local numbers (useState :20-22, zero store writes) -- v1 replaces those with real balances.</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>conversionAmount (sandbox slider); preTax and roth from taxBucketSplit(accounts)</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>PIN: the pre-tax balance shown = the pre-tax bucket on Net worth's by-type view -- same taxBucketSplit() call, agreement test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tax-bill-now line</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>'Tax bill next April: about $5,500 more', with a tap-through showing the tax-rate estimate used and a 'change it' control. Always labeled 'estimate -- your tax preparer has the exact number.'</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: rothConversion() in src/domain/planning/index.ts:91 (note: it lives in the planning module, not the retirement module). NET-NEW: surfacing its rate assumption as a user-editable input.</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>conversionAmount x estimated tax rate; rate source shown (estimated from your income / you set it)</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>PIN: the income figure behind the rate estimate = the same income the Cash flow tab uses -- no second income number.</t>
-        </is>
-      </c>
-    </row>
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Later effects pair</t>
+          <t xml:space="preserve">   Convert-this-year slider</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Two lines: 'Required withdrawals at 73: about $980 a year smaller' and 'Tax-free bucket: $118,000 -&gt; $143,000'. Plain footnote: at 73 the government requires yearly withdrawals from pre-tax accounts; converting shrinks that requirement.</t>
+          <t>Amount to convert, capped at the user's real pre-tax balance shown right below it ('from your pre-tax $310,000').</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: rmdAtAge() (src/domain/decumulation/index.ts:100) and the RMD_START_AGE=73 constant (:82) -- run on pre-tax balance with and without the conversion, projected to age 73; buckets from taxBucketSplit().</t>
+          <t>EXISTING: taxBucketSplit() in src/domain/decumulation/index.ts:10 gives the real pre-tax / tax-free / taxable buckets from accounts. Today's src/screens/RothScreen.tsx uses typed-in local numbers (useState :20-22, zero store writes) -- v1 replaces those with real balances.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>rmdAtAge(preTax projected, 73) before vs after; roth bucket before/after</t>
+          <t>conversionAmount (sandbox slider); preTax and roth from taxBucketSplit(accounts)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>PIN: the age-73 required-withdrawal figure here matches the Retirement-transition screen's year-73 row for the same balances -- one rmdAtAge() path.</t>
+          <t>PIN: the pre-tax balance shown = the pre-tax bucket on Net worth's by-type view -- same taxBucketSplit() call, agreement test.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="46" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Effect on will-it-last</t>
+          <t xml:space="preserve">   Tax-bill-now line</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Before-and-after chance ('84% -&gt; 84%, little change'). Honest when the move barely moves the odds -- the point of the decision is taxes, and the copy says so.</t>
+          <t>'Tax bill next April: about $5,500 more', with a tap-through showing the tax-rate estimate used and a 'change it' control. Always labeled 'estimate -- your tax preparer has the exact number.'</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: simulate() (src/domain/retirement/index.ts:115); the conversion nudges the inputs (tax cash paid now reduces the starting balance; later tax savings raise net spending power). NET-NEW: F11 composer maps the conversion into simulate() inputs.</t>
+          <t>EXISTING: rothConversion() in src/domain/planning/index.ts:91 (note: it lives in the planning module, not the retirement module). NET-NEW: surfacing its rate assumption as a user-editable input.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>start_balance minus the tax paid; delta labeled estimate</t>
+          <t>conversionAmount x estimated tax rate; rate source shown (estimated from your income / you set it)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>PIN: the 'before' percent = the hub headline, same selector.</t>
+          <t>PIN: the income figure behind the rate estimate = the same income the Cash flow tab uses -- no second income number.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="46" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Later effects pair</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Two lines: 'Required withdrawals at 73: about $980 a year smaller' and 'Tax-free bucket: $118,000 -&gt; $143,000'. Plain footnote: at 73 the government requires yearly withdrawals from pre-tax accounts; converting shrinks that requirement.</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: rmdAtAge() (src/domain/decumulation/index.ts:100) and the RMD_START_AGE=73 constant (:82) -- run on pre-tax balance with and without the conversion, projected to age 73; buckets from taxBucketSplit().</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>rmdAtAge(preTax projected, 73) before vs after; roth bucket before/after</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the age-73 required-withdrawal figure here matches the Retirement-transition screen's year-73 row for the same balances -- one rmdAtAge() path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Effect on will-it-last</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Before-and-after chance ('84% -&gt; 84%, little change'). Honest when the move barely moves the odds -- the point of the decision is taxes, and the copy says so.</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: simulate() (src/domain/retirement/index.ts:115); the conversion nudges the inputs (tax cash paid now reduces the starting balance; later tax savings raise net spending power). NET-NEW: F11 composer maps the conversion into simulate() inputs.</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>start_balance minus the tax paid; delta labeled estimate</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the 'before' percent = the hub headline, same selector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Save scenario / Use this plan</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Save bookmarks it; Use this plan opens the adoption sheet: conversion amount, this year's extra tax, and the reminder task it creates ('do the conversion with your brokerage before Dec 31').</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>EXISTING: saveRetirementScenario (src/store/useStore.ts:630-635). NET-NEW: F11 patch = {rothConversionThisYear amount} on the shared assumptions object + a dated action item; the app never moves money -- it records the intention and the numbers.</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>patch: rothConversionThisYear; action item with Dec 31 deadline</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>PIN: after adoption, Cash flow's April shows the extra tax as a planned expense with the same dollar figure the sheet previewed.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40" ht="56" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: No pre-tax accounts on file: explains what a conversion is in three sentences and links to 'Add your retirement accounts' on Net worth. No fake slider.
-• Scenario running (sandbox): Banner: 'Sandbox -- nothing changes until you tap Use this plan.' Slider is local state only.
+• Scenario running (sandbox): Banner: 'Trying it out -- nothing changes until you tap Use this plan.' Slider is local state only.
 • Post-adoption: Confirmation + the Dec 31 action item appears here and on the hub; Back-to-previous-plan available. Copy reminds: 'FinWise recorded the plan -- the actual conversion happens at your brokerage.'
 • Hidden balances: Dollar figures mask to dots; the percent lines and the why-do-this explainer stay.</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-    </row>
-    <row r="40" ht="46" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+    </row>
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>▶ Retirement transition + required withdrawals  ·  lens: both</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>The chief-of-staff view of the government-mandated yearly withdrawal: this year's required amount, how much of it is already taken, the deadline, a year-by-year schedule (clearly labeled estimates — future amounts move with balances), and a getting-ready checklist for the run-up to 73. Logistics and reminders — the decision of WHEN in the year to take it stays with you.</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-    </row>
-    <row r="41" ht="362.5" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+    </row>
+    <row r="43" ht="362.5" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Plan  Retirement transition|
@@ -9696,206 +10411,233 @@
 |  [x] Social Security decided |
 |  [x] Paycheck set up         |
 |  [ ] Draw order reviewed  &gt;  |
-|  [ ] Health coverage checked |
+|  [ ] Health coverage checked(i) |
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Engine EXISTS (rmdAtAge, divisors, ledger, completeness); the screen, taken-so-far tagging, and year projection wiring are NET-NEW. This screen satisfies the Plan hub's 'Retirement transition + required withdrawals' row — previously referenced but undesigned (verification blocker #1).</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Mark as taken -&gt; amount + account sheet -&gt; writes the ledger entry and updates 'still to take'. Tap a schedule year -&gt; its assumptions ('based on your balance of $X and the age-75 divisor'). Checklist rows navigate to their screens. Remind me -&gt; notification permission flow.</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 The requirement is read as one sentence ('Required withdrawal for 2026: 15,660 dollars; 8,000 taken; 7,660 still to take by December 31'). 'done'/'left'/'upcoming' are words, never color alone. All rows 44+ points.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="46" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   This-year required amount + taken-so-far + deadline</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>'Required $15,660 · Taken so far $8,000 · Still to take $7,660 by Dec 31' — the mandated amount for the current year against what has already been withdrawn.</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: rmdAtAge(preTaxBalance, age) + RMD_START_AGE=73 — src/domain/decumulation/index.ts:100/:82. Taken-so-far: NET-NEW — sum of this year's withdrawals recorded against pre-tax accounts in the transaction ledger (src/domain/transactions/index.ts) plus manual 'Mark as taken' entries.</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>pre-tax balance (taxBucketSplit), age, ledger WITHDRAWAL rows on pre-tax accounts this year, marked-taken records</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>PIN: the required amount = the pinned first step on the Cash flow draw-order sheet = the year-73 row the Roth screen compares against — one rmdAtAge() path, agreement-tested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="46" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Mark as taken</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>One tap records that the withdrawal (or part of it) was taken outside the app; asks the amount and which account it left. Writes a real ledger entry so history and balances stay honest.</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING engine: recordTransaction (src/store/useStore.ts) with type WITHDRAWAL — the same one ledger every screen reads; NET-NEW: the entry point and the 'counts toward this year's requirement' tag.</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Transaction {type: WITHDRAWAL, account_id, amount, date, note:'required withdrawal'}</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>PIN: marking here reduces 'still to take' AND shows in the account's activity history — one ledger, no side lists.</t>
-        </is>
-      </c>
-    </row>
     <row r="44" ht="46" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Year-by-year schedule (estimates)</t>
+          <t xml:space="preserve">   This-year required amount + taken-so-far + deadline</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>One row per year from 73: the mandated amount — past years show taken/(done), future years show '~' amounts labeled estimates because they move with balances and the divisor table.</t>
+          <t>'Required $15,660 · Taken so far $8,000 · Still to take $7,660 by Dec 31' — the mandated amount for the current year against what has already been withdrawn.</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: rmdAtAge() per projected year using the Uniform Lifetime divisors (src/domain/decumulation/index.ts:100); projection of the pre-tax balance via projectNestEgg (src/domain/retirement/index.ts:198) with the shared plan assumptions.</t>
+          <t>EXISTING: rmdAtAge(preTaxBalance, age) + RMD_START_AGE=73 — src/domain/decumulation/index.ts:100/:82. Taken-so-far: NET-NEW — sum of this year's withdrawals recorded against pre-tax accounts in the transaction ledger (src/domain/transactions/index.ts) plus manual 'Mark as taken' entries.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>per year: age, projected pre-tax balance, divisor, mandated amount, status</t>
+          <t>pre-tax balance (taxBucketSplit), age, ledger WITHDRAWAL rows on pre-tax accounts this year, marked-taken records</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>PIN: the schedule's assumptions are the ONE shared plan-assumptions object — adopting a scenario (e.g., a Roth conversion) visibly changes these future rows (F11 propagation).</t>
+          <t>PIN: the required amount = the pinned first step on the Cash flow draw-order sheet = the year-73 row the Roth screen compares against — one rmdAtAge() path, agreement-tested.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Remind me</t>
+          <t xml:space="preserve">   Mark as taken</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>'Remind me in November' schedules a notification ahead of the Dec 31 deadline. Pure logistics; no advice about timing beyond the legal deadline.</t>
+          <t>One tap records that the withdrawal (or part of it) was taken outside the app; asks the amount and which account it left. Writes a real ledger entry so history and balances stay honest.</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: reuses the app's notification scaffolding (same pattern as the Social Security claim-window reminder).</t>
+          <t>EXISTING engine: recordTransaction (src/store/useStore.ts) with type WITHDRAWAL — the same one ledger every screen reads; NET-NEW: the entry point and the 'counts toward this year's requirement' tag.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>reminder date, year</t>
+          <t>Transaction {type: WITHDRAWAL, account_id, amount, date, note:'required withdrawal'}</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Same reminder component as the claim-window nudge — one wording pattern.</t>
+          <t>PIN: marking here reduces 'still to take' AND shows in the account's activity history — one ledger, no side lists.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Year-by-year schedule (estimates)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>One row per year from 73: the mandated amount — past years show taken/(done), future years show '~' amounts labeled estimates because they move with balances and the divisor table.</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: rmdAtAge() per projected year using the Uniform Lifetime divisors (src/domain/decumulation/index.ts:100); projection of the pre-tax balance via projectNestEgg (src/domain/retirement/index.ts:198) with the shared plan assumptions.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>per year: age, projected pre-tax balance, divisor, mandated amount, status</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the schedule's assumptions are the ONE shared plan-assumptions object — adopting a scenario (e.g., a Roth conversion) visibly changes these future rows (F11 propagation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Remind me</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>'Remind me in November' schedules a notification ahead of the Dec 31 deadline. Pure logistics; no advice about timing beyond the legal deadline.</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: reuses the app's notification scaffolding (same pattern as the Social Security claim-window reminder).</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>reminder date, year</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Same reminder component as the claim-window nudge — one wording pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Getting-ready checklist (before 73)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Four factual readiness items — Social Security decided, paycheck set up, draw order reviewed, health coverage checked — each linking to its screen. Progress, not pressure.</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Four factual readiness items — Social Security decided, paycheck set up, draw order reviewed, health coverage checked — each linking to its screen (health coverage opens a short plain-English note — no dedicated screen in v1). Progress, not pressure.</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>EXISTING pattern: planCompleteness() checks (src/domain/completeness/index.ts:15) extended with transition items; rows link to existing screens (SS decision, Cash flow paycheck, draw-order sheet).</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>checks[] {label, done, route}</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>PIN: item states derive from the same stores the target screens read (e.g., 'Social Security decided' = ssClaimAge set on the shared assumptions) — never a manually-ticked shadow copy.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="56" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Which accounts this applies to</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>'Based on your Fidelity IRA ($415,000) — marked Retirement when you added it [edit]' — the user can SEE which of their accounts the law applies to and fix a wrong tax chip from here.</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: taxBucketSplit pre-tax members (src/domain/decumulation/index.ts:10); edit link opens the account editor.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>pre-tax accounts list</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the listed accounts are exactly the pre-tax bucket the required amount is computed from — a visible input, not a hidden one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="56" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>• Under 73: The required-withdrawal block becomes a plain explainer ('From age 73 the law requires...') with the user's own first-year estimate and start year; the getting-ready checklist leads the screen.
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>• Under 73: The required-withdrawal block becomes a plain explainer ('From age 73 the law requires...') with the user's own first-year estimate and start year; the getting-ready checklist leads the screen. A 'Remind me when this starts for me (2031)' button IS offered here — the under-73 visitor's whole reason for coming.
 • 73+, not yet taken: As wireframed; the amount also appears in Home's What-needs-you ('$7,660 still to take by Dec 31') until done — same figure, same source.
 • Taken in full: 'Done for 2026 (check) — next: ~$16,100 in 2027.' Calm; no badge fireworks.
 • Hidden balances: Dollar amounts mask to dots; ages, deadlines, and checklist stay visible.</t>
         </is>
       </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-    </row>
-    <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+    </row>
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>▶ Use this plan (adoption sheet -- shared component)  ·  lens: both</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>The founder's non-negotiable: before anything changes, see exactly what changes; after it changes, one tap gets you back. — One shared sheet every scenario ends in. Preview the exact old-to-new list, confirm to write to the ONE shared assumptions source, and promise (then deliver) a one-tap way back.</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-    </row>
-    <row r="50" ht="337.5" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+    </row>
+    <row r="53" ht="337.5" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 |        Use this plan?        |
@@ -9912,7 +10654,7 @@
 |    79%      -&gt;   84%         |
 |                              |
 | Where you'll see it          |
-|  * Home -- the top number    |
+|  * Home -- will-it-last strip|
 |  * Cash flow -- months from  |
 |    2033 show the new deposit |
 |  * Plan -- will-it-last and  |
@@ -9926,140 +10668,140 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 This sheet is THE v1.1 addition and is one shared component -- Social Security, multi-goal, Roth, and the cockpit's 'Use as my plan' (RetirementCockpit.tsx ~:236, which today writes silently with no preview or undo) all route through it. Retiring the silent write path is part of the definition of done.</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Confirm -&gt; write + toast + dismiss. Keep-my-current-plan -&gt; dismiss, sandbox intact so the user can keep tweaking. Sheet is dismissible by swipe-down (counts as Keep current). Revert reachable from hub and from the post-adoption toast for the session.</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Arrows in the diff are supplemented with 'changes from ... to ...' for screen readers. Buttons named by outcome ('Make this my plan'), never bare 'OK/Cancel'. Focus lands on the change-list heading when the sheet opens. Minimum 44-point targets.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Old-to-new change list</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Every field that will change, in plain words, old value -&gt; new value -- including the resulting will-it-last shift. Nothing not listed changes.</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F11 composer -- scenarioDiff(currentAssumptions, patch) builds rows {plain label, old, new, unit}. 'Old' reads retirementAssumptions verbatim (src/store/useStore.ts:233); 'new' is the exact patch that will be written -- the preview and the write share ONE payload, so they cannot disagree.</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>diff rows; the patch object itself</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>PIN (the load-bearing one): preview values = written values, by construction -- the confirm handler passes the same patch object it rendered to setRetirementAssumptions (src/store/useStore.ts:628). A contract test asserts render-payload equals write-payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="46" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Where-you'll-see-it list</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Per adoption, the modules that will look different and how, in one line each (Home top number, Cash flow future months, Plan hub, and Net worth's projection when relevant). Sets expectations before the tap.</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F11 propagation map (see engine spec) -- a static table from assumption field to affected surfaces; the sheet filters it to the fields in this patch.</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>field -&gt; [surface, what changes] rows</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>PIN: this list is generated from the same propagation table the engineering wiring implements -- if a surface reads the field, it is on the list; the map is the contract, not marketing copy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="46" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Undo promise + Make-this-my-plan / Keep-my-current-plan buttons</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>A sentence stating exactly where undo lives, then two equal-weight buttons -- confirm is not visually louder than cancel (no dark-pattern nudging; you decide).</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F11 adoptPlan(patch, label): (1) push a full snapshot of current assumptions onto planHistory with label + date, (2) setRetirementAssumptions(patch) (src/store/useStore.ts:628), (3) every subscribed screen re-derives. Revert = setRetirementAssumptions(whole snapshot).</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>planHistory entry {snapshot, label, date}; patch</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>PIN: revert restores every field of the snapshot, then the same agreement test that verified adoption verifies the restore -- round-trip adopt-then-revert leaves every screen byte-identical.</t>
-        </is>
-      </c>
-    </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Old-to-new change list</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Every field that will change, in plain words, old value -&gt; new value -- including the resulting will-it-last shift. Nothing not listed changes.</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F11 composer -- scenarioDiff(currentAssumptions, patch) builds rows {plain label, old, new, unit}. 'Old' reads retirementAssumptions verbatim (src/store/useStore.ts:233); 'new' is the exact patch that will be written -- the preview and the write share ONE payload, so they cannot disagree.</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>diff rows; the patch object itself</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>PIN (the load-bearing one): preview values = written values, by construction -- the confirm handler passes the same patch object it rendered to setRetirementAssumptions (src/store/useStore.ts:628). A contract test asserts render-payload equals write-payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Where-you'll-see-it list</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Per adoption, the modules that will look different and how, in one line each (Home top number, Cash flow future months, Plan hub, and Net worth's projection when relevant). Sets expectations before the tap.</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F11 propagation map (see engine spec) -- a static table from assumption field to affected surfaces; the sheet filters it to the fields in this patch.</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>field -&gt; [surface, what changes] rows</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>PIN: this list is generated from the same propagation table the engineering wiring implements -- if a surface reads the field, it is on the list; the map is the contract, not marketing copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Undo promise + Make-this-my-plan / Keep-my-current-plan buttons</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>A sentence stating exactly where undo lives, then two equal-weight buttons -- confirm is not visually louder than cancel (no dark-pattern nudging; you decide).</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F11 adoptPlan(patch, label): (1) push a full snapshot of current assumptions onto planHistory with label + date, (2) setRetirementAssumptions(patch) (src/store/useStore.ts:628), (3) every subscribed screen re-derives. Revert = setRetirementAssumptions(whole snapshot).</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>planHistory entry {snapshot, label, date}; patch</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>PIN: revert restores every field of the snapshot, then the same agreement test that verified adoption verifies the restore -- round-trip adopt-then-revert leaves every screen byte-identical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Post-adoption confirmation</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>After confirm: brief toast 'This is your plan now', the source screen flips to its adopted state, and the hub gains 'Back to previous plan (saved Jul 2)'.</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>NET-NEW: F11 -- confirmation reads the just-written store values (not the sheet's memory) as a live proof the write landed.</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>toast text from store re-read; hub revert row from planHistory[0]</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>PIN: the confirmation shows the new will-it-last percent pulled through the same selector the hub uses -- if they differ, the write failed and we say so instead of pretending.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="56" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="58" ht="56" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>• Preview (default): Sheet over the scenario screen; scrollable if the change list is long; nothing written yet.
 • Confirmed: Write, snapshot pushed, toast, sheet dismisses back to the source screen in its adopted state.
@@ -10067,34 +10809,34 @@
 • Hidden balances: Dollar values in the diff mask to dots; ages, dates, and percents stay so the user can still verify what changes.</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-    </row>
-    <row r="57" ht="46" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+    </row>
+    <row r="60" ht="46" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>▶ Will-it-last detail  ·  lens: both</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Open the hood on the one number: what it means, the honest range, what moves it, and every assumption behind it with an edit link. — The canonical number's one explanation page: plain meaning, the best-to-worst band, ranked drivers (descriptive what-ifs, not advice), and the full assumptions list with sources and edit links.</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="7" t="n"/>
-    </row>
-    <row r="58" ht="350" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="350" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>WIREFRAME</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>+------------------------------+
 | &lt; Plan   Will it last?       |
@@ -10126,167 +10868,167 @@
 +------------------------------+</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>BUILD NOTE:
 Engine fully EXISTS (simulate with band, completeness, fallback derivations). NET-NEW: this screen, the sensitivity sweep, source tagging (null-field check is trivial), and routing edits through the one-row preview instead of the silent write the cockpit does today.</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
 Tap a driver -&gt; its scenario screen pre-set to that nudge (sandbox). Tap an assumption's edit -&gt; inline editor with a one-row old-to-new preview before writing. Chart supports a horizontal age scrub with values read out as text.</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
 Chart lines are labeled bad/typical/good in words on the plot, never color-only; a text table alternative sits behind 'view as numbers'. Source tags are text. Drivers are an ordered list for screen readers. Meaning sentence targets grade-6 reading level.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="46" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Chance headline + plain meaning</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>'Likely -- 84%' plus one sentence: 'In 84 of 100 possible market futures, your money lasts to age 92.' Never 'you will be fine.'</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: simulate() (src/domain/retirement/index.ts:115) -- it runs many possible market futures with a fixed seed, so the number is stable between visits.</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>chance_of_success; horizonAge for the sentence</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>PIN: identical to the hub, Home hero, and Cash flow strip -- one selector, agreement-tested. This screen explains the number; it never re-derives a different one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="46" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Balance band chart (low / typical / high)</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Projected balance by age as three labeled lines: a bad-markets path, the typical path, and a good-markets path, with the bad-to-good chance range (71%-95%) written as text under it.</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>EXISTING: simulate() with with_band=true returns per-age band points (the BandPoint list: age with low/typical/high balances) -- already built for this.</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>BandPoint[] {age, p10 as 'bad markets', p50 as 'typical', p90 as 'good markets'}</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>PIN: the band's endpoint at the plan-to age is consistent with the chance headline (both from the SAME simulation run, not two runs).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="46" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   What-moves-it-most list</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Top three levers ranked by effect, each with a descriptive one-liner: 'Spending $500 less -&gt; 89%.' Wording is what-happens-if; the user picks what to touch.</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>NET-NEW: F11 sensitivity sweep -- re-run simulate() a handful of times, each with one assumption nudged a standard step, rank by chance delta. Deterministic (seeded), so the ranking is stable.</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>per lever: assumption, nudge size, resulting chance</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>PIN: tapping a lever opens the matching scenario screen pre-set to that nudge, which reproduces the same resulting percent -- the teaser and the tool share one engine.</t>
-        </is>
-      </c>
-    </row>
     <row r="62" ht="46" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Assumptions table with sources + edit links</t>
+          <t xml:space="preserve">   Chance headline + plain meaning</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Every input behind the number -- spending, retire age, plan-to age, return, inflation, Social Security amount and claim age, monthly saving -- each tagged 'you set it' or 'estimated from your data', each with an edit link.</t>
+          <t>'Likely -- 84%' plus one sentence: 'In 84 of 100 possible market futures, your money lasts to age 92.' Never 'you will be fine.'</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: retirementAssumptions fields (src/store/useStore.ts:427); null fields fall back to derived values (e.g. retirementSpendMonthly() in src/domain/retirement/index.ts:48), which is exactly what the 'estimated from your data' tag means. Edits write via setRetirementAssumptions (:628) AFTER a one-row version of the adoption preview.</t>
+          <t>EXISTING: simulate() (src/domain/retirement/index.ts:115) -- it runs many possible market futures with a fixed seed, so the number is stable between visits.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>field, value, source tag (user-set = field non-null; estimated = fallback used), edit route</t>
+          <t>chance_of_success; horizonAge for the sentence</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>PIN: values here = values the simulation actually consumed this run (rendered from the resolved input set, not re-read separately), so the explanation can never drift from the math.</t>
+          <t>PIN: identical to the hub, Home hero, and Cash flow strip -- one selector, agreement-tested. This screen explains the number; it never re-derives a different one.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="46" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Balance band chart (low / typical / high)</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Projected balance by age as three labeled lines: a bad-markets path, the typical path, and a good-markets path, with the bad-to-good chance range (71%-95%) written as text under it.</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: simulate() with with_band=true returns per-age band points (the BandPoint list: age with low/typical/high balances) -- already built for this.</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>BandPoint[] {age, p10 as 'bad markets', p50 as 'typical', p90 as 'good markets'}</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>PIN: the band's endpoint at the plan-to age is consistent with the chance headline (both from the SAME simulation run, not two runs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="46" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   What-moves-it-most list</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Top three levers ranked by effect, each with a descriptive one-liner: 'Spending $500 less -&gt; 89%.' Wording is what-happens-if; the user picks what to touch.</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>NET-NEW: F11 sensitivity sweep -- re-run simulate() a handful of times, each with one assumption nudged a standard step, rank by chance delta. Deterministic (seeded), so the ranking is stable.</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>per lever: assumption, nudge size, resulting chance</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>PIN: tapping a lever opens the matching scenario screen pre-set to that nudge, which reproduces the same resulting percent -- the teaser and the tool share one engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="46" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Assumptions table with sources + edit links</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Every input behind the number -- spending, retire age, plan-to age, return, inflation, Social Security amount and claim age, monthly saving -- each tagged 'you set it' or 'estimated from your data', each with an edit link.</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>EXISTING: retirementAssumptions fields (src/store/useStore.ts:427); null fields fall back to derived values (e.g. retirementSpendMonthly() in src/domain/retirement/index.ts:48), which is exactly what the 'estimated from your data' tag means. Edits write via setRetirementAssumptions (:628) AFTER a one-row version of the adoption preview.</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>field, value, source tag (user-set = field non-null; estimated = fallback used), edit route</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>PIN: values here = values the simulation actually consumed this run (rendered from the resolved input set, not re-read separately), so the explanation can never drift from the math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="46" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Sharpen-your-plan meter</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>'6 of 9' with the next best item named ('Add your pension to firm this up').</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>EXISTING: planCompleteness() (src/domain/completeness/index.ts:15) + SharpenPlanScreen.tsx.</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>doneCount, total, first undone check</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>PIN: same count as the hub and SharpenPlanScreen -- one helper.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="56" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="67" ht="56" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: Shows the three starter questions inline (age, monthly spending, savings today) and builds the first estimate right here -- this screen doubles as the friendly first-run.
 • Estimate ready: Full page as wireframed; 'estimate' appears with the headline and the band.
@@ -10294,9 +11036,9 @@
 • Hidden balances: Chart's dollar axis and assumption dollar values mask; percentages, ages, and the drivers' deltas remain.</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10565,7 +11307,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>WHAT IT IS: a small always-on check that looks at each new money-out transaction and, when one stands out, puts a calm 'Worth a look' card on Home — a fact plus two buttons, never an alarm. INPUTS: every new transaction where money leaves an account (types WITHDRAWAL, TRANSFER to an account we don't recognize as yours, or FEE) from the existing transaction record (fields used: date, type, account, amount, payee text in the note); plus that same account's last 90 days of money-out history. THE RULES (any one trips a flag; checked in this order): (1) UNUSUALLY LARGE — the amount is at least 3 times that account's typical money-out (the middle value of the last 90 days' withdrawals) AND at least $500; if the account has fewer than 5 past withdrawals to learn from, use a flat $1,000 line instead. (2) FIRST-TIME PAYEE — the payee text has never appeared on this account before AND the amount is at least $250. (3) ODD PATTERN — 3 or more money-out transactions from the same account within one calendar day adding to $1,000 or more (shown as one combined card). OUTPUT: a flag saved alongside the transaction: which transaction, which account, which rule fired, the comparison figure the rule used (e.g. 'typical is $310' — stored at flag time so the explanation never drifts), the dollar amount, a status (open / this-was-me / flagged-by-you), and timestamps. WHAT THE PERSON SEES: at most ONE card on Home at a time (the most recent, with 'and 1 more' if others are open), wording always 'Worth a look' with a magnifying-glass icon — the words scam, fraud, and alert never appear in version 1, and the card is never red. RESOLUTION: 'Yes, this was me' closes it (and for a first-time payee, remembers that payee so it never asks again); 'Something's off' shows a short factual checklist (your bank's fraud line is on the back of your card; change any recently shared codes) and keeps a quiet follow-up on Home until marked settled. LEARNING: only the known-payee memory; thresholds are fixed in v1 — no automatic tightening or loosening. HARD LIMITS: we only read; we never block, move, or report anything — the copy says so on the card's detail view. NEW FIELDS: flag record (flag_id, transaction_id, account_id, reason, comparison, amount, status, created_at, resolved_at) and a per-account known-payee list. Proposed home: src/domain/transactions/flags.ts as a pure function reviewTransactions(newOnes, history) → flags, unit-testable with no app plumbing.</t>
+          <t>WHAT IT IS: a small always-on check that looks at each new money-out transaction and, when one stands out, puts a calm 'Worth a look' card on Home — a fact plus two buttons, never an alarm. INPUTS: every new transaction where money leaves an account (types WITHDRAWAL, TRANSFER to an account we don't recognize as yours, or FEE) from the existing transaction record (fields used: date, type, account, amount, payee text in the note); plus that same account's last 90 days of money-out history. THE RULES (any one trips a flag; checked in this order): (1) UNUSUALLY LARGE — the amount is at least 3 times that account's typical money-out (the middle value of the last 90 days' withdrawals) AND at least $500; if the account has fewer than 5 past withdrawals to learn from, use a flat $1,000 line instead. (2) FIRST-TIME PAYEE — the payee text has never appeared on this account before AND the amount is at least $250. (3) ODD PATTERN — 3 or more money-out transactions from the same account within one calendar day adding to $1,000 or more (shown as one combined card). OUTPUT: a flag saved alongside the transaction: which transaction, which account, which rule fired, the comparison figure the rule used (e.g. 'typical is $310' — stored at flag time so the explanation never drifts), the dollar amount, a status (open / this-was-me / flagged-by-you), and timestamps. WHAT THE PERSON SEES: at most ONE card on Home at a time (the most recent, with 'and 1 more' if others are open), wording always 'Worth a look' with a magnifying-glass icon — the words scam, fraud, and alert never appear in version 1, and the card is never red. RESOLUTION: 'Yes, this was me' closes it (and for a first-time payee, remembers that payee so it never asks again); 'Something's off' shows a short factual checklist (call the number on the back of your bank card; change any recently shared codes) and keeps a quiet follow-up on Home until marked settled. LEARNING: only the known-payee memory; thresholds are fixed in v1 — no automatic tightening or loosening. HARD LIMITS: we only read; we never block, move, or report anything — the copy says so on the card's detail view. NEW FIELDS: flag record (flag_id, transaction_id, account_id, reason, comparison, amount, status, created_at, resolved_at) and a per-account known-payee list. Proposed home: src/domain/transactions/flags.ts as a pure function reviewTransactions(newOnes, history) → flags, unit-testable with no app plumbing. MANUAL-ENTRY RULE (added after the retired-persona walkthrough): transactions the user typed by hand are NEVER flagged — you don't interrogate someone about a number they just told you. The watch runs on connected-account transactions only, and the design says so honestly: users with no connected accounts see a one-time quiet note on the transaction history ('When you connect an account, we watch it for odd transactions — hand-typed entries are yours, we never question them') instead of a permanently silent feature that looks broken. Copy consistency: the 'Something's off' checklist says 'call the number on the back of your bank card' — the word 'fraud' stays banned in v1 copy everywhere, including the checklist.</t>
         </is>
       </c>
     </row>
@@ -10683,7 +11425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12435,328 +13177,350 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Plan · Will-it-last chance + band</t>
+          <t>Cash flow · Monthly income capture</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>simulate() -- src/domain/retirement/index.ts:115 (seeded; with_band returns per-age low/typical/high)</t>
+          <t>ri_* fields + retirementIncomeMonthly / currentRetirementIncomeMonthly — src/domain/income/onboarding.ts (screen NET-NEW; ri_*_day/_month placement fields NET-NEW)</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>chance_of_success; BandPoint[age, p10, p50, p90]; inputs resolved from retirementAssumptions (src/store/useStore.ts:233, defaults :427)</t>
+          <t>ri_ss, ri_pension, ri_annuities, freq, day/month</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>One selectWillItLast selector (NET-NEW) feeds Plan hub, Home hero, Cash flow strip, and the detail screen; cross-screen agreement test pins the digit.</t>
+          <t>Saved amounts = the named 'Guaranteed' lines on Home/Cash flow/Month detail — one source (B-31).</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Plan · Shared assumptions object</t>
+          <t>Plan · Will-it-last chance + band</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>retirementAssumptions + setRetirementAssumptions -- src/store/useStore.ts:233 / :628</t>
+          <t>simulate() -- src/domain/retirement/index.ts:115 (seeded; with_band returns per-age low/typical/high)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>retireAge, horizonAge, contribMonthly, spendMonthly, guaranteedMonthly, ssEligible, ssMonthly, ssClaimAge, expectedReturn, inflation, risk (+ NET-NEW: commitments[], rothConversionThisYear, planHistory)</t>
+          <t>chance_of_success; BandPoint[age, p10, p50, p90]; inputs resolved from retirementAssumptions (src/store/useStore.ts:233, defaults :427)</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>The ONE write target for every adoption; today read only by RetirementCockpit + SharpenPlanScreen -- v1 wires Home, Cash flow (F5), and Net worth projection to read it (core F11 build).</t>
+          <t>One selectWillItLast selector (NET-NEW) feeds Plan hub, Home hero, Cash flow strip, and the detail screen; cross-screen agreement test pins the digit.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Plan · Saved scenarios</t>
+          <t>Plan · Shared assumptions object</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>saveRetirementScenario / deleteRetirementScenario / retirementScenarios -- src/store/useStore.ts:630-635 / :636 / :235</t>
+          <t>retirementAssumptions + setRetirementAssumptions -- src/store/useStore.ts:233 / :628</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>id, name, createdAt, assumptions snapshot, retireAge, chance (+ NET-NEW: patch)</t>
+          <t>retireAge, horizonAge, contribMonthly, spendMonthly, guaranteedMonthly, ssEligible, ssMonthly, ssClaimAge, expectedReturn, inflation, risk (+ NET-NEW: commitments[], rothConversionThisYear, planHistory)</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Saving never changes the live plan; reopened scenarios re-run against today's numbers and show both saved and current chance.</t>
+          <t>The ONE write target for every adoption; today read only by RetirementCockpit + SharpenPlanScreen -- v1 wires Home, Cash flow (F5), and Net worth projection to read it (core F11 build).</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Plan · Social Security monthly by claim age</t>
+          <t>Plan · Saved scenarios</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F8 ssBenefitAtClaimAge(statementMonthly, claimAge) -- standard early-reduction / delayed-credit factors on the user's own statement amount</t>
+          <t>saveRetirementScenario / deleteRetirementScenario / retirementScenarios -- src/store/useStore.ts:630-635 / :636 / :235</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>ssMonthly (user input), claimAge 62/67/70 -&gt; monthly; lifetime = monthly x months to the live-to slider age</t>
+          <t>id, name, createdAt, assumptions snapshot, retireAge, chance (+ NET-NEW: patch)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Age-67 row equals the statement amount exactly (factor 1.0), unit-tested; adopted option's monthly = guaranteedMonthly in simulate() = Cash flow's post-claim deposit line.</t>
+          <t>Saving never changes the live plan; reopened scenarios re-run against today's numbers and show both saved and current chance.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Plan · Claim-age effect on will-it-last</t>
+          <t>Plan · Social Security monthly by claim age</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>simulate() with guaranteed_start_age (field EXISTS on RetirementInputs) -- src/domain/retirement/index.ts</t>
+          <t>NET-NEW: F8 ssBenefitAtClaimAge(statementMonthly, claimAge) -- standard early-reduction / delayed-credit factors on the user's own statement amount</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>guaranteed_start_age = 62/67/70; guaranteed_monthly_income = benefit at that age</t>
+          <t>ssMonthly (user input), claimAge 62/67/70 -&gt; monthly; lifetime = monthly x months to the live-to slider age</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Bar for the adopted claim age = hub headline percent, same seed and inputs.</t>
+          <t>Age-67 row equals the statement amount exactly (factor 1.0), unit-tested; adopted option's monthly = guaranteedMonthly in simulate() = Cash flow's post-claim deposit line.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Plan · Multi-goal capacity verdict</t>
+          <t>Plan · Claim-age effect on will-it-last</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>availableToSaveSummary() -- src/domain/goals/index.ts:70; NET-NEW F4 weigher does the combined subtraction</t>
+          <t>simulate() with guaranteed_start_age (field EXISTS on RetirementInputs) -- src/domain/retirement/index.ts</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>capacity, committed = sum of toggled goal monthlies, surplus/shortfall</t>
+          <t>guaranteed_start_age = 62/67/70; guaranteed_monthly_income = benefit at that age</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Capacity = Cash flow tab's available-to-save to the dollar (same helper); shortfall here can never contradict Cash flow.</t>
+          <t>Bar for the adopted claim age = hub headline percent, same seed and inputs.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Plan · Goal finish dates</t>
+          <t>Plan · Multi-goal capacity verdict</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>monthsToGoal() / requiredMonthly() -- src/domain/goals/index.ts:116 / :108; goals seeded via seedGoals (src/store/useStore.ts:583)</t>
+          <t>availableToSaveSummary() -- src/domain/goals/index.ts:70; NET-NEW F4 weigher does the combined subtraction</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>per goal: target, saved, monthlyAmount -&gt; end date</t>
+          <t>capacity, committed = sum of toggled goal monthlies, surplus/shortfall</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Finish date in the composer = finish date on any other goal surface at the same monthly amount.</t>
+          <t>Capacity = Cash flow tab's available-to-save to the dollar (same helper); shortfall here can never contradict Cash flow.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Plan · Extra-on-debt payoff</t>
+          <t>Plan · Goal finish dates</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>payoffPlan() -- src/domain/debt/index.ts:96</t>
+          <t>monthsToGoal() / requiredMonthly() -- src/domain/goals/index.ts:116 / :108; goals seeded via seedGoals (src/store/useStore.ts:583)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>debts + extraMonthly -&gt; payoff month, interest saved</t>
+          <t>per goal: target, saved, monthlyAmount -&gt; end date</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Payoff month here = Money/Debts screen for the same extra -- one call path.</t>
+          <t>Finish date in the composer = finish date on any other goal surface at the same monthly amount.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Plan · Retire-age effect</t>
+          <t>Plan · Extra-on-debt payoff</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>solveRetireAge() -- src/domain/retirement/index.ts:225</t>
+          <t>payoffPlan() -- src/domain/debt/index.ts:96</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>annual_contribution = retirement dial x 12; other inputs from shared assumptions</t>
+          <t>debts + extraMonthly -&gt; payoff month, interest saved</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>'Before' retire age and chance = hub's current numbers, read from the same selector.</t>
+          <t>Payoff month here = Money/Debts screen for the same extra -- one call path.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Plan · Roth buckets + balances</t>
+          <t>Plan · Retire-age effect</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>taxBucketSplit() -- src/domain/decumulation/index.ts:10</t>
+          <t>solveRetireAge() -- src/domain/retirement/index.ts:225</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>accounts -&gt; taxable / pre-tax / tax-free / cash</t>
+          <t>annual_contribution = retirement dial x 12; other inputs from shared assumptions</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Pre-tax balance on the Roth screen = Net worth by-type pre-tax bucket, agreement-tested.</t>
+          <t>'Before' retire age and chance = hub's current numbers, read from the same selector.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Plan · Roth tax-now estimate</t>
+          <t>Plan · Roth buckets + balances</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>rothConversion() -- src/domain/planning/index.ts:91 (planning module, not retirement)</t>
+          <t>taxBucketSplit() -- src/domain/decumulation/index.ts:10</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>conversionAmount x estimated rate; rate source shown and editable</t>
+          <t>accounts -&gt; taxable / pre-tax / tax-free / cash</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Income behind the rate = the same income Cash flow uses; adopted tax cost appears in Cash flow's April as a planned expense with the same figure.</t>
+          <t>Pre-tax balance on the Roth screen = Net worth by-type pre-tax bucket, agreement-tested.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Plan · Required minimum withdrawals</t>
+          <t>Plan · Roth tax-now estimate</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>rmdAtAge() / RMD_START_AGE=73 / withdrawalOrder() -- src/domain/decumulation/index.ts:100 / :82 / :64</t>
+          <t>rothConversion() -- src/domain/planning/index.ts:91 (planning module, not retirement)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>pre-tax balance projected to each year from age 73 -&gt; mandated amount per year</t>
+          <t>conversionAmount x estimated rate; rate source shown and editable</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Age-73 figure on the Roth screen = year-73 row on the retirement-transition schedule -- one rmdAtAge() path.</t>
+          <t>Income behind the rate = the same income Cash flow uses; adopted tax cost appears in Cash flow's April as a planned expense with the same figure.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Plan · Adoption diff + revert</t>
+          <t>Plan · Required minimum withdrawals</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>NET-NEW: F11 scenarioDiff(base, patch), adoptPlan(patch, label), revertPlan() -- snapshot stack planHistory (new store field)</t>
+          <t>rmdAtAge() / RMD_START_AGE=73 / withdrawalOrder() -- src/domain/decumulation/index.ts:100 / :82 / :64</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>diff rows {label, old, new}; planHistory {snapshot, label, date} x5</t>
+          <t>pre-tax balance projected to each year from age 73 -&gt; mandated amount per year</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Preview payload = write payload (same object, contract-tested); adopt-then-revert round-trip leaves every screen byte-identical.</t>
+          <t>Age-73 figure on the Roth screen = year-73 row on the retirement-transition schedule -- one rmdAtAge() path.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Plan · Sharpen-your-plan meter</t>
+          <t>Plan · Adoption diff + revert</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>planCompleteness() -- src/domain/completeness/index.ts:15; screen exists: src/screens/SharpenPlanScreen.tsx</t>
+          <t>NET-NEW: F11 scenarioDiff(base, patch), adoptPlan(patch, label), revertPlan() -- snapshot stack planHistory (new store field)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>checks[], doneCount, total, pct</t>
+          <t>diff rows {label, old, new}; planHistory {snapshot, label, date} x5</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Same count on hub, detail screen, and SharpenPlanScreen -- one helper.</t>
+          <t>Preview payload = write payload (same object, contract-tested); adopt-then-revert round-trip leaves every screen byte-identical.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>Plan · Sharpen-your-plan meter</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>planCompleteness() -- src/domain/completeness/index.ts:15; screen exists: src/screens/SharpenPlanScreen.tsx</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>checks[], doneCount, total, pct</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Same count on hub, detail screen, and SharpenPlanScreen -- one helper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>Plan · Required-withdrawal screen (this year + schedule)</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>rmdAtAge / RMD_START_AGE — src/domain/decumulation/index.ts:100/:82; taken-so-far from the transaction ledger; future years via projectNestEgg (src/domain/retirement/index.ts:198)</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>pre-tax balance, age, divisors, WITHDRAWAL ledger rows, shared plan assumptions</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Required amount = draw-order sheet's pinned step = Roth screen's year-73 comparison — one helper; schedule re-derives when a scenario is adopted (F11).</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.0-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.0-2026-07-01.xlsx
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY the suggested order is what it is, in plain wor</t>
+          <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY why the math orders it that way, in plain words</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>EXISTING: buildInsights(input, 3) rules engine in src/domain/insights/index.ts (priority-ranked, protect/grow/optimize themes) — EXTENDED with two NET-NEW rules (required-withdrawal due, Social Security claim window) and the NET-NEW F10 'worth a look' card, which when open always takes slot 1</t>
+          <t>EXISTING: buildInsights(input, 3) rules engine in src/domain/insights/index.ts (priority-ranked, protect/grow/optimize themes) — EXTENDED with two NET-NEW rules (required-withdrawal due, Social Security claim window) and the NET-NEW F10 'worth a look' card, which when open always takes slot 1 + NET-NEW goal-offtrack rule (monthsToGoal vs the goal's target date → 'College fund is 4 months behind', quantified). FEES / TAX-DRAG nudges (named in the 36-65 strategy): explicitly DEFERRED in v1 — the field dictionary carries no fee/expense-ratio data; recorded deferral, phase-2 with a data source.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="84" customHeight="1">
+    <row r="18" ht="98" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
@@ -2216,7 +2216,8 @@
 • Partial data (accounts connected, plan questions unanswered): Hero and list render from what exists; the will-it-last strip becomes an invitation: 'Answer 3 quick questions in Plan to see your odds &gt; Plan'. Missing pieces are named, never guessed.
 • Balances hidden: Every dollar becomes •••• (see the dedicated hidden-balances screen); percents, words, and the 84% chance stay.
 • Stale connection: Banner slides in under the header (see the dedicated stale screen); numbers gain 'as of &lt;date&gt;' stamps.
-• Fewer than 3 attention items: Show only real items ('What needs you (1)'); if none: 'Nothing needs you today — nice.' Never pad with filler.</t>
+• Fewer than 3 attention items: Show only real items ('What needs you (1)'); if none: 'Nothing needs you today — nice.' Never pad with filler.
+• Milestone crossed: One calm line under the hero, once: 'Your net worth just crossed $500k.' Fact-toned celebration (the strategy's stated retention moment), dismissed on tap, never repeated for the same milestone.</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -6444,8 +6445,9 @@
 |   (down about $7,000)        |
 |  Rates fall 1% -&gt; value      |
 |   roughly $102,000 - $104,000|
-|  Held to maturity you still  |
-|  get $100,000 back.          |
+|  Held to maturity, $100,000   |
+|  comes back — if the issuer  |
+|  pays as promised.          |
 |                              |
 | YOUR REPORTED RETURN (12 mo) |
 |  2.1%  [Edit]                |
@@ -6563,7 +6565,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>'Rates rise 1% -&gt; value roughly $87,000-$89,000 (down about $7,000); rates fall 1% -&gt; roughly $102,000-$104,000. Held to maturity you still get $100,000 back.' Always titled 'Estimate, not a prediction'.</t>
+          <t>'Rates rise 1% -&gt; value roughly $87,000-$89,000 (down about $7,000); rates fall 1% -&gt; roughly $102,000-$104,000. Held to maturity, $100,000 comes back — assuming the issuer pays as promised.' Always titled 'Estimate, not a prediction'.</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6648,7 +6650,7 @@
 • No coupon or no maturity (e.g. a bond fund): The rate-sensitivity card and yield-to-maturity line HIDE (no honest math possible); bond funds with a live ticker show the standard equity-style return instead. Never a guessed number.
 • Bond matured: Banner: 'This bond matured Jun 30, 2036 — record what happened' with [Record payoff]; yields and sensitivity hide (approxYTM already returns nothing when matured).
 • Hide balances on: $95,000 / $100,000 / $4,500 masked to ••••; percentages, dates and years-away remain.
-• Bond FUND (has a ticker, no maturity): Routes to the equity-style detail INCLUDING the vs-the-market card, PLUS one plain sentence in place of the rates card: 'Bond funds fall when interest rates rise — rates rose this year, which is why this fund is down.' The user leaves with the story, not just the number.</t>
+• Bond FUND (has a ticker, no maturity): Routes to the equity-style detail INCLUDING the vs-the-market card, PLUS one plain sentence in place of the rates card: 'Bond funds fall when interest rates rise — when rates rise, funds like this fall.' — stated as the general mechanism; the app never asserts what rates did this year (that would be a live market claim it cannot stand behind). The user leaves with the story, not just the number.</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
@@ -7156,17 +7158,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Monthly amount to add on top of today's saving, and a plain growth-rate choice (5/6/7% presets + your own). Sandbox — nothing changes until adopted.</t>
+          <t>Monthly amount to add on top of today's saving, and a plain growth-rate choice (5/6/7% presets + your own). Trying it out — nothing changes until adopted.</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Sandbox local state (useScenario pattern from the F11 composer); rate presets from the same expectedReturn conventions the Plan uses (retirementAssumptions, src/store/useStore.ts:427).</t>
+          <t>Local trying-it-out state (useScenario pattern from the F11 composer); rate presets from the same expectedReturn conventions the Plan uses (retirementAssumptions, src/store/useStore.ts:427).</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>addMonthly (sandbox), rate (sandbox); base = shared assumptions contribMonthly + expectedReturn</t>
+          <t>addMonthly, rate (both local while trying it out); base = shared assumptions contribMonthly + expectedReturn</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -7292,7 +7294,7 @@
       <c r="B63" s="3" t="inlineStr">
         <is>
           <t>• No retirement inputs yet: Shows 'finish your Plan basics to see this' with the three starter questions link — never a projection built on guessed inputs.
-• Sandbox running: Standard banner: 'this won't change your plan until you tap Use this plan.'
+• Trying it out: Standard banner: 'this won't change your plan until you tap Use this plan.'
 • Post-adoption: Confirmation + revert affordance per the shared adoption sheet; the slider re-baselines to the new committed saving.
 • Hidden balances: Dollar figures mask; percentages and the range shape remain.</t>
         </is>
@@ -7944,7 +7946,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ri_ss, ri_pension, ri_annuities, ri_withdrawals, ri_other, ri_*_freq, NET-NEW ri_*_month (which month an annual/quarterly source lands)</t>
+          <t>ri_ss, ri_pension, ri_annuities, ri_other (ri_withdrawals/ri_rmd EXCLUDED — replaced by the solved safe draw + the pinned required withdrawal, so nothing is counted twice), ri_*_freq, NET-NEW ri_*_month (which month an annual/quarterly source lands)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -8887,7 +8889,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY the suggested order is what it is, in plain words. Guide, never advise: the suggested order is a starting point the user can overrule, and the required-by-law withdrawal after age 73 is pinned and explained, not negotiable.</t>
+          <t>The 'steer it' module: shows the order the math would tap the four kinds of accounts (cash, taxable, pre-tax, Roth), each with its live balance; lets the user reorder and re-run to see how the will-it-last answer and the lasts-to age move; explains WHY why the math orders it that way, in plain words. Guide, never advise: the suggested order is a starting point the user can overrule, and the required-by-law withdrawal after age 73 is pinned and explained, not negotiable.</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -8908,7 +8910,7 @@
 | Where the draw comes from    |
 |  This is the order the math  |
 |  taps your accounts - a      |
-|  suggestion, not an order.   |
+|  starting point — you decide.   |
 |                              |
 |  1  Cash       $38,000  ^ v  |
 |  2  Taxable   $210,000  ^ v  |
@@ -8928,7 +8930,7 @@
 |   (estimates)                |
 |                              |
 | [ Re-run with my order ]     |
-| [ Reset to suggested ]       |
+| [ Reset to the math's order ]       |
 +------------------------------+</t>
         </is>
       </c>
@@ -8941,7 +8943,7 @@
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Drag or tap up/down arrows to reorder (except the pinned step). 'Why this order?' → explainer sheet. 'Re-run with my order' → comparison updates in place, then 'Keep this order' saves. 'Reset to suggested' → previews the default before saving. Closing without saving changes nothing.</t>
+Drag or tap up/down arrows to reorder (except the pinned step). 'Why this order?' → explainer sheet. 'Re-run with my order' → comparison updates in place, then 'Keep this order' saves. 'Reset to the math's order' → previews the default before saving. Closing without saving changes nothing.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -9013,7 +9015,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>One plain sentence per bucket ('Cash first — it earns the least, so use it before it loses to inflation', 'Roth last — tax-free growth, so let it run'), shown in a tap-through sheet.</t>
+          <t>One plain sentence per bucket ('Cash first — it earns the least, so it goes first, before inflation eats it', 'Roth last — tax-free growth, so let it run'), shown in a tap-through sheet.</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -9062,12 +9064,12 @@
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Reset to suggested</t>
+          <t xml:space="preserve">   Reset to the math's order</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>One tap back to the math's suggested order, with the change previewed the same way.</t>
+          <t>One tap back to the math's order, with the change previewed the same way.</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -9756,12 +9758,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Trying it out-only local state (same pattern as today's RetirementCockpit sandbox sliders, RetirementCockpit.tsx ~:193-198); feeds horizon_age into simulate() and the lifetime-total months. Nothing is stored until adoption.</t>
+          <t>local state while trying it out (same pattern as today's RetirementCockpit sandbox sliders, RetirementCockpit.tsx ~:193-198); feeds horizon_age into simulate() and the lifetime-total months. Nothing is stored until adoption.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>liveToAge (sandbox); horizonAge (shared, only on adoption)</t>
+          <t>liveToAge (trying it out); horizonAge (shared, only on adoption)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -9851,7 +9853,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="98" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   STATES</t>
@@ -9860,10 +9862,12 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: If no statement amount yet: the table shows a worked example in gray labeled 'example numbers', with one input box on top -- 'Type the monthly amount from your Social Security statement to see YOUR numbers.'
-• Scenario running (sandbox): Moving the slider or editing the amount shows the banner 'Trying it out -- this won't change your plan until you tap Use this plan.'
+• Scenario running (trying it out): Moving the slider or editing the amount shows the banner 'Trying it out -- this won't change your plan until you tap Use this plan.'
 • Post-adoption: The adopted column gets a 'your plan' chip; the button row becomes 'Your plan: claim at 67 -- change it' plus the hub's Back-to-previous-plan affordance.
 • Hidden balances: Monthly and lifetime dollars mask to dots; the three percent bars and ages stay visible so the shape of the decision survives hiding.
-• Already receiving benefits: One question above the fold: 'Already receiving Social Security?' → 'Enter what you get each month instead' links to the Monthly-income screen (Cash flow). The claim-timing compare is for the not-yet-claimed; a receiver is never asked for a statement amount or shown claim windows. The hub row chip then reads 'you receive $2,600/mo ✓'.</t>
+• Already receiving benefits: One question above the fold: 'Already receiving Social Security?' → 'Enter what you get each month instead' links to the Monthly-income screen (Cash flow). The claim-timing compare is for the not-yet-claimed; a receiver is never asked for a statement amount or shown claim windows. The hub row chip then reads 'you receive $2,600/mo ✓'.
+• Claim ages already passed (e.g. 68, not yet claimed): Options below the user's current age grey out with the word 'passed' ('you can no longer claim at 62'); the compare re-centers on claim-now vs 70, with the monthly amounts adjusted to their actual claiming age. Never shows a choice that no longer exists.
+• Couples (known v1 limitation, stated not hidden): One honest line under the table: 'These figures reflect one person's benefit. Spousal and survivor benefits can change the best timing for couples — v1 doesn't model them yet.' Stated plainly per the truth-teller rule.</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -10122,7 +10126,7 @@
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: No goals yet: the screen offers the four starter goals with off switches and typical example amounts in gray ('example'), plus 'Add your own'. Capacity line asks for income/spending if missing, linking to Cash flow setup.
-• Scenario running (sandbox): Persistent top banner: 'Trying it out -- nothing changes until you tap Use this plan.' All slider moves are local; leaving the screen offers 'Save as scenario?' only if something moved.
+• Scenario running (trying it out): Persistent top banner: 'Trying it out -- nothing changes until you tap Use this plan.' All slider moves are local; leaving the screen offers 'Save as scenario?' only if something moved.
 • Post-adoption: Confirmation ('This is your plan now'), goals show 'in your plan' chips, and the hub's Back-to-previous-plan row appears.
 • Hidden balances: Dollar amounts mask; toggles, dates, retire ages, and percents stay readable so the trade-off shape survives.</t>
         </is>
@@ -10176,7 +10180,7 @@
 | Effect on will-it-last       |
 |  84% -&gt; 84%  little change   |
 |                              |
-| Why do this? You pay tax on  |
+| What this trade is: tax on  |
 | what you convert now; after  |
 | that it grows and comes out  |
 | tax-free, and the government |
@@ -10202,7 +10206,7 @@
       <c r="E34" s="3" t="inlineStr">
         <is>
           <t>ACCESSIBILITY:
-All four results are plain sentences (screen-reader friendly by construction). Slider has steppers and typed entry. 'Estimate' is text, not a color or icon alone. The why-do-this paragraph targets a grade-6 reading level.</t>
+All four results are plain sentences (screen-reader friendly by construction). Slider has steppers and typed entry. 'Estimate' is text, not a color or icon alone. The what-this-trade-is paragraph targets a grade-6 reading level.</t>
         </is>
       </c>
     </row>
@@ -10350,9 +10354,9 @@
       <c r="B40" s="3" t="inlineStr">
         <is>
           <t>• Nothing captured: No pre-tax accounts on file: explains what a conversion is in three sentences and links to 'Add your retirement accounts' on Net worth. No fake slider.
-• Scenario running (sandbox): Banner: 'Trying it out -- nothing changes until you tap Use this plan.' Slider is local state only.
+• Scenario running (trying it out): Banner: 'Trying it out -- nothing changes until you tap Use this plan.' Slider is local state only.
 • Post-adoption: Confirmation + the Dec 31 action item appears here and on the hub; Back-to-previous-plan available. Copy reminds: 'FinWise recorded the plan -- the actual conversion happens at your brokerage.'
-• Hidden balances: Dollar figures mask to dots; the percent lines and the why-do-this explainer stay.</t>
+• Hidden balances: Dollar figures mask to dots; the percent lines and the what-this-trade-is explainer stay.</t>
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
@@ -10877,7 +10881,7 @@
       <c r="D61" s="3" t="inlineStr">
         <is>
           <t>INTERACTIONS:
-Tap a driver -&gt; its scenario screen pre-set to that nudge (sandbox). Tap an assumption's edit -&gt; inline editor with a one-row old-to-new preview before writing. Chart supports a horizontal age scrub with values read out as text.</t>
+Tap a driver -&gt; its scenario screen pre-set to that nudge (trying it out). Tap an assumption's edit -&gt; inline editor with a one-row old-to-new preview before writing. Chart supports a horizontal age scrub with values read out as text.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -11134,7 +11138,8 @@
 - Negative month: a month where bills exceed income shows a real minus with a word+icon flag and one sentence naming the bill and whether the year still covers it. Never clipped to zero, never color-only.
 - Age 73+: the required-by-law withdrawal from pre-tax accounts (rmdAtAge) is surfaced in the draw-order module and counted inside the draw, not added on top — no double counting.
 - Stale balances: every number derived from balances carries an 'as of' date when the newest linked-account sync is older than the threshold; the tone stays calm and factual.
-- Hidden balances: the engine still runs; the UI masks dollars but keeps shape, flags, and words.</t>
+- Hidden balances: the engine still runs; the UI masks dollars but keeps shape, flags, and words.
+GUARANTEED — EXACT DEFINITION (added at strategy-trace review; prevents double counting): guaranteed = ri_ss + ri_pension + ri_annuities + ri_other, received-now only. ri_withdrawals and ri_rmd are EXCLUDED from guaranteed income — the solved safe draw and the pinned required withdrawal REPLACE them, so a savings-draw is never counted twice in the paycheck. The B-31 snapshot pin (snapshot.guaranteed_monthly_income) aligns to this definition. NOTED v1 BOUNDARIES (strategy trace): a big purchase's effect on WHICH account gets tapped shows only via the steer-sheet re-run; overspend-vs-paycheck tracking is scenario-path only ('try it in Plan') — both named boundaries, phase-2 candidates.</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11350,7 @@
 HOW (plain English): a bond is a list of future payments — the yearly coupon each year until maturity, plus the face value at the end. Today's $95,000 value implies a going rate for this bond (its yield if held to maturity, about 5.1% — we already compute this with approxYTM, src/domain/bonds/index.ts:33). To estimate the effect of a rate move, we simply re-add up those same future payments using a rate 1% higher (and 1% lower): each payment is worth a bit less today when rates are higher, and a bit more when rates are lower. That re-added total is the estimated new market value. In code: NET-NEW pure helper bondRateSensitivity(bond, delta) in src/domain/bonds — newValue = sum over each year t of coupon/(1+y+delta)^t, plus face/(1+y+delta)^n, where y = approxYTM, n = yearsToMaturity (src/domain/bonds/index.ts:24).
 INPUTS (all existing fields): face_value, coupon_rate, maturity_date, balance (current value) — via bondInfo (src/domain/bonds/index.ts:16).
 OUTPUT: a RANGE, not a point — the repriced value ± about 1% of value (covers the approximation in the starting yield and payment timing), rounded to the nearest $1,000. Shown both directions: rates up 1% and rates down 1%. Example bond ($100,000 face, 4.5% coupon, 10 years left, worth $95,000): rates up 1% -&gt; roughly $87,000-$89,000 (down about $7,000); rates down 1% -&gt; roughly $102,000-$104,000. Founder's check case: the same bond with about 15 years left lands at roughly $85,000 at 6% yields — the engine uses THIS bond's actual maturity, which is why the number is specific, not generic.
-ALWAYS PAIRED WITH the reassurance line: 'Held to maturity you still get the face value back' — the rate move only matters if sold early.
+ALWAYS PAIRED WITH the reassurance line: 'Held to maturity the face value comes back — assuming the issuer pays as promised' — the rate move only matters if sold early.
 WHEN HIDDEN: no coupon rate, no maturity date, matured (yearsToMaturity &lt;= 0), or no current value — exactly the cases where approxYTM already returns nothing. Bond FUNDS (no maturity) never show this card. Never guess a duration for a bond we don't have facts for.
 LABELING: card title carries 'Estimate, not a prediction'; the info dot explains the method in two sentences; values say 'roughly'. Colorblind-safe: 'down/up' words + arrows, never color alone. Test pins: monotonic (higher rate -&gt; lower value), reproduces the example above within the stated range, hidden-state cases return null.</t>
         </is>
@@ -11410,7 +11415,7 @@
           <t>WHAT IT ANSWERS: 'How much of my invested money is in one thing?' — a quantified fact, no advice.
 HOW: NET-NEW thin helper topHoldingConcentration(rows) in src/domain/performance reusing the weight already computed by attribution (src/domain/performance/index.ts:174): weight = holding value / total priced value. Fires at &gt;= 25% for a single holding. The account-level version EXISTS and stays: the 'concentration' insight at src/domain/insights/index.ts:45 fires when one account holds &gt; 40% of invested money.
 OUTPUT: one line — '31% of your invested money is in one stock (NVDA)' — shown on Invest main between the laggards and the holdings list; tapping scrolls to that holding.
-WORDING RULES: percent + the word 'one stock/one account' + the name; never 'too much', never 'consider selling'. When both holding-level and account-level fire, show the holding-level one (more specific) — never two callouts. Test pins: threshold constants referenced from one place; the callout % equals the same holding's listed share; suppressed below threshold and when total priced value is zero.</t>
+WORDING RULES: percent + the word 'one stock/one account' + the name; never 'too much', never 'consider selling'. When both holding-level and account-level fire, show the holding-level one (more specific) — never two callouts. Test pins: threshold constants referenced from one place; the callout % equals the same holding's listed share; suppressed below threshold and when total priced value is zero. PEER FRAMING (the 36-65 strategy and high-level v1.2 C2 asked for 'more than most people your age'): explicitly DEFERRED in v1 — there is no honest peer-benchmark data source; shipping the phrase without one would be an invented fact. Recorded as a decision, not an omission; phase-2 candidate with a sourced benchmark.</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12884,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>ri_ss, ri_pension, ri_annuities, ri_withdrawals, ri_other, ri_*_freq, NET-NEW ri_*_month/ri_*_day</t>
+          <t>ri_ss, ri_pension, ri_annuities, ri_other (ri_withdrawals/ri_rmd EXCLUDED — replaced by the solved safe draw + the pinned required withdrawal, so nothing is counted twice), ri_*_freq, NET-NEW ri_*_month/ri_*_day</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
